--- a/TestCase/UMPay End-to-End Test Cases.xlsx
+++ b/TestCase/UMPay End-to-End Test Cases.xlsx
@@ -20,8 +20,12 @@
     <sheet name="Global_Transfer" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Profile" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Bills" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Test Result" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="METADATA" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Notification" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Trade_Record" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Wallet" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Payment" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Test Result" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="METADATA" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Login'!$A$8:$AA$23</definedName>
@@ -34,10 +38,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="MMMM\ DD&quot;, &quot;YYYY"/>
     <numFmt numFmtId="165" formatCode="[$-409]M/D/YYYY"/>
     <numFmt numFmtId="166" formatCode="00.00%"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -252,7 +257,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -557,6 +562,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -919,7 +927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:T23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1"/>
@@ -2541,7 +2549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S12"/>
+  <dimension ref="A1:T12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -3223,7 +3231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S12"/>
+  <dimension ref="A1:T12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -3889,7 +3897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S12"/>
+  <dimension ref="A1:T12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -4558,7 +4566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -4871,17 +4879,39 @@
           <t>User is on the Bills page</t>
         </is>
       </c>
-      <c r="J9" s="73" t="n"/>
-      <c r="K9" s="74" t="n"/>
+      <c r="J9" s="73" t="inlineStr">
+        <is>
+          <t>The ledger listed the account's transactions, newest first</t>
+        </is>
+      </c>
+      <c r="K9" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="L9" s="74" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M9" s="58" t="n"/>
-      <c r="N9" s="75" t="n"/>
-      <c r="O9" s="53" t="n"/>
-      <c r="P9" s="76" t="n"/>
+      <c r="M9" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N9" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O9" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P9" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
       <c r="Q9" s="70" t="n"/>
       <c r="R9" s="70" t="n"/>
       <c r="S9" s="77" t="inlineStr">
@@ -4938,17 +4968,39 @@
           <t>User is on the Bills page</t>
         </is>
       </c>
-      <c r="J10" s="73" t="n"/>
-      <c r="K10" s="74" t="n"/>
+      <c r="J10" s="73" t="inlineStr">
+        <is>
+          <t>The type filter offered every kind the platform records</t>
+        </is>
+      </c>
+      <c r="K10" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="L10" s="74" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M10" s="58" t="n"/>
-      <c r="N10" s="75" t="n"/>
-      <c r="O10" s="53" t="n"/>
-      <c r="P10" s="76" t="n"/>
+      <c r="M10" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N10" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O10" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P10" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
       <c r="Q10" s="70" t="n"/>
       <c r="R10" s="70" t="n"/>
       <c r="S10" s="77" t="inlineStr">
@@ -5006,17 +5058,39 @@
           <t>User is on the Bills page</t>
         </is>
       </c>
-      <c r="J11" s="73" t="n"/>
-      <c r="K11" s="74" t="n"/>
+      <c r="J11" s="73" t="inlineStr">
+        <is>
+          <t>Filtering by Convert left only Convert transactions</t>
+        </is>
+      </c>
+      <c r="K11" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="L11" s="74" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M11" s="58" t="n"/>
-      <c r="N11" s="75" t="n"/>
-      <c r="O11" s="53" t="n"/>
-      <c r="P11" s="76" t="n"/>
+      <c r="M11" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N11" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O11" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P11" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
       <c r="Q11" s="70" t="n"/>
       <c r="R11" s="70" t="n"/>
       <c r="S11" s="77" t="inlineStr">
@@ -5074,17 +5148,39 @@
           <t>User is on the Bills page</t>
         </is>
       </c>
-      <c r="J12" s="73" t="n"/>
-      <c r="K12" s="74" t="n"/>
+      <c r="J12" s="73" t="inlineStr">
+        <is>
+          <t>Only amounts between 1 and 100 were listed</t>
+        </is>
+      </c>
+      <c r="K12" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="L12" s="74" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M12" s="58" t="n"/>
-      <c r="N12" s="75" t="n"/>
-      <c r="O12" s="53" t="n"/>
-      <c r="P12" s="76" t="n"/>
+      <c r="M12" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N12" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O12" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P12" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
       <c r="Q12" s="70" t="n"/>
       <c r="R12" s="70" t="n"/>
       <c r="S12" s="77" t="inlineStr">
@@ -5142,17 +5238,39 @@
           <t>User is on the Bills page</t>
         </is>
       </c>
-      <c r="J13" s="73" t="n"/>
-      <c r="K13" s="74" t="n"/>
+      <c r="J13" s="73" t="inlineStr">
+        <is>
+          <t>Only transactions from the chosen day were listed</t>
+        </is>
+      </c>
+      <c r="K13" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="L13" s="74" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M13" s="58" t="n"/>
-      <c r="N13" s="53" t="n"/>
-      <c r="O13" s="53" t="n"/>
-      <c r="P13" s="76" t="n"/>
+      <c r="M13" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N13" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O13" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P13" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
       <c r="Q13" s="70" t="n"/>
       <c r="R13" s="70" t="n"/>
       <c r="S13" s="77" t="inlineStr">
@@ -5210,17 +5328,39 @@
           <t>User is on the Bills page</t>
         </is>
       </c>
-      <c r="J14" s="73" t="n"/>
-      <c r="K14" s="74" t="n"/>
+      <c r="J14" s="73" t="inlineStr">
+        <is>
+          <t>The ledger said it had no data for those dates</t>
+        </is>
+      </c>
+      <c r="K14" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="L14" s="74" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M14" s="58" t="n"/>
-      <c r="N14" s="53" t="n"/>
-      <c r="O14" s="53" t="n"/>
-      <c r="P14" s="76" t="n"/>
+      <c r="M14" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N14" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O14" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P14" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
       <c r="Q14" s="70" t="n"/>
       <c r="R14" s="70" t="n"/>
       <c r="S14" s="77" t="inlineStr">
@@ -5280,17 +5420,39 @@
           <t>User is on the Bills page</t>
         </is>
       </c>
-      <c r="J15" s="73" t="n"/>
-      <c r="K15" s="74" t="n"/>
+      <c r="J15" s="73" t="inlineStr">
+        <is>
+          <t>Reset cleared the filter and brought the whole ledger back</t>
+        </is>
+      </c>
+      <c r="K15" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="L15" s="74" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M15" s="58" t="n"/>
-      <c r="N15" s="53" t="n"/>
-      <c r="O15" s="53" t="n"/>
-      <c r="P15" s="76" t="n"/>
+      <c r="M15" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N15" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O15" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P15" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
       <c r="Q15" s="70" t="n"/>
       <c r="R15" s="70" t="n"/>
       <c r="S15" s="77" t="inlineStr">
@@ -5348,17 +5510,39 @@
           <t>User is on the Bills page</t>
         </is>
       </c>
-      <c r="J16" s="73" t="n"/>
-      <c r="K16" s="74" t="n"/>
+      <c r="J16" s="73" t="inlineStr">
+        <is>
+          <t>The detail named the transaction number, the date and what moved</t>
+        </is>
+      </c>
+      <c r="K16" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="L16" s="74" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M16" s="58" t="n"/>
-      <c r="N16" s="53" t="n"/>
-      <c r="O16" s="53" t="n"/>
-      <c r="P16" s="76" t="n"/>
+      <c r="M16" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N16" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O16" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P16" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
       <c r="Q16" s="70" t="n"/>
       <c r="R16" s="70" t="n"/>
       <c r="S16" s="77" t="inlineStr">
@@ -5416,17 +5600,39 @@
           <t>User is on the Bills page</t>
         </is>
       </c>
-      <c r="J17" s="73" t="n"/>
-      <c r="K17" s="74" t="n"/>
+      <c r="J17" s="73" t="inlineStr">
+        <is>
+          <t>Download produced a receipt file with content in it</t>
+        </is>
+      </c>
+      <c r="K17" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="L17" s="74" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M17" s="58" t="n"/>
-      <c r="N17" s="53" t="n"/>
-      <c r="O17" s="53" t="n"/>
-      <c r="P17" s="76" t="n"/>
+      <c r="M17" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N17" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O17" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P17" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
       <c r="Q17" s="70" t="n"/>
       <c r="R17" s="70" t="n"/>
       <c r="S17" s="77" t="inlineStr">
@@ -5485,17 +5691,39 @@
           <t>User is on the Bills page</t>
         </is>
       </c>
-      <c r="J18" s="73" t="n"/>
-      <c r="K18" s="74" t="n"/>
+      <c r="J18" s="73" t="inlineStr">
+        <is>
+          <t>Share offered a way to copy the transaction</t>
+        </is>
+      </c>
+      <c r="K18" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="L18" s="74" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M18" s="58" t="n"/>
-      <c r="N18" s="53" t="n"/>
-      <c r="O18" s="53" t="n"/>
-      <c r="P18" s="76" t="n"/>
+      <c r="M18" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N18" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O18" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P18" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
       <c r="Q18" s="70" t="n"/>
       <c r="R18" s="70" t="n"/>
       <c r="S18" s="77" t="inlineStr">
@@ -5552,6 +5780,5589 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
+  <dimension ref="A1:T19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
+    <col width="10" customWidth="1" style="51" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1" s="51">
+      <c r="A1" s="52" t="inlineStr">
+        <is>
+          <t>Project Name</t>
+        </is>
+      </c>
+      <c r="B1" s="53" t="inlineStr">
+        <is>
+          <t>UMPay</t>
+        </is>
+      </c>
+      <c r="D1" s="54" t="n"/>
+      <c r="H1" s="55" t="n"/>
+      <c r="K1" s="56" t="n"/>
+      <c r="L1" s="54" t="n"/>
+      <c r="M1" s="54" t="n"/>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" s="51">
+      <c r="A2" s="57" t="inlineStr">
+        <is>
+          <t>Module/Feature Name</t>
+        </is>
+      </c>
+      <c r="B2" s="58" t="inlineStr">
+        <is>
+          <t>Notification</t>
+        </is>
+      </c>
+      <c r="D2" s="54" t="n"/>
+      <c r="K2" s="56" t="n"/>
+      <c r="L2" s="54" t="n"/>
+      <c r="M2" s="54" t="n"/>
+      <c r="N2" s="54" t="n"/>
+      <c r="P2" s="59" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="Q2" s="59" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="R2" s="59" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1" s="51">
+      <c r="A3" s="57" t="inlineStr">
+        <is>
+          <t>Reference Document</t>
+        </is>
+      </c>
+      <c r="B3" s="58" t="n"/>
+      <c r="D3" s="54" t="n"/>
+      <c r="N3" s="60" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="O3" s="61">
+        <f>COUNTIF(K:K,"PASS")</f>
+        <v/>
+      </c>
+      <c r="P3" s="61">
+        <f>COUNTIFS(K:K,"PASS",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="61">
+        <f>COUNTIFS(K:K,"PASS",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R3" s="61">
+        <f>COUNTIFS(K:K,"PASS",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1" s="51">
+      <c r="A4" s="57" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B4" s="53" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="D4" s="54" t="n"/>
+      <c r="N4" s="60" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="O4" s="62">
+        <f>COUNTIF(K:K,"FAIL")</f>
+        <v/>
+      </c>
+      <c r="P4" s="62">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q4" s="62">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R4" s="62">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1" s="51">
+      <c r="A5" s="57" t="inlineStr">
+        <is>
+          <t>Date of Creation</t>
+        </is>
+      </c>
+      <c r="B5" s="63" t="n">
+        <v>46272</v>
+      </c>
+      <c r="D5" s="54" t="n"/>
+      <c r="N5" s="60" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="O5" s="64">
+        <f>COUNTIF(K:K,"PENDING")</f>
+        <v/>
+      </c>
+      <c r="P5" s="64">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q5" s="64">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R5" s="64">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1" s="51">
+      <c r="A6" s="57" t="inlineStr">
+        <is>
+          <t>Date of Review</t>
+        </is>
+      </c>
+      <c r="B6" s="63" t="n">
+        <v>46272</v>
+      </c>
+      <c r="D6" s="54" t="n"/>
+      <c r="H6" s="55" t="n"/>
+    </row>
+    <row r="7" ht="20.25" customHeight="1" s="51">
+      <c r="D7" s="54" t="n"/>
+      <c r="H7" s="55" t="n"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1" s="51">
+      <c r="A8" s="65" t="inlineStr">
+        <is>
+          <t>TEST CASE ID</t>
+        </is>
+      </c>
+      <c r="B8" s="65" t="inlineStr">
+        <is>
+          <t>TEST SCENARIO</t>
+        </is>
+      </c>
+      <c r="C8" s="65" t="inlineStr">
+        <is>
+          <t>TEST CASE</t>
+        </is>
+      </c>
+      <c r="D8" s="65" t="inlineStr">
+        <is>
+          <t>TEST CATEGORY</t>
+        </is>
+      </c>
+      <c r="E8" s="65" t="inlineStr">
+        <is>
+          <t>PRE-CONDITION</t>
+        </is>
+      </c>
+      <c r="F8" s="65" t="inlineStr">
+        <is>
+          <t>TEST STEPS</t>
+        </is>
+      </c>
+      <c r="G8" s="65" t="inlineStr">
+        <is>
+          <t>TEST DATA</t>
+        </is>
+      </c>
+      <c r="H8" s="65" t="inlineStr">
+        <is>
+          <t>EXPECTED RESULTS</t>
+        </is>
+      </c>
+      <c r="I8" s="65" t="inlineStr">
+        <is>
+          <t>POST CONDITION</t>
+        </is>
+      </c>
+      <c r="J8" s="65" t="inlineStr">
+        <is>
+          <t>ACTUAL RESULT</t>
+        </is>
+      </c>
+      <c r="K8" s="65" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="L8" s="65" t="inlineStr">
+        <is>
+          <t>PRIORITY</t>
+        </is>
+      </c>
+      <c r="M8" s="65" t="inlineStr">
+        <is>
+          <t>TESTER</t>
+        </is>
+      </c>
+      <c r="N8" s="65" t="inlineStr">
+        <is>
+          <t>TEST DATE</t>
+        </is>
+      </c>
+      <c r="O8" s="65" t="inlineStr">
+        <is>
+          <t>DEVICE</t>
+        </is>
+      </c>
+      <c r="P8" s="65" t="inlineStr">
+        <is>
+          <t>BROWSER</t>
+        </is>
+      </c>
+      <c r="Q8" s="65" t="inlineStr">
+        <is>
+          <t>ISSUE LINK</t>
+        </is>
+      </c>
+      <c r="R8" s="65" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="S8" s="66" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" s="51">
+      <c r="A9" s="67" t="inlineStr">
+        <is>
+          <t>TC_001</t>
+        </is>
+      </c>
+      <c r="B9" s="79" t="inlineStr">
+        <is>
+          <t>Notification</t>
+        </is>
+      </c>
+      <c r="C9" s="72" t="inlineStr">
+        <is>
+          <t>The bell opens the account's notifications</t>
+        </is>
+      </c>
+      <c r="D9" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E9" s="71" t="inlineStr">
+        <is>
+          <t>User is signed in</t>
+        </is>
+      </c>
+      <c r="F9" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Notifications page
+-Then the notifications should list what the platform has told the account</t>
+        </is>
+      </c>
+      <c r="G9" s="72" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H9" s="73" t="inlineStr">
+        <is>
+          <t>The bell should open the notification page, listing what the platform has told the account</t>
+        </is>
+      </c>
+      <c r="I9" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Notification page</t>
+        </is>
+      </c>
+      <c r="J9" s="73" t="inlineStr">
+        <is>
+          <t>The bell opened /v2/notification and listed the notifications</t>
+        </is>
+      </c>
+      <c r="K9" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L9" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M9" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N9" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O9" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P9" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q9" s="70" t="n"/>
+      <c r="R9" s="70" t="n"/>
+      <c r="S9" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15.75" customHeight="1" s="51">
+      <c r="A10" s="67" t="inlineStr">
+        <is>
+          <t>TC_002</t>
+        </is>
+      </c>
+      <c r="B10" s="79" t="inlineStr">
+        <is>
+          <t>Notification</t>
+        </is>
+      </c>
+      <c r="C10" s="72" t="inlineStr">
+        <is>
+          <t>The notifications are kept in three tabs</t>
+        </is>
+      </c>
+      <c r="D10" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E10" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Notification page</t>
+        </is>
+      </c>
+      <c r="F10" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Notifications page
+-Then the notifications should offer the tabs "Transactions, Announcements, Messages"</t>
+        </is>
+      </c>
+      <c r="G10" s="72" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H10" s="73" t="inlineStr">
+        <is>
+          <t>The page should offer the Transactions, Announcements and Messages tabs</t>
+        </is>
+      </c>
+      <c r="I10" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Notification page</t>
+        </is>
+      </c>
+      <c r="J10" s="73" t="inlineStr">
+        <is>
+          <t>Transactions, Announcements and Messages were all offered</t>
+        </is>
+      </c>
+      <c r="K10" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L10" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M10" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N10" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O10" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P10" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q10" s="70" t="n"/>
+      <c r="R10" s="70" t="n"/>
+      <c r="S10" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15.75" customHeight="1" s="51">
+      <c r="A11" s="67" t="inlineStr">
+        <is>
+          <t>TC_003</t>
+        </is>
+      </c>
+      <c r="B11" s="79" t="inlineStr">
+        <is>
+          <t>Notification Transactions</t>
+        </is>
+      </c>
+      <c r="C11" s="72" t="inlineStr">
+        <is>
+          <t>Every transaction notification names its kind, amount, currency and date</t>
+        </is>
+      </c>
+      <c r="D11" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E11" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Notification page</t>
+        </is>
+      </c>
+      <c r="F11" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Notifications page
+-Then each notification should name its kind, amount, currency and when it happened</t>
+        </is>
+      </c>
+      <c r="G11" s="72" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H11" s="73" t="inlineStr">
+        <is>
+          <t>Every card should name the kind of transaction, the amount, the currency and when it happened</t>
+        </is>
+      </c>
+      <c r="I11" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Notification page</t>
+        </is>
+      </c>
+      <c r="J11" s="73" t="inlineStr">
+        <is>
+          <t>Every card named its kind, amount, currency and created date</t>
+        </is>
+      </c>
+      <c r="K11" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L11" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M11" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N11" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O11" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P11" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q11" s="70" t="n"/>
+      <c r="R11" s="70" t="n"/>
+      <c r="S11" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="51">
+      <c r="A12" s="67" t="inlineStr">
+        <is>
+          <t>TC_004</t>
+        </is>
+      </c>
+      <c r="B12" s="79" t="inlineStr">
+        <is>
+          <t>Notification Transactions</t>
+        </is>
+      </c>
+      <c r="C12" s="72" t="inlineStr">
+        <is>
+          <t>The transaction notifications are listed newest first</t>
+        </is>
+      </c>
+      <c r="D12" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E12" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Notification page</t>
+        </is>
+      </c>
+      <c r="F12" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Notifications page
+-Then the notifications should be listed newest first</t>
+        </is>
+      </c>
+      <c r="G12" s="72" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H12" s="73" t="inlineStr">
+        <is>
+          <t>The newest notification should be at the top and the oldest at the bottom</t>
+        </is>
+      </c>
+      <c r="I12" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Notification page</t>
+        </is>
+      </c>
+      <c r="J12" s="73" t="inlineStr">
+        <is>
+          <t>The notifications were listed newest first</t>
+        </is>
+      </c>
+      <c r="K12" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L12" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M12" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N12" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O12" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P12" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q12" s="70" t="n"/>
+      <c r="R12" s="70" t="n"/>
+      <c r="S12" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15.75" customHeight="1" s="51">
+      <c r="A13" s="67" t="inlineStr">
+        <is>
+          <t>TC_005</t>
+        </is>
+      </c>
+      <c r="B13" s="79" t="inlineStr">
+        <is>
+          <t>Notification Transactions</t>
+        </is>
+      </c>
+      <c r="C13" s="72" t="inlineStr">
+        <is>
+          <t>Each amount is written with the symbol its currency uses</t>
+        </is>
+      </c>
+      <c r="D13" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E13" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Notification page</t>
+        </is>
+      </c>
+      <c r="F13" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Notifications page
+-Then each amount should be written with the symbol its currency uses</t>
+        </is>
+      </c>
+      <c r="G13" s="72" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H13" s="73" t="inlineStr">
+        <is>
+          <t>Each amount should be a figure carrying its wallet symbol, and a wallet should be written the same way on every card</t>
+        </is>
+      </c>
+      <c r="I13" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Notification page</t>
+        </is>
+      </c>
+      <c r="J13" s="73" t="inlineStr">
+        <is>
+          <t>Each amount carried its wallet symbol, the same one throughout</t>
+        </is>
+      </c>
+      <c r="K13" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L13" s="74" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M13" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N13" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O13" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P13" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q13" s="70" t="n"/>
+      <c r="R13" s="70" t="n"/>
+      <c r="S13" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1" s="51">
+      <c r="A14" s="67" t="inlineStr">
+        <is>
+          <t>TC_006</t>
+        </is>
+      </c>
+      <c r="B14" s="79" t="inlineStr">
+        <is>
+          <t>Notification Transactions</t>
+        </is>
+      </c>
+      <c r="C14" s="72" t="inlineStr">
+        <is>
+          <t>Reaching the end of the list brings in older notifications</t>
+        </is>
+      </c>
+      <c r="D14" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E14" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Notification page</t>
+        </is>
+      </c>
+      <c r="F14" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Notifications page
+-And I scroll to the end of the notifications
+-Then more notifications should have been brought in</t>
+        </is>
+      </c>
+      <c r="G14" s="72" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H14" s="73" t="inlineStr">
+        <is>
+          <t>Scrolling to the bottom should bring in the next of the notifications</t>
+        </is>
+      </c>
+      <c r="I14" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Notification page</t>
+        </is>
+      </c>
+      <c r="J14" s="73" t="inlineStr">
+        <is>
+          <t>Reaching the end took the list from 20 notifications to 60</t>
+        </is>
+      </c>
+      <c r="K14" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L14" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M14" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N14" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O14" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P14" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q14" s="70" t="n"/>
+      <c r="R14" s="70" t="n"/>
+      <c r="S14" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1" s="51">
+      <c r="A15" s="67" t="inlineStr">
+        <is>
+          <t>TC_007</t>
+        </is>
+      </c>
+      <c r="B15" s="79" t="inlineStr">
+        <is>
+          <t>Notification Announcements</t>
+        </is>
+      </c>
+      <c r="C15" s="72" t="inlineStr">
+        <is>
+          <t>The Announcements tab shows what the platform has announced</t>
+        </is>
+      </c>
+      <c r="D15" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E15" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Notification page</t>
+        </is>
+      </c>
+      <c r="F15" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Notifications page
+-And I move to the tab named in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-Then every announcement should carry a message and when it arrived</t>
+        </is>
+      </c>
+      <c r="G15" s="72" t="inlineStr">
+        <is>
+          <t>Tab: Announcements</t>
+        </is>
+      </c>
+      <c r="H15" s="73" t="inlineStr">
+        <is>
+          <t>Every announcement should carry its own message and when it arrived</t>
+        </is>
+      </c>
+      <c r="I15" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Notification page</t>
+        </is>
+      </c>
+      <c r="J15" s="73" t="inlineStr">
+        <is>
+          <t>All 20 announcements carried a message and when they arrived</t>
+        </is>
+      </c>
+      <c r="K15" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L15" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M15" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N15" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O15" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P15" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q15" s="70" t="n"/>
+      <c r="R15" s="70" t="n"/>
+      <c r="S15" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="51">
+      <c r="A16" s="67" t="inlineStr">
+        <is>
+          <t>TC_008</t>
+        </is>
+      </c>
+      <c r="B16" s="79" t="inlineStr">
+        <is>
+          <t>Notification Messages</t>
+        </is>
+      </c>
+      <c r="C16" s="72" t="inlineStr">
+        <is>
+          <t>The Messages tab shows the conversation with customer service</t>
+        </is>
+      </c>
+      <c r="D16" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E16" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Notification page</t>
+        </is>
+      </c>
+      <c r="F16" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Notifications page
+-And I move to the tab named in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-Then the conversation with customer service should be shown</t>
+        </is>
+      </c>
+      <c r="G16" s="72" t="inlineStr">
+        <is>
+          <t>Tab: Messages</t>
+        </is>
+      </c>
+      <c r="H16" s="73" t="inlineStr">
+        <is>
+          <t>The conversation with customer service should be shown</t>
+        </is>
+      </c>
+      <c r="I16" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Notification page</t>
+        </is>
+      </c>
+      <c r="J16" s="73" t="inlineStr">
+        <is>
+          <t>The conversation with customer service was shown</t>
+        </is>
+      </c>
+      <c r="K16" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L16" s="74" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M16" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N16" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O16" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P16" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q16" s="70" t="n"/>
+      <c r="R16" s="70" t="n"/>
+      <c r="S16" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1" s="51">
+      <c r="A17" s="67" t="inlineStr">
+        <is>
+          <t>TC_009</t>
+        </is>
+      </c>
+      <c r="B17" s="79" t="inlineStr">
+        <is>
+          <t>Notification Tabs</t>
+        </is>
+      </c>
+      <c r="C17" s="72" t="inlineStr">
+        <is>
+          <t>Moving to another tab changes what is listed</t>
+        </is>
+      </c>
+      <c r="D17" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E17" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Notification page</t>
+        </is>
+      </c>
+      <c r="F17" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Notifications page
+-And I move to the tab named in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-Then what is listed should change</t>
+        </is>
+      </c>
+      <c r="G17" s="72" t="inlineStr">
+        <is>
+          <t>Tab: Announcements</t>
+        </is>
+      </c>
+      <c r="H17" s="73" t="inlineStr">
+        <is>
+          <t>Choosing another tab should change what is listed rather than only highlighting the tab</t>
+        </is>
+      </c>
+      <c r="I17" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Notification page</t>
+        </is>
+      </c>
+      <c r="J17" s="73" t="inlineStr">
+        <is>
+          <t>Choosing another tab changed what was listed</t>
+        </is>
+      </c>
+      <c r="K17" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L17" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M17" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N17" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O17" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P17" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q17" s="70" t="n"/>
+      <c r="R17" s="70" t="n"/>
+      <c r="S17" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15.75" customHeight="1" s="51">
+      <c r="A18" s="67" t="inlineStr">
+        <is>
+          <t>TC_010</t>
+        </is>
+      </c>
+      <c r="B18" s="79" t="inlineStr">
+        <is>
+          <t>Notification Read State</t>
+        </is>
+      </c>
+      <c r="C18" s="72" t="inlineStr">
+        <is>
+          <t>The unread count agrees with what the list marks unread</t>
+        </is>
+      </c>
+      <c r="D18" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E18" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Notification page</t>
+        </is>
+      </c>
+      <c r="F18" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Notifications page
+-And I look through the notifications
+-Then the unread count should agree with the marks in the list</t>
+        </is>
+      </c>
+      <c r="G18" s="72" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H18" s="73" t="inlineStr">
+        <is>
+          <t>The list should never mark more notifications unread than the bell says are waiting, and nothing should be marked when the bell says nothing is unread</t>
+        </is>
+      </c>
+      <c r="I18" s="73" t="inlineStr">
+        <is>
+          <t>The notifications seen are marked read</t>
+        </is>
+      </c>
+      <c r="J18" s="73" t="inlineStr">
+        <is>
+          <t>The list marked 116 unread against a bell of 412, which agree</t>
+        </is>
+      </c>
+      <c r="K18" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L18" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M18" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N18" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O18" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P18" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q18" s="70" t="n"/>
+      <c r="R18" s="70" t="n"/>
+      <c r="S18" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="51">
+      <c r="A19" s="67" t="inlineStr">
+        <is>
+          <t>TC_011</t>
+        </is>
+      </c>
+      <c r="B19" s="79" t="inlineStr">
+        <is>
+          <t>Notification Read State</t>
+        </is>
+      </c>
+      <c r="C19" s="72" t="inlineStr">
+        <is>
+          <t>What has been read is not forgotten when the page is loaded again</t>
+        </is>
+      </c>
+      <c r="D19" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E19" s="71" t="inlineStr">
+        <is>
+          <t>The notifications have been looked through</t>
+        </is>
+      </c>
+      <c r="F19" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Notifications page
+-And I look through the notifications
+-Then looking should not have added to the unread count
+-When I reload the notifications
+-Then what has been seen should still be marked read</t>
+        </is>
+      </c>
+      <c r="G19" s="72" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H19" s="73" t="inlineStr">
+        <is>
+          <t>Looking should never add to the unread count, and the count should not climb back after the page is loaded again</t>
+        </is>
+      </c>
+      <c r="I19" s="73" t="inlineStr">
+        <is>
+          <t>The notifications seen are marked read</t>
+        </is>
+      </c>
+      <c r="J19" s="73" t="inlineStr">
+        <is>
+          <t>The count did not climb after looking, nor after a reload</t>
+        </is>
+      </c>
+      <c r="K19" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L19" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M19" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N19" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O19" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P19" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q19" s="70" t="n"/>
+      <c r="R19" s="70" t="n"/>
+      <c r="S19" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="7">
+    <dataValidation sqref="K9:K19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"PASS,FAIL,PENDING"</formula1>
+    </dataValidation>
+    <dataValidation sqref="P9:P19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>METADATA!$H$2:$H$8</formula1>
+    </dataValidation>
+    <dataValidation sqref="O9:O19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>METADATA!$J$2:$J$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="D9:D19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>METADATA!$N$2:$N$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="B4 M9:M19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>METADATA!$F$2:$F$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="L9:L19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"HIGH,MEDIUM,LOW"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"WPAY,UMPay,OFL,UNCS"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S14" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S16" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S19" r:id="rId11"/>
+  </hyperlinks>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.9840277777777779" bottom="0.9840277777777779" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="0" useFirstPageNumber="0" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:T19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
+    <col width="10" customWidth="1" style="51" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1" s="51">
+      <c r="A1" s="52" t="inlineStr">
+        <is>
+          <t>Project Name</t>
+        </is>
+      </c>
+      <c r="B1" s="53" t="inlineStr">
+        <is>
+          <t>UMPay</t>
+        </is>
+      </c>
+      <c r="D1" s="54" t="n"/>
+      <c r="H1" s="55" t="n"/>
+      <c r="K1" s="56" t="n"/>
+      <c r="L1" s="54" t="n"/>
+      <c r="M1" s="54" t="n"/>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" s="51">
+      <c r="A2" s="57" t="inlineStr">
+        <is>
+          <t>Module/Feature Name</t>
+        </is>
+      </c>
+      <c r="B2" s="58" t="inlineStr">
+        <is>
+          <t>Trade Record</t>
+        </is>
+      </c>
+      <c r="D2" s="54" t="n"/>
+      <c r="K2" s="56" t="n"/>
+      <c r="L2" s="54" t="n"/>
+      <c r="M2" s="54" t="n"/>
+      <c r="N2" s="54" t="n"/>
+      <c r="P2" s="59" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="Q2" s="59" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="R2" s="59" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1" s="51">
+      <c r="A3" s="57" t="inlineStr">
+        <is>
+          <t>Reference Document</t>
+        </is>
+      </c>
+      <c r="B3" s="58" t="n"/>
+      <c r="D3" s="54" t="n"/>
+      <c r="N3" s="60" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="O3" s="61">
+        <f>COUNTIF(K:K,"PASS")</f>
+        <v/>
+      </c>
+      <c r="P3" s="61">
+        <f>COUNTIFS(K:K,"PASS",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="61">
+        <f>COUNTIFS(K:K,"PASS",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R3" s="61">
+        <f>COUNTIFS(K:K,"PASS",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1" s="51">
+      <c r="A4" s="57" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B4" s="53" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="D4" s="54" t="n"/>
+      <c r="N4" s="60" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="O4" s="62">
+        <f>COUNTIF(K:K,"FAIL")</f>
+        <v/>
+      </c>
+      <c r="P4" s="62">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q4" s="62">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R4" s="62">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1" s="51">
+      <c r="A5" s="57" t="inlineStr">
+        <is>
+          <t>Date of Creation</t>
+        </is>
+      </c>
+      <c r="B5" s="63" t="n">
+        <v>46272</v>
+      </c>
+      <c r="D5" s="54" t="n"/>
+      <c r="N5" s="60" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="O5" s="64">
+        <f>COUNTIF(K:K,"PENDING")</f>
+        <v/>
+      </c>
+      <c r="P5" s="64">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q5" s="64">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R5" s="64">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1" s="51">
+      <c r="A6" s="57" t="inlineStr">
+        <is>
+          <t>Date of Review</t>
+        </is>
+      </c>
+      <c r="B6" s="63" t="n">
+        <v>46272</v>
+      </c>
+      <c r="D6" s="54" t="n"/>
+      <c r="H6" s="55" t="n"/>
+    </row>
+    <row r="7" ht="20.25" customHeight="1" s="51">
+      <c r="D7" s="54" t="n"/>
+      <c r="H7" s="55" t="n"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1" s="51">
+      <c r="A8" s="65" t="inlineStr">
+        <is>
+          <t>TEST CASE ID</t>
+        </is>
+      </c>
+      <c r="B8" s="65" t="inlineStr">
+        <is>
+          <t>TEST SCENARIO</t>
+        </is>
+      </c>
+      <c r="C8" s="65" t="inlineStr">
+        <is>
+          <t>TEST CASE</t>
+        </is>
+      </c>
+      <c r="D8" s="65" t="inlineStr">
+        <is>
+          <t>TEST CATEGORY</t>
+        </is>
+      </c>
+      <c r="E8" s="65" t="inlineStr">
+        <is>
+          <t>PRE-CONDITION</t>
+        </is>
+      </c>
+      <c r="F8" s="65" t="inlineStr">
+        <is>
+          <t>TEST STEPS</t>
+        </is>
+      </c>
+      <c r="G8" s="65" t="inlineStr">
+        <is>
+          <t>TEST DATA</t>
+        </is>
+      </c>
+      <c r="H8" s="65" t="inlineStr">
+        <is>
+          <t>EXPECTED RESULTS</t>
+        </is>
+      </c>
+      <c r="I8" s="65" t="inlineStr">
+        <is>
+          <t>POST CONDITION</t>
+        </is>
+      </c>
+      <c r="J8" s="65" t="inlineStr">
+        <is>
+          <t>ACTUAL RESULT</t>
+        </is>
+      </c>
+      <c r="K8" s="65" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="L8" s="65" t="inlineStr">
+        <is>
+          <t>PRIORITY</t>
+        </is>
+      </c>
+      <c r="M8" s="65" t="inlineStr">
+        <is>
+          <t>TESTER</t>
+        </is>
+      </c>
+      <c r="N8" s="65" t="inlineStr">
+        <is>
+          <t>TEST DATE</t>
+        </is>
+      </c>
+      <c r="O8" s="65" t="inlineStr">
+        <is>
+          <t>DEVICE</t>
+        </is>
+      </c>
+      <c r="P8" s="65" t="inlineStr">
+        <is>
+          <t>BROWSER</t>
+        </is>
+      </c>
+      <c r="Q8" s="65" t="inlineStr">
+        <is>
+          <t>ISSUE LINK</t>
+        </is>
+      </c>
+      <c r="R8" s="65" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="S8" s="66" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" s="51">
+      <c r="A9" s="67" t="inlineStr">
+        <is>
+          <t>TC_001</t>
+        </is>
+      </c>
+      <c r="B9" s="79" t="inlineStr">
+        <is>
+          <t>Trade Record</t>
+        </is>
+      </c>
+      <c r="C9" s="72" t="inlineStr">
+        <is>
+          <t>The profile drawer opens the account's trade record</t>
+        </is>
+      </c>
+      <c r="D9" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E9" s="71" t="inlineStr">
+        <is>
+          <t>User is signed in</t>
+        </is>
+      </c>
+      <c r="F9" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Trade Record page
+-Then the trade record should list the orders the account has raised</t>
+        </is>
+      </c>
+      <c r="G9" s="72" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H9" s="73" t="inlineStr">
+        <is>
+          <t>The trade record should open from the profile drawer, listing the orders the account has raised</t>
+        </is>
+      </c>
+      <c r="I9" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Trade Record page</t>
+        </is>
+      </c>
+      <c r="J9" s="73" t="inlineStr">
+        <is>
+          <t>The drawer opened /v2/trade-record and listed 20 orders</t>
+        </is>
+      </c>
+      <c r="K9" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L9" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M9" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N9" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O9" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P9" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q9" s="70" t="n"/>
+      <c r="R9" s="70" t="n"/>
+      <c r="S9" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15.75" customHeight="1" s="51">
+      <c r="A10" s="67" t="inlineStr">
+        <is>
+          <t>TC_002</t>
+        </is>
+      </c>
+      <c r="B10" s="79" t="inlineStr">
+        <is>
+          <t>Trade Record</t>
+        </is>
+      </c>
+      <c r="C10" s="72" t="inlineStr">
+        <is>
+          <t>The trade record is kept in three tabs</t>
+        </is>
+      </c>
+      <c r="D10" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E10" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Trade Record page</t>
+        </is>
+      </c>
+      <c r="F10" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Trade Record page
+-Then the trade record should offer the tabs "Deposit/Withdraw, International Transfer, International School Fee"</t>
+        </is>
+      </c>
+      <c r="G10" s="72" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H10" s="73" t="inlineStr">
+        <is>
+          <t>The page should offer the Deposit/Withdraw, International Transfer and International School Fee tabs</t>
+        </is>
+      </c>
+      <c r="I10" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Trade Record page</t>
+        </is>
+      </c>
+      <c r="J10" s="73" t="inlineStr">
+        <is>
+          <t>Deposit/Withdraw, International Transfer and International School Fee were all offered</t>
+        </is>
+      </c>
+      <c r="K10" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L10" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M10" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N10" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O10" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P10" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q10" s="70" t="n"/>
+      <c r="R10" s="70" t="n"/>
+      <c r="S10" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15.75" customHeight="1" s="51">
+      <c r="A11" s="67" t="inlineStr">
+        <is>
+          <t>TC_003</t>
+        </is>
+      </c>
+      <c r="B11" s="79" t="inlineStr">
+        <is>
+          <t>Trade Record Deposit/Withdraw</t>
+        </is>
+      </c>
+      <c r="C11" s="72" t="inlineStr">
+        <is>
+          <t>Every order names its number, currency, amount and how it ended</t>
+        </is>
+      </c>
+      <c r="D11" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E11" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Trade Record page</t>
+        </is>
+      </c>
+      <c r="F11" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Trade Record page
+-Then every order should name its number, currency, amount and how it ended</t>
+        </is>
+      </c>
+      <c r="G11" s="72" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H11" s="73" t="inlineStr">
+        <is>
+          <t>Every order should name its number, its currency, its amount and the status it ended in</t>
+        </is>
+      </c>
+      <c r="I11" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Trade Record page</t>
+        </is>
+      </c>
+      <c r="J11" s="73" t="inlineStr">
+        <is>
+          <t>All 20 orders named their number, currency, amount and status</t>
+        </is>
+      </c>
+      <c r="K11" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L11" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M11" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N11" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O11" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P11" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q11" s="70" t="n"/>
+      <c r="R11" s="70" t="n"/>
+      <c r="S11" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="51">
+      <c r="A12" s="67" t="inlineStr">
+        <is>
+          <t>TC_004</t>
+        </is>
+      </c>
+      <c r="B12" s="79" t="inlineStr">
+        <is>
+          <t>Trade Record Deposit/Withdraw</t>
+        </is>
+      </c>
+      <c r="C12" s="72" t="inlineStr">
+        <is>
+          <t>No two orders share a number</t>
+        </is>
+      </c>
+      <c r="D12" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E12" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Trade Record page</t>
+        </is>
+      </c>
+      <c r="F12" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Trade Record page
+-Then no two orders should share a number</t>
+        </is>
+      </c>
+      <c r="G12" s="72" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H12" s="73" t="inlineStr">
+        <is>
+          <t>No order number should appear more than once in the list</t>
+        </is>
+      </c>
+      <c r="I12" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Trade Record page</t>
+        </is>
+      </c>
+      <c r="J12" s="73" t="inlineStr">
+        <is>
+          <t>All 20 orders carried a number of their own</t>
+        </is>
+      </c>
+      <c r="K12" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L12" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M12" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N12" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O12" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P12" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q12" s="70" t="n"/>
+      <c r="R12" s="70" t="n"/>
+      <c r="S12" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15.75" customHeight="1" s="51">
+      <c r="A13" s="67" t="inlineStr">
+        <is>
+          <t>TC_005</t>
+        </is>
+      </c>
+      <c r="B13" s="79" t="inlineStr">
+        <is>
+          <t>Trade Record Deposit/Withdraw</t>
+        </is>
+      </c>
+      <c r="C13" s="72" t="inlineStr">
+        <is>
+          <t>A converted order shows both what was received and the rate</t>
+        </is>
+      </c>
+      <c r="D13" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E13" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Trade Record page</t>
+        </is>
+      </c>
+      <c r="F13" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Trade Record page
+-Then any converted order should show both what was received and the rate</t>
+        </is>
+      </c>
+      <c r="G13" s="72" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H13" s="73" t="inlineStr">
+        <is>
+          <t>An order that was converted should show both the amount received and the exchange rate, never one without the other</t>
+        </is>
+      </c>
+      <c r="I13" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Trade Record page</t>
+        </is>
+      </c>
+      <c r="J13" s="73" t="inlineStr">
+        <is>
+          <t>6 of the 20 orders were converted, each showing both the received amount and the rate</t>
+        </is>
+      </c>
+      <c r="K13" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L13" s="74" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M13" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N13" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O13" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P13" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q13" s="70" t="n"/>
+      <c r="R13" s="70" t="n"/>
+      <c r="S13" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1" s="51">
+      <c r="A14" s="67" t="inlineStr">
+        <is>
+          <t>TC_006</t>
+        </is>
+      </c>
+      <c r="B14" s="79" t="inlineStr">
+        <is>
+          <t>Trade Record Deposit/Withdraw</t>
+        </is>
+      </c>
+      <c r="C14" s="72" t="inlineStr">
+        <is>
+          <t>Reaching the end of the record brings in older orders</t>
+        </is>
+      </c>
+      <c r="D14" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E14" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Trade Record page</t>
+        </is>
+      </c>
+      <c r="F14" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Trade Record page
+-And I scroll to the end of the trade record
+-Then more orders should have been brought in</t>
+        </is>
+      </c>
+      <c r="G14" s="72" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H14" s="73" t="inlineStr">
+        <is>
+          <t>Scrolling to the bottom should bring in the next of the orders</t>
+        </is>
+      </c>
+      <c r="I14" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Trade Record page</t>
+        </is>
+      </c>
+      <c r="J14" s="73" t="inlineStr">
+        <is>
+          <t>Reaching the end took the list from 20 orders to 60</t>
+        </is>
+      </c>
+      <c r="K14" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L14" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M14" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N14" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O14" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P14" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q14" s="70" t="n"/>
+      <c r="R14" s="70" t="n"/>
+      <c r="S14" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1" s="51">
+      <c r="A15" s="67" t="inlineStr">
+        <is>
+          <t>TC_007</t>
+        </is>
+      </c>
+      <c r="B15" s="79" t="inlineStr">
+        <is>
+          <t>Trade Record Transfers</t>
+        </is>
+      </c>
+      <c r="C15" s="72" t="inlineStr">
+        <is>
+          <t>An international transfer is charged its fee plus its amount</t>
+        </is>
+      </c>
+      <c r="D15" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E15" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Trade Record page</t>
+        </is>
+      </c>
+      <c r="F15" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Trade Record page
+-And I move to the trade record tab named in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-Then every international transfer should add up to its total</t>
+        </is>
+      </c>
+      <c r="G15" s="72" t="inlineStr">
+        <is>
+          <t>Tab: International Transfer</t>
+        </is>
+      </c>
+      <c r="H15" s="73" t="inlineStr">
+        <is>
+          <t>The total charged should be exactly the fee plus the amount sent</t>
+        </is>
+      </c>
+      <c r="I15" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Trade Record page</t>
+        </is>
+      </c>
+      <c r="J15" s="73" t="inlineStr">
+        <is>
+          <t>All 20 international transfers were charged exactly their fee plus their amount</t>
+        </is>
+      </c>
+      <c r="K15" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L15" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M15" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N15" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O15" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P15" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q15" s="70" t="n"/>
+      <c r="R15" s="70" t="n"/>
+      <c r="S15" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="51">
+      <c r="A16" s="67" t="inlineStr">
+        <is>
+          <t>TC_008</t>
+        </is>
+      </c>
+      <c r="B16" s="79" t="inlineStr">
+        <is>
+          <t>Trade Record Transfers</t>
+        </is>
+      </c>
+      <c r="C16" s="72" t="inlineStr">
+        <is>
+          <t>A school fee order names its order number, total and when it was created</t>
+        </is>
+      </c>
+      <c r="D16" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E16" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Trade Record page</t>
+        </is>
+      </c>
+      <c r="F16" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Trade Record page
+-And I move to the trade record tab named in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-Then every school fee order should name its order number, total and when it was created</t>
+        </is>
+      </c>
+      <c r="G16" s="72" t="inlineStr">
+        <is>
+          <t>Tab: International School Fee</t>
+        </is>
+      </c>
+      <c r="H16" s="73" t="inlineStr">
+        <is>
+          <t>Every school fee order should name its order number, its total and when it was created</t>
+        </is>
+      </c>
+      <c r="I16" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Trade Record page</t>
+        </is>
+      </c>
+      <c r="J16" s="73" t="inlineStr">
+        <is>
+          <t>Every school fee order named its order number, total and created date</t>
+        </is>
+      </c>
+      <c r="K16" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L16" s="74" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M16" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N16" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O16" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P16" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q16" s="70" t="n"/>
+      <c r="R16" s="70" t="n"/>
+      <c r="S16" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1" s="51">
+      <c r="A17" s="67" t="inlineStr">
+        <is>
+          <t>TC_009</t>
+        </is>
+      </c>
+      <c r="B17" s="79" t="inlineStr">
+        <is>
+          <t>Trade Record</t>
+        </is>
+      </c>
+      <c r="C17" s="72" t="inlineStr">
+        <is>
+          <t>Moving to another tab changes what the record lists</t>
+        </is>
+      </c>
+      <c r="D17" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E17" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Trade Record page</t>
+        </is>
+      </c>
+      <c r="F17" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Trade Record page
+-And I move to the trade record tab named in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-Then what the trade record lists should change</t>
+        </is>
+      </c>
+      <c r="G17" s="72" t="inlineStr">
+        <is>
+          <t>Tab: International Transfer</t>
+        </is>
+      </c>
+      <c r="H17" s="73" t="inlineStr">
+        <is>
+          <t>Choosing another tab should change what is listed rather than only highlighting the tab</t>
+        </is>
+      </c>
+      <c r="I17" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Trade Record page</t>
+        </is>
+      </c>
+      <c r="J17" s="73" t="inlineStr">
+        <is>
+          <t>Choosing another tab changed what was listed</t>
+        </is>
+      </c>
+      <c r="K17" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L17" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M17" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N17" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O17" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P17" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q17" s="70" t="n"/>
+      <c r="R17" s="70" t="n"/>
+      <c r="S17" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15.75" customHeight="1" s="51">
+      <c r="A18" s="67" t="inlineStr">
+        <is>
+          <t>TC_010</t>
+        </is>
+      </c>
+      <c r="B18" s="79" t="inlineStr">
+        <is>
+          <t>Trade Record Order</t>
+        </is>
+      </c>
+      <c r="C18" s="72" t="inlineStr">
+        <is>
+          <t>An order in the record opens the order itself</t>
+        </is>
+      </c>
+      <c r="D18" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E18" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Trade Record page</t>
+        </is>
+      </c>
+      <c r="F18" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Trade Record page
+-And I open the newest order
+-Then the order's own page should open</t>
+        </is>
+      </c>
+      <c r="G18" s="72" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H18" s="73" t="inlineStr">
+        <is>
+          <t>Opening an order should go to that order's own page, at an address naming the order</t>
+        </is>
+      </c>
+      <c r="I18" s="73" t="inlineStr">
+        <is>
+          <t>User is on the order's own page</t>
+        </is>
+      </c>
+      <c r="J18" s="73" t="inlineStr">
+        <is>
+          <t>The order opened at /deposit/zG0XAW5778xqoDYL?orderId=zG0XAW5778xqoDYL&amp;orderStatus=6&amp;navigateFrom=%2Fv2%2Ftrade-record</t>
+        </is>
+      </c>
+      <c r="K18" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L18" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M18" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N18" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O18" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P18" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q18" s="70" t="n"/>
+      <c r="R18" s="70" t="n"/>
+      <c r="S18" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="51">
+      <c r="A19" s="67" t="inlineStr">
+        <is>
+          <t>TC_011</t>
+        </is>
+      </c>
+      <c r="B19" s="79" t="inlineStr">
+        <is>
+          <t>Trade Record Order</t>
+        </is>
+      </c>
+      <c r="C19" s="72" t="inlineStr">
+        <is>
+          <t>Going back from an order returns to the trade record</t>
+        </is>
+      </c>
+      <c r="D19" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E19" s="71" t="inlineStr">
+        <is>
+          <t>User is on an order's own page</t>
+        </is>
+      </c>
+      <c r="F19" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Trade Record page
+-And I open the newest order
+-Then the order's own page should open
+-When I go back to the trade record
+-Then the trade record should be listing again</t>
+        </is>
+      </c>
+      <c r="G19" s="72" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H19" s="73" t="inlineStr">
+        <is>
+          <t>Going back should return to the trade record, still listing the orders</t>
+        </is>
+      </c>
+      <c r="I19" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Trade Record page</t>
+        </is>
+      </c>
+      <c r="J19" s="73" t="inlineStr">
+        <is>
+          <t>Going back returned to the trade record, still listing its orders</t>
+        </is>
+      </c>
+      <c r="K19" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L19" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M19" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N19" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O19" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P19" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q19" s="70" t="n"/>
+      <c r="R19" s="70" t="n"/>
+      <c r="S19" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="7">
+    <dataValidation sqref="K9:K19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"PASS,FAIL,PENDING"</formula1>
+    </dataValidation>
+    <dataValidation sqref="P9:P19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>METADATA!$H$2:$H$8</formula1>
+    </dataValidation>
+    <dataValidation sqref="O9:O19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>METADATA!$J$2:$J$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="D9:D19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>METADATA!$N$2:$N$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="B4 M9:M19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>METADATA!$F$2:$F$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="L9:L19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"HIGH,MEDIUM,LOW"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"WPAY,UMPay,OFL,UNCS"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S14" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S16" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S19" r:id="rId11"/>
+  </hyperlinks>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.9840277777777779" bottom="0.9840277777777779" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="0" useFirstPageNumber="0" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:T21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
+    <col width="10" customWidth="1" style="51" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1" s="51">
+      <c r="A1" s="52" t="inlineStr">
+        <is>
+          <t>Project Name</t>
+        </is>
+      </c>
+      <c r="B1" s="53" t="inlineStr">
+        <is>
+          <t>UMPay</t>
+        </is>
+      </c>
+      <c r="D1" s="54" t="n"/>
+      <c r="H1" s="55" t="n"/>
+      <c r="K1" s="56" t="n"/>
+      <c r="L1" s="54" t="n"/>
+      <c r="M1" s="54" t="n"/>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" s="51">
+      <c r="A2" s="57" t="inlineStr">
+        <is>
+          <t>Module/Feature Name</t>
+        </is>
+      </c>
+      <c r="B2" s="58" t="inlineStr">
+        <is>
+          <t>Wallet</t>
+        </is>
+      </c>
+      <c r="D2" s="54" t="n"/>
+      <c r="K2" s="56" t="n"/>
+      <c r="L2" s="54" t="n"/>
+      <c r="M2" s="54" t="n"/>
+      <c r="N2" s="54" t="n"/>
+      <c r="P2" s="59" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="Q2" s="59" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="R2" s="59" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1" s="51">
+      <c r="A3" s="57" t="inlineStr">
+        <is>
+          <t>Reference Document</t>
+        </is>
+      </c>
+      <c r="B3" s="58" t="n"/>
+      <c r="D3" s="54" t="n"/>
+      <c r="N3" s="60" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="O3" s="61">
+        <f>COUNTIF(K:K,"PASS")</f>
+        <v/>
+      </c>
+      <c r="P3" s="61">
+        <f>COUNTIFS(K:K,"PASS",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="61">
+        <f>COUNTIFS(K:K,"PASS",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R3" s="61">
+        <f>COUNTIFS(K:K,"PASS",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1" s="51">
+      <c r="A4" s="57" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B4" s="53" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="D4" s="54" t="n"/>
+      <c r="N4" s="60" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="O4" s="62">
+        <f>COUNTIF(K:K,"FAIL")</f>
+        <v/>
+      </c>
+      <c r="P4" s="62">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q4" s="62">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R4" s="62">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1" s="51">
+      <c r="A5" s="57" t="inlineStr">
+        <is>
+          <t>Date of Creation</t>
+        </is>
+      </c>
+      <c r="B5" s="63" t="n">
+        <v>46272</v>
+      </c>
+      <c r="D5" s="54" t="n"/>
+      <c r="N5" s="60" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="O5" s="64">
+        <f>COUNTIF(K:K,"PENDING")</f>
+        <v/>
+      </c>
+      <c r="P5" s="64">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q5" s="64">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R5" s="64">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1" s="51">
+      <c r="A6" s="57" t="inlineStr">
+        <is>
+          <t>Date of Review</t>
+        </is>
+      </c>
+      <c r="B6" s="63" t="n">
+        <v>46272</v>
+      </c>
+      <c r="D6" s="54" t="n"/>
+      <c r="H6" s="55" t="n"/>
+    </row>
+    <row r="7" ht="20.25" customHeight="1" s="51">
+      <c r="D7" s="54" t="n"/>
+      <c r="H7" s="55" t="n"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1" s="51">
+      <c r="A8" s="65" t="inlineStr">
+        <is>
+          <t>TEST CASE ID</t>
+        </is>
+      </c>
+      <c r="B8" s="65" t="inlineStr">
+        <is>
+          <t>TEST SCENARIO</t>
+        </is>
+      </c>
+      <c r="C8" s="65" t="inlineStr">
+        <is>
+          <t>TEST CASE</t>
+        </is>
+      </c>
+      <c r="D8" s="65" t="inlineStr">
+        <is>
+          <t>TEST CATEGORY</t>
+        </is>
+      </c>
+      <c r="E8" s="65" t="inlineStr">
+        <is>
+          <t>PRE-CONDITION</t>
+        </is>
+      </c>
+      <c r="F8" s="65" t="inlineStr">
+        <is>
+          <t>TEST STEPS</t>
+        </is>
+      </c>
+      <c r="G8" s="65" t="inlineStr">
+        <is>
+          <t>TEST DATA</t>
+        </is>
+      </c>
+      <c r="H8" s="65" t="inlineStr">
+        <is>
+          <t>EXPECTED RESULTS</t>
+        </is>
+      </c>
+      <c r="I8" s="65" t="inlineStr">
+        <is>
+          <t>POST CONDITION</t>
+        </is>
+      </c>
+      <c r="J8" s="65" t="inlineStr">
+        <is>
+          <t>ACTUAL RESULT</t>
+        </is>
+      </c>
+      <c r="K8" s="65" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="L8" s="65" t="inlineStr">
+        <is>
+          <t>PRIORITY</t>
+        </is>
+      </c>
+      <c r="M8" s="65" t="inlineStr">
+        <is>
+          <t>TESTER</t>
+        </is>
+      </c>
+      <c r="N8" s="65" t="inlineStr">
+        <is>
+          <t>TEST DATE</t>
+        </is>
+      </c>
+      <c r="O8" s="65" t="inlineStr">
+        <is>
+          <t>DEVICE</t>
+        </is>
+      </c>
+      <c r="P8" s="65" t="inlineStr">
+        <is>
+          <t>BROWSER</t>
+        </is>
+      </c>
+      <c r="Q8" s="65" t="inlineStr">
+        <is>
+          <t>ISSUE LINK</t>
+        </is>
+      </c>
+      <c r="R8" s="65" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="S8" s="66" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" s="51">
+      <c r="A9" s="67" t="inlineStr">
+        <is>
+          <t>TC_001</t>
+        </is>
+      </c>
+      <c r="B9" s="79" t="inlineStr">
+        <is>
+          <t>Wallet</t>
+        </is>
+      </c>
+      <c r="C9" s="72" t="inlineStr">
+        <is>
+          <t>The profile drawer opens the account's wallets</t>
+        </is>
+      </c>
+      <c r="D9" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E9" s="71" t="inlineStr">
+        <is>
+          <t>User is signed in</t>
+        </is>
+      </c>
+      <c r="F9" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Wallet page
+-Then the page should list the wallets the account holds</t>
+        </is>
+      </c>
+      <c r="G9" s="72" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H9" s="73" t="inlineStr">
+        <is>
+          <t>The wallet page should open from the profile drawer, listing every wallet the account holds</t>
+        </is>
+      </c>
+      <c r="I9" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Wallet page</t>
+        </is>
+      </c>
+      <c r="J9" s="73" t="inlineStr">
+        <is>
+          <t>The drawer opened /v2/wallet, listing 10 wallets: HKD, IDR, VND, PHP, MYR, BDT, USD, THB, MXN, BRL</t>
+        </is>
+      </c>
+      <c r="K9" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L9" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M9" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N9" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O9" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P9" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q9" s="70" t="n"/>
+      <c r="R9" s="70" t="n"/>
+      <c r="S9" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15.75" customHeight="1" s="51">
+      <c r="A10" s="67" t="inlineStr">
+        <is>
+          <t>TC_002</t>
+        </is>
+      </c>
+      <c r="B10" s="79" t="inlineStr">
+        <is>
+          <t>Wallet List</t>
+        </is>
+      </c>
+      <c r="C10" s="72" t="inlineStr">
+        <is>
+          <t>Every wallet names its currency, country, balance and what is blocked</t>
+        </is>
+      </c>
+      <c r="D10" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E10" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Wallet page</t>
+        </is>
+      </c>
+      <c r="F10" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Wallet page
+-Then every wallet should name its currency, country, balance and what is blocked</t>
+        </is>
+      </c>
+      <c r="G10" s="72" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H10" s="73" t="inlineStr">
+        <is>
+          <t>Every wallet should name its currency, its country, its balance and its blocked amount</t>
+        </is>
+      </c>
+      <c r="I10" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Wallet page</t>
+        </is>
+      </c>
+      <c r="J10" s="73" t="inlineStr">
+        <is>
+          <t>All 10 wallets named their currency, country, balance and blocked amount</t>
+        </is>
+      </c>
+      <c r="K10" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L10" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M10" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N10" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O10" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P10" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q10" s="70" t="n"/>
+      <c r="R10" s="70" t="n"/>
+      <c r="S10" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15.75" customHeight="1" s="51">
+      <c r="A11" s="67" t="inlineStr">
+        <is>
+          <t>TC_003</t>
+        </is>
+      </c>
+      <c r="B11" s="79" t="inlineStr">
+        <is>
+          <t>Wallet List</t>
+        </is>
+      </c>
+      <c r="C11" s="72" t="inlineStr">
+        <is>
+          <t>Exactly one wallet is the main wallet</t>
+        </is>
+      </c>
+      <c r="D11" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E11" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Wallet page</t>
+        </is>
+      </c>
+      <c r="F11" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Wallet page
+-Then exactly one wallet should be the main wallet</t>
+        </is>
+      </c>
+      <c r="G11" s="72" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H11" s="73" t="inlineStr">
+        <is>
+          <t>One wallet should be marked as the main wallet, and every other should offer to become it</t>
+        </is>
+      </c>
+      <c r="I11" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Wallet page</t>
+        </is>
+      </c>
+      <c r="J11" s="73" t="inlineStr">
+        <is>
+          <t>The main wallet was HKD, and the other 9 each offered to become it</t>
+        </is>
+      </c>
+      <c r="K11" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L11" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M11" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N11" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O11" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P11" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q11" s="70" t="n"/>
+      <c r="R11" s="70" t="n"/>
+      <c r="S11" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="51">
+      <c r="A12" s="67" t="inlineStr">
+        <is>
+          <t>TC_004</t>
+        </is>
+      </c>
+      <c r="B12" s="79" t="inlineStr">
+        <is>
+          <t>Wallet List</t>
+        </is>
+      </c>
+      <c r="C12" s="72" t="inlineStr">
+        <is>
+          <t>Each wallet states its balance and what is blocked in its own currency</t>
+        </is>
+      </c>
+      <c r="D12" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E12" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Wallet page</t>
+        </is>
+      </c>
+      <c r="F12" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Wallet page
+-Then each wallet's figures should be written in its own currency</t>
+        </is>
+      </c>
+      <c r="G12" s="72" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H12" s="73" t="inlineStr">
+        <is>
+          <t>A wallet's balance and its blocked amount should be written in the same currency symbol</t>
+        </is>
+      </c>
+      <c r="I12" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Wallet page</t>
+        </is>
+      </c>
+      <c r="J12" s="73" t="inlineStr">
+        <is>
+          <t>Every wallet used one symbol throughout: HKD=HK$, IDR=Rp, MYR=RM, USD=US$, BRL=R$, MXN=MXN$ and so on</t>
+        </is>
+      </c>
+      <c r="K12" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L12" s="74" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M12" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N12" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O12" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P12" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q12" s="70" t="n"/>
+      <c r="R12" s="70" t="n"/>
+      <c r="S12" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15.75" customHeight="1" s="51">
+      <c r="A13" s="67" t="inlineStr">
+        <is>
+          <t>TC_005</t>
+        </is>
+      </c>
+      <c r="B13" s="79" t="inlineStr">
+        <is>
+          <t>Wallet Chart</t>
+        </is>
+      </c>
+      <c r="C13" s="72" t="inlineStr">
+        <is>
+          <t>The chart only names countries the account holds a wallet for</t>
+        </is>
+      </c>
+      <c r="D13" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E13" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Wallet page</t>
+        </is>
+      </c>
+      <c r="F13" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Wallet page
+-Then every country in the chart should be one the account holds a wallet for</t>
+        </is>
+      </c>
+      <c r="G13" s="72" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H13" s="73" t="inlineStr">
+        <is>
+          <t>Every country in the assets chart should be one the account holds a wallet for</t>
+        </is>
+      </c>
+      <c r="I13" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Wallet page</t>
+        </is>
+      </c>
+      <c r="J13" s="73" t="inlineStr">
+        <is>
+          <t>The chart named Indonesia, Vietnam, Philippines, Malaysia and Bangladesh, all of them wallets the account holds</t>
+        </is>
+      </c>
+      <c r="K13" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L13" s="74" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M13" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N13" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O13" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P13" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q13" s="70" t="n"/>
+      <c r="R13" s="70" t="n"/>
+      <c r="S13" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1" s="51">
+      <c r="A14" s="67" t="inlineStr">
+        <is>
+          <t>TC_006</t>
+        </is>
+      </c>
+      <c r="B14" s="79" t="inlineStr">
+        <is>
+          <t>Wallet Detail</t>
+        </is>
+      </c>
+      <c r="C14" s="72" t="inlineStr">
+        <is>
+          <t>A wallet opens its own page</t>
+        </is>
+      </c>
+      <c r="D14" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E14" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Wallet page</t>
+        </is>
+      </c>
+      <c r="F14" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Wallet page
+-And I open the wallet named in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-Then that wallet's own page should open
+-And the wallet should state its total, what is available and what is locked</t>
+        </is>
+      </c>
+      <c r="G14" s="72" t="inlineStr">
+        <is>
+          <t>Wallet: HKD</t>
+        </is>
+      </c>
+      <c r="H14" s="73" t="inlineStr">
+        <is>
+          <t>Opening a wallet should go to that wallet's own page, stating its total, available and locked balances</t>
+        </is>
+      </c>
+      <c r="I14" s="73" t="inlineStr">
+        <is>
+          <t>User is on the wallet's own page</t>
+        </is>
+      </c>
+      <c r="J14" s="73" t="inlineStr">
+        <is>
+          <t>The HKD wallet opened at /v2/wallet/detail/record?currencyCode=HKD, stating all three balances</t>
+        </is>
+      </c>
+      <c r="K14" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L14" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M14" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N14" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O14" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P14" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q14" s="70" t="n"/>
+      <c r="R14" s="70" t="n"/>
+      <c r="S14" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1" s="51">
+      <c r="A15" s="67" t="inlineStr">
+        <is>
+          <t>TC_007</t>
+        </is>
+      </c>
+      <c r="B15" s="79" t="inlineStr">
+        <is>
+          <t>Wallet Detail</t>
+        </is>
+      </c>
+      <c r="C15" s="72" t="inlineStr">
+        <is>
+          <t>A wallet's total is what is available plus what is locked</t>
+        </is>
+      </c>
+      <c r="D15" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E15" s="71" t="inlineStr">
+        <is>
+          <t>User is on a wallet's own page</t>
+        </is>
+      </c>
+      <c r="F15" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Wallet page
+-And I open the wallet named in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-Then the wallet's total should be what is available plus what is locked</t>
+        </is>
+      </c>
+      <c r="G15" s="72" t="inlineStr">
+        <is>
+          <t>Wallet: HKD</t>
+        </is>
+      </c>
+      <c r="H15" s="73" t="inlineStr">
+        <is>
+          <t>The total balance should equal the available balance plus the amount locked</t>
+        </is>
+      </c>
+      <c r="I15" s="73" t="inlineStr">
+        <is>
+          <t>User is on the wallet's own page</t>
+        </is>
+      </c>
+      <c r="J15" s="73" t="inlineStr">
+        <is>
+          <t>8369.51 available plus 5544.32 locked came to the stated total of 13913.83</t>
+        </is>
+      </c>
+      <c r="K15" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L15" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M15" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N15" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O15" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P15" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q15" s="70" t="n"/>
+      <c r="R15" s="70" t="n"/>
+      <c r="S15" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="51">
+      <c r="A16" s="67" t="inlineStr">
+        <is>
+          <t>TC_008</t>
+        </is>
+      </c>
+      <c r="B16" s="79" t="inlineStr">
+        <is>
+          <t>Wallet Detail</t>
+        </is>
+      </c>
+      <c r="C16" s="72" t="inlineStr">
+        <is>
+          <t>A wallet keeps what has moved and what is held in two tabs</t>
+        </is>
+      </c>
+      <c r="D16" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E16" s="71" t="inlineStr">
+        <is>
+          <t>User is on a wallet's own page</t>
+        </is>
+      </c>
+      <c r="F16" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Wallet page
+-And I open the wallet named in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-Then the wallet should offer the tabs "Record, Locked"</t>
+        </is>
+      </c>
+      <c r="G16" s="72" t="inlineStr">
+        <is>
+          <t>Wallet: HKD</t>
+        </is>
+      </c>
+      <c r="H16" s="73" t="inlineStr">
+        <is>
+          <t>The wallet should offer a Record tab and a Locked tab</t>
+        </is>
+      </c>
+      <c r="I16" s="73" t="inlineStr">
+        <is>
+          <t>User is on the wallet's own page</t>
+        </is>
+      </c>
+      <c r="J16" s="73" t="inlineStr">
+        <is>
+          <t>The wallet offered both the Record and Locked tabs</t>
+        </is>
+      </c>
+      <c r="K16" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L16" s="74" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M16" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N16" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O16" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P16" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q16" s="70" t="n"/>
+      <c r="R16" s="70" t="n"/>
+      <c r="S16" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1" s="51">
+      <c r="A17" s="67" t="inlineStr">
+        <is>
+          <t>TC_009</t>
+        </is>
+      </c>
+      <c r="B17" s="79" t="inlineStr">
+        <is>
+          <t>Wallet Detail</t>
+        </is>
+      </c>
+      <c r="C17" s="72" t="inlineStr">
+        <is>
+          <t>The Record tab lists what has moved in that wallet</t>
+        </is>
+      </c>
+      <c r="D17" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E17" s="71" t="inlineStr">
+        <is>
+          <t>User is on a wallet's own page</t>
+        </is>
+      </c>
+      <c r="F17" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Wallet page
+-And I open the wallet named in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-And I move to the wallet's "Record" tab
+-Then every movement should name what it was, when it happened and how much</t>
+        </is>
+      </c>
+      <c r="G17" s="72" t="inlineStr">
+        <is>
+          <t>Wallet: HKD</t>
+        </is>
+      </c>
+      <c r="H17" s="73" t="inlineStr">
+        <is>
+          <t>Every movement should name what it was, when it happened and how much</t>
+        </is>
+      </c>
+      <c r="I17" s="73" t="inlineStr">
+        <is>
+          <t>User is on the wallet's own page</t>
+        </is>
+      </c>
+      <c r="J17" s="73" t="inlineStr">
+        <is>
+          <t>The Record tab listed 20 movements, the newest being Convert 2026-09-07 15:44:33 HK$-1</t>
+        </is>
+      </c>
+      <c r="K17" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L17" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M17" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N17" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O17" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P17" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q17" s="70" t="n"/>
+      <c r="R17" s="70" t="n"/>
+      <c r="S17" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15.75" customHeight="1" s="51">
+      <c r="A18" s="67" t="inlineStr">
+        <is>
+          <t>TC_010</t>
+        </is>
+      </c>
+      <c r="B18" s="79" t="inlineStr">
+        <is>
+          <t>Wallet Detail</t>
+        </is>
+      </c>
+      <c r="C18" s="72" t="inlineStr">
+        <is>
+          <t>The Locked tab lists what is being held against that wallet</t>
+        </is>
+      </c>
+      <c r="D18" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E18" s="71" t="inlineStr">
+        <is>
+          <t>User is on a wallet's own page</t>
+        </is>
+      </c>
+      <c r="F18" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Wallet page
+-And I open the wallet named in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-And I move to the wallet's "Locked" tab
+-Then every movement should name what it was, when it happened and how much</t>
+        </is>
+      </c>
+      <c r="G18" s="72" t="inlineStr">
+        <is>
+          <t>Wallet: HKD</t>
+        </is>
+      </c>
+      <c r="H18" s="73" t="inlineStr">
+        <is>
+          <t>Every held amount should name what it was, when it happened and how much</t>
+        </is>
+      </c>
+      <c r="I18" s="73" t="inlineStr">
+        <is>
+          <t>User is on the wallet's own page</t>
+        </is>
+      </c>
+      <c r="J18" s="73" t="inlineStr">
+        <is>
+          <t>The Locked tab listed 20 held amounts, the newest being Withdraw 2026-09-07 12:28:22 HK$-107</t>
+        </is>
+      </c>
+      <c r="K18" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L18" s="74" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M18" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N18" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O18" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P18" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q18" s="70" t="n"/>
+      <c r="R18" s="70" t="n"/>
+      <c r="S18" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="51">
+      <c r="A19" s="67" t="inlineStr">
+        <is>
+          <t>TC_011</t>
+        </is>
+      </c>
+      <c r="B19" s="79" t="inlineStr">
+        <is>
+          <t>Wallet Detail</t>
+        </is>
+      </c>
+      <c r="C19" s="72" t="inlineStr">
+        <is>
+          <t>A wallet's own page offers to make it the main wallet</t>
+        </is>
+      </c>
+      <c r="D19" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E19" s="71" t="inlineStr">
+        <is>
+          <t>User is on a wallet's own page</t>
+        </is>
+      </c>
+      <c r="F19" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Wallet page
+-And I open the wallet named in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-Then the wallet should offer to become the main wallet</t>
+        </is>
+      </c>
+      <c r="G19" s="72" t="inlineStr">
+        <is>
+          <t>Wallet: HKD</t>
+        </is>
+      </c>
+      <c r="H19" s="73" t="inlineStr">
+        <is>
+          <t>The wallet should offer a Set as main button</t>
+        </is>
+      </c>
+      <c r="I19" s="73" t="inlineStr">
+        <is>
+          <t>User is on the wallet's own page</t>
+        </is>
+      </c>
+      <c r="J19" s="73" t="inlineStr">
+        <is>
+          <t>The wallet offered to become the main wallet</t>
+        </is>
+      </c>
+      <c r="K19" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L19" s="74" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M19" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N19" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O19" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P19" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q19" s="70" t="n"/>
+      <c r="R19" s="70" t="n"/>
+      <c r="S19" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" s="51">
+      <c r="A20" s="67" t="inlineStr">
+        <is>
+          <t>TC_012</t>
+        </is>
+      </c>
+      <c r="B20" s="79" t="inlineStr">
+        <is>
+          <t>Wallet Detail</t>
+        </is>
+      </c>
+      <c r="C20" s="72" t="inlineStr">
+        <is>
+          <t>Going back from a wallet returns to the list</t>
+        </is>
+      </c>
+      <c r="D20" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E20" s="71" t="inlineStr">
+        <is>
+          <t>User is on a wallet's own page</t>
+        </is>
+      </c>
+      <c r="F20" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Wallet page
+-And I open the wallet named in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-Then that wallet's own page should open
+-When I go back to the wallets
+-Then the wallets should be listed again</t>
+        </is>
+      </c>
+      <c r="G20" s="72" t="inlineStr">
+        <is>
+          <t>Wallet: HKD</t>
+        </is>
+      </c>
+      <c r="H20" s="73" t="inlineStr">
+        <is>
+          <t>Going back should return to the list of wallets</t>
+        </is>
+      </c>
+      <c r="I20" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Wallet page</t>
+        </is>
+      </c>
+      <c r="J20" s="73" t="inlineStr">
+        <is>
+          <t>Going back returned to the wallet list, all 10 still listed</t>
+        </is>
+      </c>
+      <c r="K20" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L20" s="74" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M20" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N20" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O20" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P20" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q20" s="70" t="n"/>
+      <c r="R20" s="70" t="n"/>
+      <c r="S20" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" s="51">
+      <c r="A21" s="67" t="inlineStr">
+        <is>
+          <t>TC_013</t>
+        </is>
+      </c>
+      <c r="B21" s="79" t="inlineStr">
+        <is>
+          <t>Wallet Main</t>
+        </is>
+      </c>
+      <c r="C21" s="72" t="inlineStr">
+        <is>
+          <t>The main wallet can be moved to another wallet and put back</t>
+        </is>
+      </c>
+      <c r="D21" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E21" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Wallet page</t>
+        </is>
+      </c>
+      <c r="F21" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Wallet page
+-And I make the wallet named in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;" the main one
+-Then that wallet should become the main one
+-When I put the main wallet back
+-Then the wallet that was main should be main again</t>
+        </is>
+      </c>
+      <c r="G21" s="72" t="inlineStr">
+        <is>
+          <t>Move the main wallet to IDR</t>
+        </is>
+      </c>
+      <c r="H21" s="73" t="inlineStr">
+        <is>
+          <t>The chosen wallet should become the main one, and setting the first one back should restore it</t>
+        </is>
+      </c>
+      <c r="I21" s="73" t="inlineStr">
+        <is>
+          <t>The main wallet is as it was found</t>
+        </is>
+      </c>
+      <c r="J21" s="73" t="inlineStr">
+        <is>
+          <t>The main wallet moved from HKD to IDR and was put back to HKD, with nothing asked first</t>
+        </is>
+      </c>
+      <c r="K21" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L21" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M21" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N21" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O21" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P21" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q21" s="70" t="n"/>
+      <c r="R21" s="70" t="n"/>
+      <c r="S21" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="7">
+    <dataValidation sqref="K9:K21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"PASS,FAIL,PENDING"</formula1>
+    </dataValidation>
+    <dataValidation sqref="P9:P21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>METADATA!$H$2:$H$8</formula1>
+    </dataValidation>
+    <dataValidation sqref="O9:O21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>METADATA!$J$2:$J$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="D9:D21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>METADATA!$N$2:$N$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="B4 M9:M21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>METADATA!$F$2:$F$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="L9:L21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"HIGH,MEDIUM,LOW"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"WPAY,UMPay,OFL,UNCS"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S14" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S16" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S19" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S20" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S21" r:id="rId13"/>
+  </hyperlinks>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.9840277777777779" bottom="0.9840277777777779" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="0" useFirstPageNumber="0" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:T21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
+    <col width="10" customWidth="1" style="51" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1" s="51">
+      <c r="A1" s="52" t="inlineStr">
+        <is>
+          <t>Project Name</t>
+        </is>
+      </c>
+      <c r="B1" s="53" t="inlineStr">
+        <is>
+          <t>UMPay</t>
+        </is>
+      </c>
+      <c r="D1" s="54" t="n"/>
+      <c r="H1" s="55" t="n"/>
+      <c r="K1" s="56" t="n"/>
+      <c r="L1" s="54" t="n"/>
+      <c r="M1" s="54" t="n"/>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" s="51">
+      <c r="A2" s="57" t="inlineStr">
+        <is>
+          <t>Module/Feature Name</t>
+        </is>
+      </c>
+      <c r="B2" s="58" t="inlineStr">
+        <is>
+          <t>Payment</t>
+        </is>
+      </c>
+      <c r="D2" s="54" t="n"/>
+      <c r="K2" s="56" t="n"/>
+      <c r="L2" s="54" t="n"/>
+      <c r="M2" s="54" t="n"/>
+      <c r="N2" s="54" t="n"/>
+      <c r="P2" s="59" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="Q2" s="59" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="R2" s="59" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1" s="51">
+      <c r="A3" s="57" t="inlineStr">
+        <is>
+          <t>Reference Document</t>
+        </is>
+      </c>
+      <c r="B3" s="58" t="n"/>
+      <c r="D3" s="54" t="n"/>
+      <c r="N3" s="60" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="O3" s="61">
+        <f>COUNTIF(K:K,"PASS")</f>
+        <v/>
+      </c>
+      <c r="P3" s="61">
+        <f>COUNTIFS(K:K,"PASS",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="61">
+        <f>COUNTIFS(K:K,"PASS",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R3" s="61">
+        <f>COUNTIFS(K:K,"PASS",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1" s="51">
+      <c r="A4" s="57" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B4" s="53" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="D4" s="54" t="n"/>
+      <c r="N4" s="60" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="O4" s="62">
+        <f>COUNTIF(K:K,"FAIL")</f>
+        <v/>
+      </c>
+      <c r="P4" s="62">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q4" s="62">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R4" s="62">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1" s="51">
+      <c r="A5" s="57" t="inlineStr">
+        <is>
+          <t>Date of Creation</t>
+        </is>
+      </c>
+      <c r="B5" s="63" t="n">
+        <v>46272</v>
+      </c>
+      <c r="D5" s="54" t="n"/>
+      <c r="N5" s="60" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="O5" s="64">
+        <f>COUNTIF(K:K,"PENDING")</f>
+        <v/>
+      </c>
+      <c r="P5" s="64">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q5" s="64">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R5" s="64">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1" s="51">
+      <c r="A6" s="57" t="inlineStr">
+        <is>
+          <t>Date of Review</t>
+        </is>
+      </c>
+      <c r="B6" s="63" t="n">
+        <v>46272</v>
+      </c>
+      <c r="D6" s="54" t="n"/>
+      <c r="H6" s="55" t="n"/>
+    </row>
+    <row r="7" ht="20.25" customHeight="1" s="51">
+      <c r="D7" s="54" t="n"/>
+      <c r="H7" s="55" t="n"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1" s="51">
+      <c r="A8" s="65" t="inlineStr">
+        <is>
+          <t>TEST CASE ID</t>
+        </is>
+      </c>
+      <c r="B8" s="65" t="inlineStr">
+        <is>
+          <t>TEST SCENARIO</t>
+        </is>
+      </c>
+      <c r="C8" s="65" t="inlineStr">
+        <is>
+          <t>TEST CASE</t>
+        </is>
+      </c>
+      <c r="D8" s="65" t="inlineStr">
+        <is>
+          <t>TEST CATEGORY</t>
+        </is>
+      </c>
+      <c r="E8" s="65" t="inlineStr">
+        <is>
+          <t>PRE-CONDITION</t>
+        </is>
+      </c>
+      <c r="F8" s="65" t="inlineStr">
+        <is>
+          <t>TEST STEPS</t>
+        </is>
+      </c>
+      <c r="G8" s="65" t="inlineStr">
+        <is>
+          <t>TEST DATA</t>
+        </is>
+      </c>
+      <c r="H8" s="65" t="inlineStr">
+        <is>
+          <t>EXPECTED RESULTS</t>
+        </is>
+      </c>
+      <c r="I8" s="65" t="inlineStr">
+        <is>
+          <t>POST CONDITION</t>
+        </is>
+      </c>
+      <c r="J8" s="65" t="inlineStr">
+        <is>
+          <t>ACTUAL RESULT</t>
+        </is>
+      </c>
+      <c r="K8" s="65" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="L8" s="65" t="inlineStr">
+        <is>
+          <t>PRIORITY</t>
+        </is>
+      </c>
+      <c r="M8" s="65" t="inlineStr">
+        <is>
+          <t>TESTER</t>
+        </is>
+      </c>
+      <c r="N8" s="65" t="inlineStr">
+        <is>
+          <t>TEST DATE</t>
+        </is>
+      </c>
+      <c r="O8" s="65" t="inlineStr">
+        <is>
+          <t>DEVICE</t>
+        </is>
+      </c>
+      <c r="P8" s="65" t="inlineStr">
+        <is>
+          <t>BROWSER</t>
+        </is>
+      </c>
+      <c r="Q8" s="65" t="inlineStr">
+        <is>
+          <t>ISSUE LINK</t>
+        </is>
+      </c>
+      <c r="R8" s="65" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="S8" s="66" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" s="51">
+      <c r="A9" s="67" t="inlineStr">
+        <is>
+          <t>TC_001</t>
+        </is>
+      </c>
+      <c r="B9" s="79" t="inlineStr">
+        <is>
+          <t>Payment</t>
+        </is>
+      </c>
+      <c r="C9" s="72" t="inlineStr">
+        <is>
+          <t>The profile drawer opens the account's payment accounts</t>
+        </is>
+      </c>
+      <c r="D9" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E9" s="71" t="inlineStr">
+        <is>
+          <t>User is signed in</t>
+        </is>
+      </c>
+      <c r="F9" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Payment page
+-Then the page should list the payment accounts the account can be paid out to</t>
+        </is>
+      </c>
+      <c r="G9" s="72" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H9" s="73" t="inlineStr">
+        <is>
+          <t>The payment page should open from the profile drawer, listing the accounts the user can be paid out to</t>
+        </is>
+      </c>
+      <c r="I9" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Payment page</t>
+        </is>
+      </c>
+      <c r="J9" s="73" t="inlineStr">
+        <is>
+          <t>The drawer opened /settings-payment, listing 6 providers: AFIRME, Bangkok Bank Plc., DANA, HSBC, FPS, USDT-TRC 20</t>
+        </is>
+      </c>
+      <c r="K9" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L9" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M9" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N9" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O9" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P9" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q9" s="70" t="n"/>
+      <c r="R9" s="70" t="n"/>
+      <c r="S9" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15.75" customHeight="1" s="51">
+      <c r="A10" s="67" t="inlineStr">
+        <is>
+          <t>TC_002</t>
+        </is>
+      </c>
+      <c r="B10" s="79" t="inlineStr">
+        <is>
+          <t>Payment List</t>
+        </is>
+      </c>
+      <c r="C10" s="72" t="inlineStr">
+        <is>
+          <t>Every saved account names its provider and what identifies it</t>
+        </is>
+      </c>
+      <c r="D10" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E10" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Payment page</t>
+        </is>
+      </c>
+      <c r="F10" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Payment page
+-Then every saved account should name its provider and what identifies it</t>
+        </is>
+      </c>
+      <c r="G10" s="72" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H10" s="73" t="inlineStr">
+        <is>
+          <t>Every saved account should name its provider and carry the details that identify it, with none of them blank</t>
+        </is>
+      </c>
+      <c r="I10" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Payment page</t>
+        </is>
+      </c>
+      <c r="J10" s="73" t="inlineStr">
+        <is>
+          <t>Every saved account named its provider and carried its details, none of them blank</t>
+        </is>
+      </c>
+      <c r="K10" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L10" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M10" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N10" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O10" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P10" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q10" s="70" t="n"/>
+      <c r="R10" s="70" t="n"/>
+      <c r="S10" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15.75" customHeight="1" s="51">
+      <c r="A11" s="67" t="inlineStr">
+        <is>
+          <t>TC_003</t>
+        </is>
+      </c>
+      <c r="B11" s="79" t="inlineStr">
+        <is>
+          <t>Payment List</t>
+        </is>
+      </c>
+      <c r="C11" s="72" t="inlineStr">
+        <is>
+          <t>Every saved account offers to be changed and removed</t>
+        </is>
+      </c>
+      <c r="D11" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E11" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Payment page</t>
+        </is>
+      </c>
+      <c r="F11" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Payment page
+-Then every saved account should offer to be changed and removed</t>
+        </is>
+      </c>
+      <c r="G11" s="72" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H11" s="73" t="inlineStr">
+        <is>
+          <t>Each saved account should offer a way to change it and a way to remove it</t>
+        </is>
+      </c>
+      <c r="I11" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Payment page</t>
+        </is>
+      </c>
+      <c r="J11" s="73" t="inlineStr">
+        <is>
+          <t>12 payment accounts across 6 providers, each offering to be changed and removed</t>
+        </is>
+      </c>
+      <c r="K11" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L11" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M11" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N11" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O11" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P11" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q11" s="70" t="n"/>
+      <c r="R11" s="70" t="n"/>
+      <c r="S11" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="51">
+      <c r="A12" s="67" t="inlineStr">
+        <is>
+          <t>TC_004</t>
+        </is>
+      </c>
+      <c r="B12" s="79" t="inlineStr">
+        <is>
+          <t>Payment List</t>
+        </is>
+      </c>
+      <c r="C12" s="72" t="inlineStr">
+        <is>
+          <t>A saved account can be opened to be changed</t>
+        </is>
+      </c>
+      <c r="D12" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E12" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Payment page</t>
+        </is>
+      </c>
+      <c r="F12" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Payment page
+-And I open the first saved account to change it
+-Then somewhere to change it should open</t>
+        </is>
+      </c>
+      <c r="G12" s="72" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H12" s="73" t="inlineStr">
+        <is>
+          <t>Choosing to change a saved account should open somewhere it can be changed</t>
+        </is>
+      </c>
+      <c r="I12" s="73" t="inlineStr">
+        <is>
+          <t>User is on the edit form</t>
+        </is>
+      </c>
+      <c r="J12" s="73" t="inlineStr">
+        <is>
+          <t>Changing an account opened /settings-payment/create?mode=form&amp;id=3024</t>
+        </is>
+      </c>
+      <c r="K12" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L12" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M12" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N12" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O12" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P12" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q12" s="70" t="n"/>
+      <c r="R12" s="70" t="n"/>
+      <c r="S12" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15.75" customHeight="1" s="51">
+      <c r="A13" s="67" t="inlineStr">
+        <is>
+          <t>TC_005</t>
+        </is>
+      </c>
+      <c r="B13" s="79" t="inlineStr">
+        <is>
+          <t>Payment Add</t>
+        </is>
+      </c>
+      <c r="C13" s="72" t="inlineStr">
+        <is>
+          <t>The page offers to add a payment account</t>
+        </is>
+      </c>
+      <c r="D13" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E13" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Payment page</t>
+        </is>
+      </c>
+      <c r="F13" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Payment page
+-And I start adding a payment account
+-Then the form for a new payment account should open</t>
+        </is>
+      </c>
+      <c r="G13" s="72" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H13" s="73" t="inlineStr">
+        <is>
+          <t>Add Payment should open the form for a new payment account</t>
+        </is>
+      </c>
+      <c r="I13" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Add Payment form</t>
+        </is>
+      </c>
+      <c r="J13" s="73" t="inlineStr">
+        <is>
+          <t>Add Payment opened /settings-payment/create</t>
+        </is>
+      </c>
+      <c r="K13" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L13" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M13" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N13" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O13" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P13" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q13" s="70" t="n"/>
+      <c r="R13" s="70" t="n"/>
+      <c r="S13" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1" s="51">
+      <c r="A14" s="67" t="inlineStr">
+        <is>
+          <t>TC_006</t>
+        </is>
+      </c>
+      <c r="B14" s="79" t="inlineStr">
+        <is>
+          <t>Payment Add</t>
+        </is>
+      </c>
+      <c r="C14" s="72" t="inlineStr">
+        <is>
+          <t>The form asks for a currency and offers every way of being paid</t>
+        </is>
+      </c>
+      <c r="D14" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E14" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Add Payment form</t>
+        </is>
+      </c>
+      <c r="F14" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Payment page
+-And I start adding a payment account
+-Then the form should ask for a currency and offer "E-Wallet, Bank, USDT"</t>
+        </is>
+      </c>
+      <c r="G14" s="72" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H14" s="73" t="inlineStr">
+        <is>
+          <t>The form should state the currency and offer E-Wallet, Bank and USDT</t>
+        </is>
+      </c>
+      <c r="I14" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Add Payment form</t>
+        </is>
+      </c>
+      <c r="J14" s="73" t="inlineStr">
+        <is>
+          <t>The form was set to Hong Kong and offered E-Wallet, Bank and USDT</t>
+        </is>
+      </c>
+      <c r="K14" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L14" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M14" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N14" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O14" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P14" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q14" s="70" t="n"/>
+      <c r="R14" s="70" t="n"/>
+      <c r="S14" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1" s="51">
+      <c r="A15" s="67" t="inlineStr">
+        <is>
+          <t>TC_007</t>
+        </is>
+      </c>
+      <c r="B15" s="79" t="inlineStr">
+        <is>
+          <t>Payment Add</t>
+        </is>
+      </c>
+      <c r="C15" s="72" t="inlineStr">
+        <is>
+          <t>Choosing to be paid by bank offers banks with their fees and how long they take</t>
+        </is>
+      </c>
+      <c r="D15" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E15" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Add Payment form</t>
+        </is>
+      </c>
+      <c r="F15" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Payment page
+-And I start adding a payment account
+-And I choose the way of being paid named in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-Then the providers offered should each name how long they take and what they charge</t>
+        </is>
+      </c>
+      <c r="G15" s="72" t="inlineStr">
+        <is>
+          <t>Way: Bank</t>
+        </is>
+      </c>
+      <c r="H15" s="73" t="inlineStr">
+        <is>
+          <t>Every bank offered should name how long it takes and what it charges</t>
+        </is>
+      </c>
+      <c r="I15" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Add Payment form</t>
+        </is>
+      </c>
+      <c r="J15" s="73" t="inlineStr">
+        <is>
+          <t>Offered 4 banks - Bank of China 6.20%, HSBC 6.00%, Hang Seng Bank 6.00%, Standard Chartered Bank 6.00% - each Duration:2mn</t>
+        </is>
+      </c>
+      <c r="K15" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L15" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M15" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N15" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O15" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P15" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q15" s="70" t="n"/>
+      <c r="R15" s="70" t="n"/>
+      <c r="S15" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="51">
+      <c r="A16" s="67" t="inlineStr">
+        <is>
+          <t>TC_008</t>
+        </is>
+      </c>
+      <c r="B16" s="79" t="inlineStr">
+        <is>
+          <t>Payment Add</t>
+        </is>
+      </c>
+      <c r="C16" s="72" t="inlineStr">
+        <is>
+          <t>Choosing to be paid by e-wallet offers e-wallets with their fees and how long they take</t>
+        </is>
+      </c>
+      <c r="D16" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E16" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Add Payment form</t>
+        </is>
+      </c>
+      <c r="F16" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Payment page
+-And I start adding a payment account
+-And I choose the way of being paid named in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-Then the providers offered should each name how long they take and what they charge</t>
+        </is>
+      </c>
+      <c r="G16" s="72" t="inlineStr">
+        <is>
+          <t>Way: E-Wallet</t>
+        </is>
+      </c>
+      <c r="H16" s="73" t="inlineStr">
+        <is>
+          <t>Every e-wallet offered should name how long it takes and what it charges</t>
+        </is>
+      </c>
+      <c r="I16" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Add Payment form</t>
+        </is>
+      </c>
+      <c r="J16" s="73" t="inlineStr">
+        <is>
+          <t>Offered FPS, Duration:2mn, Fee Charge:7.00%</t>
+        </is>
+      </c>
+      <c r="K16" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L16" s="74" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M16" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N16" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O16" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P16" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q16" s="70" t="n"/>
+      <c r="R16" s="70" t="n"/>
+      <c r="S16" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1" s="51">
+      <c r="A17" s="67" t="inlineStr">
+        <is>
+          <t>TC_009</t>
+        </is>
+      </c>
+      <c r="B17" s="79" t="inlineStr">
+        <is>
+          <t>Payment Add</t>
+        </is>
+      </c>
+      <c r="C17" s="72" t="inlineStr">
+        <is>
+          <t>Choosing to be paid in USDT offers what it can be sent through</t>
+        </is>
+      </c>
+      <c r="D17" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E17" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Add Payment form</t>
+        </is>
+      </c>
+      <c r="F17" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Payment page
+-And I start adding a payment account
+-And I choose the way of being paid named in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-Then the providers offered should each name how long they take and what they charge</t>
+        </is>
+      </c>
+      <c r="G17" s="72" t="inlineStr">
+        <is>
+          <t>Way: USDT</t>
+        </is>
+      </c>
+      <c r="H17" s="73" t="inlineStr">
+        <is>
+          <t>Every USDT network offered should name how long it takes and what it charges</t>
+        </is>
+      </c>
+      <c r="I17" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Add Payment form</t>
+        </is>
+      </c>
+      <c r="J17" s="73" t="inlineStr">
+        <is>
+          <t>Offered USDT-TRC 20, Duration:1mn, Fee Charge:7.00%</t>
+        </is>
+      </c>
+      <c r="K17" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L17" s="74" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M17" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N17" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O17" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P17" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q17" s="70" t="n"/>
+      <c r="R17" s="70" t="n"/>
+      <c r="S17" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15.75" customHeight="1" s="51">
+      <c r="A18" s="67" t="inlineStr">
+        <is>
+          <t>TC_010</t>
+        </is>
+      </c>
+      <c r="B18" s="79" t="inlineStr">
+        <is>
+          <t>Payment Add</t>
+        </is>
+      </c>
+      <c r="C18" s="72" t="inlineStr">
+        <is>
+          <t>The providers can be searched</t>
+        </is>
+      </c>
+      <c r="D18" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E18" s="71" t="inlineStr">
+        <is>
+          <t>A way of being paid has been chosen</t>
+        </is>
+      </c>
+      <c r="F18" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Payment page
+-And I start adding a payment account
+-And I choose the way of being paid named in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-Then the providers should be searchable</t>
+        </is>
+      </c>
+      <c r="G18" s="72" t="inlineStr">
+        <is>
+          <t>Way: Bank</t>
+        </is>
+      </c>
+      <c r="H18" s="73" t="inlineStr">
+        <is>
+          <t>The list of providers should offer a search</t>
+        </is>
+      </c>
+      <c r="I18" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Add Payment form</t>
+        </is>
+      </c>
+      <c r="J18" s="73" t="inlineStr">
+        <is>
+          <t>The providers offered a search</t>
+        </is>
+      </c>
+      <c r="K18" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L18" s="74" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M18" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N18" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O18" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P18" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q18" s="70" t="n"/>
+      <c r="R18" s="70" t="n"/>
+      <c r="S18" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="51">
+      <c r="A19" s="67" t="inlineStr">
+        <is>
+          <t>TC_011</t>
+        </is>
+      </c>
+      <c r="B19" s="79" t="inlineStr">
+        <is>
+          <t>Payment Add</t>
+        </is>
+      </c>
+      <c r="C19" s="72" t="inlineStr">
+        <is>
+          <t>Searching the providers leaves only what was searched for</t>
+        </is>
+      </c>
+      <c r="D19" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E19" s="71" t="inlineStr">
+        <is>
+          <t>A way of being paid has been chosen</t>
+        </is>
+      </c>
+      <c r="F19" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Payment page
+-And I start adding a payment account
+-And I choose the way of being paid named in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-And I search the providers for what is in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-Then only the providers matching it should be left</t>
+        </is>
+      </c>
+      <c r="G19" s="72" t="inlineStr">
+        <is>
+          <t>Search: Bank</t>
+        </is>
+      </c>
+      <c r="H19" s="73" t="inlineStr">
+        <is>
+          <t>Only the providers whose name matches the search should be left</t>
+        </is>
+      </c>
+      <c r="I19" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Add Payment form</t>
+        </is>
+      </c>
+      <c r="J19" s="73" t="inlineStr">
+        <is>
+          <t>Searching for Bank took 4 providers down to 3, all of them matching</t>
+        </is>
+      </c>
+      <c r="K19" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L19" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M19" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N19" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O19" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P19" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q19" s="70" t="n"/>
+      <c r="R19" s="70" t="n"/>
+      <c r="S19" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" s="51">
+      <c r="A20" s="67" t="inlineStr">
+        <is>
+          <t>TC_012</t>
+        </is>
+      </c>
+      <c r="B20" s="79" t="inlineStr">
+        <is>
+          <t>Payment Add</t>
+        </is>
+      </c>
+      <c r="C20" s="72" t="inlineStr">
+        <is>
+          <t>Closing the providers leaves the form as it was</t>
+        </is>
+      </c>
+      <c r="D20" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E20" s="71" t="inlineStr">
+        <is>
+          <t>A way of being paid has been chosen</t>
+        </is>
+      </c>
+      <c r="F20" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Payment page
+-And I start adding a payment account
+-And I choose the way of being paid named in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-And I close what is being asked
+-Then the form should still be there</t>
+        </is>
+      </c>
+      <c r="G20" s="72" t="inlineStr">
+        <is>
+          <t>Way: Bank</t>
+        </is>
+      </c>
+      <c r="H20" s="73" t="inlineStr">
+        <is>
+          <t>Closing the list should leave the form with its currency and its ways of being paid</t>
+        </is>
+      </c>
+      <c r="I20" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Add Payment form</t>
+        </is>
+      </c>
+      <c r="J20" s="73" t="inlineStr">
+        <is>
+          <t>The form was still there, offering E-Wallet, Bank and USDT</t>
+        </is>
+      </c>
+      <c r="K20" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L20" s="74" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M20" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N20" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O20" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P20" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q20" s="70" t="n"/>
+      <c r="R20" s="70" t="n"/>
+      <c r="S20" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" s="51">
+      <c r="A21" s="67" t="inlineStr">
+        <is>
+          <t>TC_013</t>
+        </is>
+      </c>
+      <c r="B21" s="79" t="inlineStr">
+        <is>
+          <t>Payment Add</t>
+        </is>
+      </c>
+      <c r="C21" s="72" t="inlineStr">
+        <is>
+          <t>Going back from adding one returns to the saved accounts</t>
+        </is>
+      </c>
+      <c r="D21" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E21" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Add Payment form</t>
+        </is>
+      </c>
+      <c r="F21" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Payment page
+-And I start adding a payment account
+-Then the form for a new payment account should open
+-When I go back to the payment accounts
+-Then the payment accounts should be listed again</t>
+        </is>
+      </c>
+      <c r="G21" s="72" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H21" s="73" t="inlineStr">
+        <is>
+          <t>Going back should return to the list of saved payment accounts</t>
+        </is>
+      </c>
+      <c r="I21" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Payment page</t>
+        </is>
+      </c>
+      <c r="J21" s="73" t="inlineStr">
+        <is>
+          <t>Going back returned to the payment accounts, all 6 providers still listed</t>
+        </is>
+      </c>
+      <c r="K21" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L21" s="74" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M21" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N21" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O21" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P21" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q21" s="70" t="n"/>
+      <c r="R21" s="70" t="n"/>
+      <c r="S21" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="7">
+    <dataValidation sqref="K9:K21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"PASS,FAIL,PENDING"</formula1>
+    </dataValidation>
+    <dataValidation sqref="P9:P21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>METADATA!$H$2:$H$8</formula1>
+    </dataValidation>
+    <dataValidation sqref="O9:O21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>METADATA!$J$2:$J$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="D9:D21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>METADATA!$N$2:$N$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="B4 M9:M21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>METADATA!$F$2:$F$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="L9:L21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"HIGH,MEDIUM,LOW"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"WPAY,UMPay,OFL,UNCS"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S14" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S16" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S19" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S20" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S21" r:id="rId13"/>
+  </hyperlinks>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.9840277777777779" bottom="0.9840277777777779" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="0" useFirstPageNumber="0" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
   <dimension ref="A1:M943"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
@@ -5632,7 +11443,7 @@
         </is>
       </c>
       <c r="K3" s="89">
-        <f>SUM(C3,F3,C8,F8,C13,F13,C18,F18,C23,F23,C28)</f>
+        <f>SUM(C3,F3,C8,F8,C13,F13,C18,F18,C23,F23,C28,F28,C33,F33,C38,F38)</f>
         <v/>
       </c>
       <c r="L3" s="90">
@@ -5666,7 +11477,7 @@
         </is>
       </c>
       <c r="K4" s="92">
-        <f>SUM(C4,F4,C9,F9,C14,F14,C19,F19,C24,F24,C29)</f>
+        <f>SUM(C4,F4,C9,F9,C14,F14,C19,F19,C24,F24,C29,F29,C34,F34,C39,F39)</f>
         <v/>
       </c>
       <c r="L4" s="93">
@@ -5700,7 +11511,7 @@
         </is>
       </c>
       <c r="K5" s="96">
-        <f>SUM(C5,F5,C10,F10,C15,F15,C20,F20,C25,F25,C30)</f>
+        <f>SUM(C5,F5,C10,F10,C15,F15,C20,F20,C25,F25,C30,F30,C35,F35,C40,F40)</f>
         <v/>
       </c>
       <c r="L5" s="97">
@@ -5811,15 +11622,15 @@
         </is>
       </c>
       <c r="K9" s="92">
-        <f>SUM(Login!P3,Reset_Password!P3,Deposit!P3,Register!P3,Withdraw!P3,Convert!P3,International_School_Fee!P3,Profile!P3,Transfer!P3,Domestic_Transfer!P3,Global_Transfer!P3)</f>
+        <f>SUM(Login!P3,Reset_Password!P3,Deposit!P3,Register!P3,Withdraw!P3,Convert!P3,International_School_Fee!P3,Profile!P3,Transfer!P3,Domestic_Transfer!P3,Global_Transfer!P3,Bills!P3,Notification!P3,Trade_Record!P3,Wallet!P3,Payment!P3)</f>
         <v/>
       </c>
       <c r="L9" s="95">
-        <f>SUM(Login!Q3,Reset_Password!Q3,Deposit!Q3,Register!Q3,Withdraw!Q3,Convert!Q3,International_School_Fee!Q3,Profile!Q3,Transfer!Q3,Domestic_Transfer!Q3,Global_Transfer!Q3)</f>
+        <f>SUM(Login!Q3,Reset_Password!Q3,Deposit!Q3,Register!Q3,Withdraw!Q3,Convert!Q3,International_School_Fee!Q3,Profile!Q3,Transfer!Q3,Domestic_Transfer!Q3,Global_Transfer!Q3,Bills!Q3,Notification!Q3,Trade_Record!Q3,Wallet!Q3,Payment!Q3)</f>
         <v/>
       </c>
       <c r="M9" s="88">
-        <f>SUM(Login!R3,Reset_Password!R3,Deposit!R3,Register!R3,Withdraw!R3,Convert!R3,International_School_Fee!R3,Profile!R3,Transfer!R3,Domestic_Transfer!R3,Global_Transfer!R3)</f>
+        <f>SUM(Login!R3,Reset_Password!R3,Deposit!R3,Register!R3,Withdraw!R3,Convert!R3,International_School_Fee!R3,Profile!R3,Transfer!R3,Domestic_Transfer!R3,Global_Transfer!R3,Bills!R3,Notification!R3,Trade_Record!R3,Wallet!R3,Payment!R3)</f>
         <v/>
       </c>
     </row>
@@ -5849,15 +11660,15 @@
         </is>
       </c>
       <c r="K10" s="92">
-        <f>SUM(Login!P4,Reset_Password!P4,Deposit!P4,Register!P4,Withdraw!P4,Convert!P4,International_School_Fee!P4,Profile!P4,Transfer!P4,Domestic_Transfer!P4,Global_Transfer!P4)</f>
+        <f>SUM(Login!P4,Reset_Password!P4,Deposit!P4,Register!P4,Withdraw!P4,Convert!P4,International_School_Fee!P4,Profile!P4,Transfer!P4,Domestic_Transfer!P4,Global_Transfer!P4,Bills!P4,Notification!P4,Trade_Record!P4,Wallet!P4,Payment!P4)</f>
         <v/>
       </c>
       <c r="L10" s="95">
-        <f>SUM(Login!Q4,Reset_Password!Q4,Deposit!Q4,Register!Q4,Withdraw!Q4,Convert!Q4,International_School_Fee!Q4,Profile!Q4,Transfer!Q4,Domestic_Transfer!Q4,Global_Transfer!Q4)</f>
+        <f>SUM(Login!Q4,Reset_Password!Q4,Deposit!Q4,Register!Q4,Withdraw!Q4,Convert!Q4,International_School_Fee!Q4,Profile!Q4,Transfer!Q4,Domestic_Transfer!Q4,Global_Transfer!Q4,Bills!Q4,Notification!Q4,Trade_Record!Q4,Wallet!Q4,Payment!Q4)</f>
         <v/>
       </c>
       <c r="M10" s="88">
-        <f>SUM(Login!R4,Reset_Password!R4,Deposit!R4,Register!R4,Withdraw!R4,Convert!R4,International_School_Fee!R4,Profile!R4,Transfer!R4,Domestic_Transfer!R4,Global_Transfer!R4)</f>
+        <f>SUM(Login!R4,Reset_Password!R4,Deposit!R4,Register!R4,Withdraw!R4,Convert!R4,International_School_Fee!R4,Profile!R4,Transfer!R4,Domestic_Transfer!R4,Global_Transfer!R4,Bills!R4,Notification!R4,Trade_Record!R4,Wallet!R4,Payment!R4)</f>
         <v/>
       </c>
     </row>
@@ -5871,15 +11682,15 @@
         </is>
       </c>
       <c r="K11" s="92">
-        <f>SUM(Login!P5,Reset_Password!P5,Deposit!P5,Register!P5,Withdraw!P5,Convert!P5,International_School_Fee!P5,Profile!P5,Transfer!P5,Domestic_Transfer!P5,Global_Transfer!P5)</f>
+        <f>SUM(Login!P5,Reset_Password!P5,Deposit!P5,Register!P5,Withdraw!P5,Convert!P5,International_School_Fee!P5,Profile!P5,Transfer!P5,Domestic_Transfer!P5,Global_Transfer!P5,Bills!P5,Notification!P5,Trade_Record!P5,Wallet!P5,Payment!P5)</f>
         <v/>
       </c>
       <c r="L11" s="95">
-        <f>SUM(Login!Q5,Reset_Password!Q5,Deposit!Q5,Register!Q5,Withdraw!Q5,Convert!Q5,International_School_Fee!Q5,Profile!Q5,Transfer!Q5,Domestic_Transfer!Q5,Global_Transfer!Q5)</f>
+        <f>SUM(Login!Q5,Reset_Password!Q5,Deposit!Q5,Register!Q5,Withdraw!Q5,Convert!Q5,International_School_Fee!Q5,Profile!Q5,Transfer!Q5,Domestic_Transfer!Q5,Global_Transfer!Q5,Bills!Q5,Notification!Q5,Trade_Record!Q5,Wallet!Q5,Payment!Q5)</f>
         <v/>
       </c>
       <c r="M11" s="88">
-        <f>SUM(Login!R5,Reset_Password!R5,Deposit!R5,Register!R5,Withdraw!R5,Convert!R5,International_School_Fee!R5,Profile!R5,Transfer!R5,Domestic_Transfer!R5,Global_Transfer!R5)</f>
+        <f>SUM(Login!R5,Reset_Password!R5,Deposit!R5,Register!R5,Withdraw!R5,Convert!R5,International_School_Fee!R5,Profile!R5,Transfer!R5,Domestic_Transfer!R5,Global_Transfer!R5,Bills!R5,Notification!R5,Trade_Record!R5,Wallet!R5,Payment!R5)</f>
         <v/>
       </c>
     </row>
@@ -6247,7 +12058,11 @@
       </c>
       <c r="C27" s="83" t="n"/>
       <c r="D27" s="54" t="n"/>
-      <c r="E27" s="54" t="n"/>
+      <c r="E27" s="82" t="inlineStr">
+        <is>
+          <t>Bills</t>
+        </is>
+      </c>
       <c r="F27" s="54" t="n"/>
       <c r="G27" s="54" t="n"/>
       <c r="H27" s="54" t="n"/>
@@ -6268,8 +12083,15 @@
         <v/>
       </c>
       <c r="D28" s="54" t="n"/>
-      <c r="E28" s="54" t="n"/>
-      <c r="F28" s="54" t="n"/>
+      <c r="E28" s="86" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F28" s="87">
+        <f>COUNTIF(Bills!K:K,"PASS")</f>
+        <v/>
+      </c>
       <c r="G28" s="54" t="n"/>
       <c r="H28" s="54" t="n"/>
       <c r="I28" s="54" t="n"/>
@@ -6289,8 +12111,15 @@
         <v/>
       </c>
       <c r="D29" s="54" t="n"/>
-      <c r="E29" s="54" t="n"/>
-      <c r="F29" s="54" t="n"/>
+      <c r="E29" s="86" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F29" s="87">
+        <f>COUNTIF(Bills!K:K,"FAIL")</f>
+        <v/>
+      </c>
       <c r="G29" s="54" t="n"/>
       <c r="H29" s="54" t="n"/>
       <c r="I29" s="54" t="n"/>
@@ -6310,8 +12139,15 @@
         <v/>
       </c>
       <c r="D30" s="54" t="n"/>
-      <c r="E30" s="54" t="n"/>
-      <c r="F30" s="54" t="n"/>
+      <c r="E30" s="87" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F30" s="87">
+        <f>COUNTIF(Bills!K:K,"PENDING")</f>
+        <v/>
+      </c>
       <c r="G30" s="54" t="n"/>
       <c r="H30" s="54" t="n"/>
       <c r="I30" s="54" t="n"/>
@@ -6334,10 +12170,18 @@
     </row>
     <row r="32" ht="15.75" customHeight="1" s="51">
       <c r="A32" s="102" t="n"/>
-      <c r="B32" s="102" t="n"/>
+      <c r="B32" s="82" t="inlineStr">
+        <is>
+          <t>Notification</t>
+        </is>
+      </c>
       <c r="C32" s="94" t="n"/>
       <c r="D32" s="54" t="n"/>
-      <c r="E32" s="54" t="n"/>
+      <c r="E32" s="82" t="inlineStr">
+        <is>
+          <t>Trade_Record</t>
+        </is>
+      </c>
       <c r="F32" s="54" t="n"/>
       <c r="G32" s="54" t="n"/>
       <c r="H32" s="54" t="n"/>
@@ -6349,11 +12193,25 @@
     </row>
     <row r="33" ht="15.75" customHeight="1" s="51">
       <c r="A33" s="102" t="n"/>
-      <c r="B33" s="102" t="n"/>
-      <c r="C33" s="94" t="n"/>
+      <c r="B33" s="86" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C33" s="87">
+        <f>COUNTIF(Notification!K:K,"PASS")</f>
+        <v/>
+      </c>
       <c r="D33" s="54" t="n"/>
-      <c r="E33" s="54" t="n"/>
-      <c r="F33" s="54" t="n"/>
+      <c r="E33" s="86" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F33" s="87">
+        <f>COUNTIF(Trade_Record!K:K,"PASS")</f>
+        <v/>
+      </c>
       <c r="G33" s="54" t="n"/>
       <c r="H33" s="54" t="n"/>
       <c r="I33" s="54" t="n"/>
@@ -6364,11 +12222,25 @@
     </row>
     <row r="34" ht="15.75" customHeight="1" s="51">
       <c r="A34" s="102" t="n"/>
-      <c r="B34" s="102" t="n"/>
-      <c r="C34" s="94" t="n"/>
+      <c r="B34" s="86" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C34" s="87">
+        <f>COUNTIF(Notification!K:K,"FAIL")</f>
+        <v/>
+      </c>
       <c r="D34" s="54" t="n"/>
-      <c r="E34" s="54" t="n"/>
-      <c r="F34" s="54" t="n"/>
+      <c r="E34" s="86" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F34" s="87">
+        <f>COUNTIF(Trade_Record!K:K,"FAIL")</f>
+        <v/>
+      </c>
       <c r="G34" s="54" t="n"/>
       <c r="H34" s="54" t="n"/>
       <c r="I34" s="54" t="n"/>
@@ -6379,11 +12251,25 @@
     </row>
     <row r="35" ht="15.75" customHeight="1" s="51">
       <c r="A35" s="102" t="n"/>
-      <c r="B35" s="102" t="n"/>
-      <c r="C35" s="94" t="n"/>
+      <c r="B35" s="87" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C35" s="87">
+        <f>COUNTIF(Notification!K:K,"PENDING")</f>
+        <v/>
+      </c>
       <c r="D35" s="54" t="n"/>
-      <c r="E35" s="54" t="n"/>
-      <c r="F35" s="54" t="n"/>
+      <c r="E35" s="87" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F35" s="87">
+        <f>COUNTIF(Trade_Record!K:K,"PENDING")</f>
+        <v/>
+      </c>
       <c r="G35" s="54" t="n"/>
       <c r="H35" s="54" t="n"/>
       <c r="I35" s="54" t="n"/>
@@ -6409,10 +12295,18 @@
     </row>
     <row r="37" ht="15.75" customHeight="1" s="51">
       <c r="A37" s="102" t="n"/>
-      <c r="B37" s="102" t="n"/>
+      <c r="B37" s="82" t="inlineStr">
+        <is>
+          <t>Wallet</t>
+        </is>
+      </c>
       <c r="C37" s="94" t="n"/>
       <c r="D37" s="54" t="n"/>
-      <c r="E37" s="54" t="n"/>
+      <c r="E37" s="82" t="inlineStr">
+        <is>
+          <t>Payment</t>
+        </is>
+      </c>
       <c r="F37" s="54" t="n"/>
       <c r="G37" s="54" t="n"/>
       <c r="H37" s="54" t="n"/>
@@ -6424,11 +12318,25 @@
     </row>
     <row r="38" ht="15.75" customHeight="1" s="51">
       <c r="A38" s="102" t="n"/>
-      <c r="B38" s="102" t="n"/>
-      <c r="C38" s="94" t="n"/>
+      <c r="B38" s="86" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C38" s="87">
+        <f>COUNTIF(Wallet!K:K,"PASS")</f>
+        <v/>
+      </c>
       <c r="D38" s="54" t="n"/>
-      <c r="E38" s="54" t="n"/>
-      <c r="F38" s="54" t="n"/>
+      <c r="E38" s="86" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F38" s="87">
+        <f>COUNTIF(Payment!K:K,"PASS")</f>
+        <v/>
+      </c>
       <c r="G38" s="54" t="n"/>
       <c r="H38" s="54" t="n"/>
       <c r="I38" s="54" t="n"/>
@@ -6439,11 +12347,25 @@
     </row>
     <row r="39" ht="15.75" customHeight="1" s="51">
       <c r="A39" s="102" t="n"/>
-      <c r="B39" s="102" t="n"/>
-      <c r="C39" s="94" t="n"/>
+      <c r="B39" s="86" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C39" s="87">
+        <f>COUNTIF(Wallet!K:K,"FAIL")</f>
+        <v/>
+      </c>
       <c r="D39" s="54" t="n"/>
-      <c r="E39" s="54" t="n"/>
-      <c r="F39" s="54" t="n"/>
+      <c r="E39" s="86" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F39" s="87">
+        <f>COUNTIF(Payment!K:K,"FAIL")</f>
+        <v/>
+      </c>
       <c r="G39" s="54" t="n"/>
       <c r="H39" s="54" t="n"/>
       <c r="I39" s="54" t="n"/>
@@ -6454,11 +12376,25 @@
     </row>
     <row r="40" ht="15.75" customHeight="1" s="51">
       <c r="A40" s="102" t="n"/>
-      <c r="B40" s="102" t="n"/>
-      <c r="C40" s="94" t="n"/>
+      <c r="B40" s="87" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C40" s="87">
+        <f>COUNTIF(Wallet!K:K,"PENDING")</f>
+        <v/>
+      </c>
       <c r="D40" s="54" t="n"/>
-      <c r="E40" s="54" t="n"/>
-      <c r="F40" s="54" t="n"/>
+      <c r="E40" s="87" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F40" s="87">
+        <f>COUNTIF(Payment!K:K,"PENDING")</f>
+        <v/>
+      </c>
       <c r="G40" s="54" t="n"/>
       <c r="H40" s="54" t="n"/>
       <c r="I40" s="54" t="n"/>
@@ -20032,7 +25968,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20251,7 +26187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:T14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1"/>
@@ -21100,7 +27036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AA23"/>
+  <dimension ref="A1:AB23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="2"/>
@@ -22890,7 +28826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:T14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="2"/>
@@ -23745,7 +29681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S12"/>
+  <dimension ref="A1:T12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="2"/>
@@ -24419,7 +30355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:T21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -25956,7 +31892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AA29"/>
+  <dimension ref="A1:AB29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="2"/>
@@ -28015,7 +33951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="2"/>
@@ -29233,7 +35169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S11"/>
+  <dimension ref="A1:T11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>

--- a/TestCase/UMPay End-to-End Test Cases.xlsx
+++ b/TestCase/UMPay End-to-End Test Cases.xlsx
@@ -41923,7 +41923,7 @@
       </c>
       <c r="B2" s="58" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Reset Password</t>
         </is>
       </c>
       <c r="D2" s="54" t="n"/>

--- a/TestCase/UMPay End-to-End Test Cases.xlsx
+++ b/TestCase/UMPay End-to-End Test Cases.xlsx
@@ -937,7 +937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:T26"/>
+  <dimension ref="A1:S26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1"/>
@@ -2829,7 +2829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:T18"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -4065,7 +4065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:T15"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -5006,7 +5006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:T18"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -6220,7 +6220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:T19"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -7521,7 +7521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:T19"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -8822,7 +8822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:T21"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -10310,7 +10310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:T25"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -12180,7 +12180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:T22"/>
+  <dimension ref="A1:S22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -13760,7 +13760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:T18"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -14983,7 +14983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:T21"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -16479,7 +16479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:T15"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1"/>
@@ -17417,7 +17417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:T18"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -18640,7 +18640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:T21"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -20137,7 +20137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:T19"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -21435,7 +21435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:T18"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -22645,7 +22645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:T20"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -24044,7 +24044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:T14"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -24897,7 +24897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:T14"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -25748,7 +25748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -41886,7 +41886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AB24"/>
+  <dimension ref="A1:AA24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="2"/>
@@ -43666,12 +43666,12 @@
       </c>
       <c r="J24" s="72" t="inlineStr">
         <is>
-          <t>COULD NOT BE RUN - the platform answered the one-time-code request with 400 "Too Many Requests" (POST /api/notification/otp), so the verification step was never reached and going back from it could not be tried. This says nothing about the application either way; the account has simply asked for too many codes today. To be re-run once the limit clears</t>
+          <t>The reset by email reached the verification step, going back from it returned to the reset form, and no new password was set. This had been pending: the platform was answering the one-time-code request with 400 Too Many Requests after the endpoint had been exercised repeatedly, and the case could not be run at all until that cleared.</t>
         </is>
       </c>
       <c r="K24" s="53" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L24" s="53" t="inlineStr">
@@ -43685,7 +43685,7 @@
         </is>
       </c>
       <c r="N24" s="103" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="O24" s="53" t="inlineStr">
         <is>
@@ -43768,7 +43768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:T14"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="2"/>
@@ -44623,7 +44623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="2"/>
@@ -45670,7 +45670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:T21"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -47207,7 +47207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:T19"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="2"/>
@@ -48518,7 +48518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:T20"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -49951,7 +49951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>

--- a/TestCase/UMPay End-to-End Test Cases.xlsx
+++ b/TestCase/UMPay End-to-End Test Cases.xlsx
@@ -937,7 +937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S26"/>
+  <dimension ref="A1:T28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1"/>
@@ -2765,30 +2765,215 @@
         </is>
       </c>
     </row>
+    <row r="27" ht="15.75" customHeight="1" s="51">
+      <c r="A27" s="67" t="inlineStr">
+        <is>
+          <t>TC_019</t>
+        </is>
+      </c>
+      <c r="B27" s="68" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="C27" s="69" t="inlineStr">
+        <is>
+          <t>Signing in offers two factor authentication and lets it be skipped</t>
+        </is>
+      </c>
+      <c r="D27" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E27" s="71" t="inlineStr">
+        <is>
+          <t>User has valid credentials</t>
+        </is>
+      </c>
+      <c r="F27" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-Then the two factor prompt should be shown
+-When I skip the two factor prompt
+-Then I should be let through to the home page</t>
+        </is>
+      </c>
+      <c r="G27" s="67" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H27" s="73" t="inlineStr">
+        <is>
+          <t>Signing in should offer to set up two factor authentication, and skipping it should let the account through to its own home page</t>
+        </is>
+      </c>
+      <c r="I27" s="73" t="inlineStr">
+        <is>
+          <t>User is on the home page</t>
+        </is>
+      </c>
+      <c r="J27" s="73" t="inlineStr">
+        <is>
+          <t>The prompt was offered and skipping it let the account through to the home page with its wallets showing. The suite skips this prompt in twenty-one step classes and a few hundred times in a full pass, and had never once asked whether it was there to be skipped</t>
+        </is>
+      </c>
+      <c r="K27" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L27" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M27" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N27" s="103" t="n">
+        <v>46274</v>
+      </c>
+      <c r="O27" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P27" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q27" s="70" t="n"/>
+      <c r="R27" s="70" t="n"/>
+      <c r="S27" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1" s="51">
+      <c r="A28" s="67" t="inlineStr">
+        <is>
+          <t>TC_020</t>
+        </is>
+      </c>
+      <c r="B28" s="68" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="C28" s="69" t="inlineStr">
+        <is>
+          <t>Skipping two factor authentication does not stop it being offered again</t>
+        </is>
+      </c>
+      <c r="D28" s="70" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E28" s="71" t="inlineStr">
+        <is>
+          <t>User has skipped the two factor prompt and signed out</t>
+        </is>
+      </c>
+      <c r="F28" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-Then the two factor prompt should be shown
+-When I skip the two factor prompt
+-And I open the profile drawer
+-And I ask to log out
+-And I answer "Yes"
+-Then I should be signed out
+-When I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-Then the two factor prompt should be shown</t>
+        </is>
+      </c>
+      <c r="G28" s="67" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H28" s="73" t="inlineStr">
+        <is>
+          <t>Signing in again should offer two factor authentication again, since a security control offered once and never afterwards is one the account can only ever have by accident</t>
+        </is>
+      </c>
+      <c r="I28" s="73" t="inlineStr">
+        <is>
+          <t>User is on the home page</t>
+        </is>
+      </c>
+      <c r="J28" s="73" t="inlineStr">
+        <is>
+          <t>DEFECT - after skipping the prompt, signing out and signing straight back in on the same browser is never asked again. A fresh browser is asked every time, which every other scenario in the suite demonstrates a few hundred times a run, so the prompt is being remembered as dismissed for the browser rather than for the session. Whether that is intended is for the team to say; what it means is that somebody who skips it once is not asked to protect their account again on that machine</t>
+        </is>
+      </c>
+      <c r="K28" s="74" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L28" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M28" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N28" s="103" t="n">
+        <v>46274</v>
+      </c>
+      <c r="O28" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P28" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q28" s="70" t="n"/>
+      <c r="R28" s="70" t="n"/>
+      <c r="S28" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A8:AA23"/>
   <dataValidations count="7">
-    <dataValidation sqref="K9:K26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
+    <dataValidation sqref="K9:K28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
       <formula1>"PASS,FAIL,PENDING"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="P9:P26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
+    <dataValidation sqref="P9:P28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
       <formula1>METADATA!$H$2:$H$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="O9:O26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
+    <dataValidation sqref="O9:O28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
       <formula1>METADATA!$J$2:$J$7</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="D9:D26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
+    <dataValidation sqref="D9:D28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
       <formula1>METADATA!$N$2:$N$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="B4 M9:M26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
+    <dataValidation sqref="B4 M9:M28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
       <formula1>METADATA!$F$2:$F$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="L9:L26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
+    <dataValidation sqref="L9:L28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
       <formula1>"HIGH,MEDIUM,LOW"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2816,6 +3001,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S24" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S25" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S26" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S27" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S28" r:id="rId20"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.9840277777777779" bottom="0.9840277777777779" header="0.511805555555555" footer="0.511805555555555"/>
@@ -2829,7 +3016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -4065,7 +4252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:T17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -4954,29 +5141,215 @@
         </is>
       </c>
     </row>
+    <row r="16" ht="15.75" customHeight="1" s="51">
+      <c r="A16" s="67" t="inlineStr">
+        <is>
+          <t>TC_008</t>
+        </is>
+      </c>
+      <c r="B16" s="79" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="C16" s="72" t="inlineStr">
+        <is>
+          <t>Cancelling the logout leaves the account signed in</t>
+        </is>
+      </c>
+      <c r="D16" s="70" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E16" s="71" t="inlineStr">
+        <is>
+          <t>User is signed in with the profile drawer open</t>
+        </is>
+      </c>
+      <c r="F16" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the profile drawer
+-And I ask to log out
+-Then the application should ask whether I mean it
+-When I answer "Cancel"
+-Then I should still be signed in</t>
+        </is>
+      </c>
+      <c r="G16" s="72" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H16" s="73" t="inlineStr">
+        <is>
+          <t>Cancelling the logout confirmation should leave the session alone - a question that signs you out whichever button is pressed is not a question</t>
+        </is>
+      </c>
+      <c r="I16" s="73" t="inlineStr">
+        <is>
+          <t>User is still signed in</t>
+        </is>
+      </c>
+      <c r="J16" s="73" t="inlineStr">
+        <is>
+          <t>The logout question offers Cancel and Yes. Answering Cancel left the account signed in. This case was described in the notes at the top of Profile.feature and its steps had been written, but the scenario itself was never added - so nothing had ever held the Cancel button to doing anything at all</t>
+        </is>
+      </c>
+      <c r="K16" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L16" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M16" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N16" s="103" t="n">
+        <v>46274</v>
+      </c>
+      <c r="O16" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P16" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q16" s="70" t="n"/>
+      <c r="R16" s="70" t="n"/>
+      <c r="S16" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1" s="51">
+      <c r="A17" s="67" t="inlineStr">
+        <is>
+          <t>TC_009</t>
+        </is>
+      </c>
+      <c r="B17" s="79" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="C17" s="72" t="inlineStr">
+        <is>
+          <t>Going back after signing out does not show the account again</t>
+        </is>
+      </c>
+      <c r="D17" s="70" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E17" s="71" t="inlineStr">
+        <is>
+          <t>User has just signed out</t>
+        </is>
+      </c>
+      <c r="F17" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the profile drawer
+-And I ask to log out
+-Then the application should ask whether I mean it
+-When I answer "Yes"
+-Then I should be signed out
+-When I go back in the browser
+-Then the account should not be shown again</t>
+        </is>
+      </c>
+      <c r="G17" s="72" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H17" s="73" t="inlineStr">
+        <is>
+          <t>Stepping back to a page drawn while signed in should not show the account again, or signing out on a shared machine would leave it readable by whoever sits down next</t>
+        </is>
+      </c>
+      <c r="I17" s="73" t="inlineStr">
+        <is>
+          <t>User is signed out</t>
+        </is>
+      </c>
+      <c r="J17" s="73" t="inlineStr">
+        <is>
+          <t>After signing out, going back in the browser did not put the account on the screen again</t>
+        </is>
+      </c>
+      <c r="K17" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L17" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M17" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N17" s="103" t="n">
+        <v>46274</v>
+      </c>
+      <c r="O17" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P17" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q17" s="70" t="n"/>
+      <c r="R17" s="70" t="n"/>
+      <c r="S17" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="7">
-    <dataValidation sqref="K9:K15" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
+    <dataValidation sqref="K9:K17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
       <formula1>"PASS,FAIL,PENDING"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="P9:P15" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
+    <dataValidation sqref="P9:P17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
       <formula1>METADATA!$H$2:$H$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="O9:O15" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
+    <dataValidation sqref="O9:O17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
       <formula1>METADATA!$J$2:$J$7</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="D9:D15" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
+    <dataValidation sqref="D9:D17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
       <formula1>METADATA!$N$2:$N$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="B4 M9:M15" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
+    <dataValidation sqref="B4 M9:M17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
       <formula1>METADATA!$F$2:$F$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="L9:L15" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
+    <dataValidation sqref="L9:L17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
       <formula1>"HIGH,MEDIUM,LOW"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4993,6 +5366,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S14" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S16" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId9"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.9840277777777779" bottom="0.9840277777777779" header="0.511805555555555" footer="0.511805555555555"/>
@@ -5006,7 +5381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -6220,7 +6595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:T19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -7521,7 +7896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:T21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -8773,1308 +9148,6 @@
         </is>
       </c>
     </row>
-  </sheetData>
-  <dataValidations count="7">
-    <dataValidation sqref="K9:K19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"PASS,FAIL,PENDING"</formula1>
-    </dataValidation>
-    <dataValidation sqref="P9:P19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>METADATA!$H$2:$H$8</formula1>
-    </dataValidation>
-    <dataValidation sqref="O9:O19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>METADATA!$J$2:$J$7</formula1>
-    </dataValidation>
-    <dataValidation sqref="D9:D19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>METADATA!$N$2:$N$3</formula1>
-    </dataValidation>
-    <dataValidation sqref="B4 M9:M19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>METADATA!$F$2:$F$4</formula1>
-    </dataValidation>
-    <dataValidation sqref="L9:L19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"HIGH,MEDIUM,LOW"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"WPAY,UMPay,OFL,UNCS"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S14" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S16" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S19" r:id="rId11"/>
-  </hyperlinks>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.9840277777777779" bottom="0.9840277777777779" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="0" useFirstPageNumber="0" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <dimension ref="A1:S21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
-  <cols>
-    <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
-    <col width="10" customWidth="1" style="51" min="19" max="19"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="51">
-      <c r="A1" s="52" t="inlineStr">
-        <is>
-          <t>Project Name</t>
-        </is>
-      </c>
-      <c r="B1" s="53" t="inlineStr">
-        <is>
-          <t>UMPay</t>
-        </is>
-      </c>
-      <c r="D1" s="54" t="n"/>
-      <c r="H1" s="55" t="n"/>
-      <c r="K1" s="56" t="n"/>
-      <c r="L1" s="54" t="n"/>
-      <c r="M1" s="54" t="n"/>
-    </row>
-    <row r="2" ht="15.75" customHeight="1" s="51">
-      <c r="A2" s="57" t="inlineStr">
-        <is>
-          <t>Module/Feature Name</t>
-        </is>
-      </c>
-      <c r="B2" s="58" t="inlineStr">
-        <is>
-          <t>Wallet</t>
-        </is>
-      </c>
-      <c r="D2" s="54" t="n"/>
-      <c r="K2" s="56" t="n"/>
-      <c r="L2" s="54" t="n"/>
-      <c r="M2" s="54" t="n"/>
-      <c r="N2" s="54" t="n"/>
-      <c r="P2" s="59" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="Q2" s="59" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="R2" s="59" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1" s="51">
-      <c r="A3" s="57" t="inlineStr">
-        <is>
-          <t>Reference Document</t>
-        </is>
-      </c>
-      <c r="B3" s="58" t="n"/>
-      <c r="D3" s="54" t="n"/>
-      <c r="N3" s="60" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="O3" s="61">
-        <f>COUNTIF(K:K,"PASS")</f>
-        <v/>
-      </c>
-      <c r="P3" s="61">
-        <f>COUNTIFS(K:K,"PASS",L:L,"HIGH")</f>
-        <v/>
-      </c>
-      <c r="Q3" s="61">
-        <f>COUNTIFS(K:K,"PASS",L:L,"MEDIUM")</f>
-        <v/>
-      </c>
-      <c r="R3" s="61">
-        <f>COUNTIFS(K:K,"PASS",L:L,"LOW")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1" s="51">
-      <c r="A4" s="57" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B4" s="53" t="inlineStr">
-        <is>
-          <t>KIMA</t>
-        </is>
-      </c>
-      <c r="D4" s="54" t="n"/>
-      <c r="N4" s="60" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="O4" s="62">
-        <f>COUNTIF(K:K,"FAIL")</f>
-        <v/>
-      </c>
-      <c r="P4" s="62">
-        <f>COUNTIFS(K:K,"FAIL",L:L,"HIGH")</f>
-        <v/>
-      </c>
-      <c r="Q4" s="62">
-        <f>COUNTIFS(K:K,"FAIL",L:L,"MEDIUM")</f>
-        <v/>
-      </c>
-      <c r="R4" s="62">
-        <f>COUNTIFS(K:K,"FAIL",L:L,"LOW")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1" s="51">
-      <c r="A5" s="57" t="inlineStr">
-        <is>
-          <t>Date of Creation</t>
-        </is>
-      </c>
-      <c r="B5" s="63" t="n">
-        <v>46272</v>
-      </c>
-      <c r="D5" s="54" t="n"/>
-      <c r="N5" s="60" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="O5" s="64">
-        <f>COUNTIF(K:K,"PENDING")</f>
-        <v/>
-      </c>
-      <c r="P5" s="64">
-        <f>COUNTIFS(K:K,"PENDING",L:L,"HIGH")</f>
-        <v/>
-      </c>
-      <c r="Q5" s="64">
-        <f>COUNTIFS(K:K,"PENDING",L:L,"MEDIUM")</f>
-        <v/>
-      </c>
-      <c r="R5" s="64">
-        <f>COUNTIFS(K:K,"PENDING",L:L,"LOW")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1" s="51">
-      <c r="A6" s="57" t="inlineStr">
-        <is>
-          <t>Date of Review</t>
-        </is>
-      </c>
-      <c r="B6" s="63" t="n">
-        <v>46272</v>
-      </c>
-      <c r="D6" s="54" t="n"/>
-      <c r="H6" s="55" t="n"/>
-    </row>
-    <row r="7" ht="20.25" customHeight="1" s="51">
-      <c r="D7" s="54" t="n"/>
-      <c r="H7" s="55" t="n"/>
-    </row>
-    <row r="8" ht="15.75" customHeight="1" s="51">
-      <c r="A8" s="65" t="inlineStr">
-        <is>
-          <t>TEST CASE ID</t>
-        </is>
-      </c>
-      <c r="B8" s="65" t="inlineStr">
-        <is>
-          <t>TEST SCENARIO</t>
-        </is>
-      </c>
-      <c r="C8" s="65" t="inlineStr">
-        <is>
-          <t>TEST CASE</t>
-        </is>
-      </c>
-      <c r="D8" s="65" t="inlineStr">
-        <is>
-          <t>TEST CATEGORY</t>
-        </is>
-      </c>
-      <c r="E8" s="65" t="inlineStr">
-        <is>
-          <t>PRE-CONDITION</t>
-        </is>
-      </c>
-      <c r="F8" s="65" t="inlineStr">
-        <is>
-          <t>TEST STEPS</t>
-        </is>
-      </c>
-      <c r="G8" s="65" t="inlineStr">
-        <is>
-          <t>TEST DATA</t>
-        </is>
-      </c>
-      <c r="H8" s="65" t="inlineStr">
-        <is>
-          <t>EXPECTED RESULTS</t>
-        </is>
-      </c>
-      <c r="I8" s="65" t="inlineStr">
-        <is>
-          <t>POST CONDITION</t>
-        </is>
-      </c>
-      <c r="J8" s="65" t="inlineStr">
-        <is>
-          <t>ACTUAL RESULT</t>
-        </is>
-      </c>
-      <c r="K8" s="65" t="inlineStr">
-        <is>
-          <t>STATUS</t>
-        </is>
-      </c>
-      <c r="L8" s="65" t="inlineStr">
-        <is>
-          <t>PRIORITY</t>
-        </is>
-      </c>
-      <c r="M8" s="65" t="inlineStr">
-        <is>
-          <t>TESTER</t>
-        </is>
-      </c>
-      <c r="N8" s="65" t="inlineStr">
-        <is>
-          <t>TEST DATE</t>
-        </is>
-      </c>
-      <c r="O8" s="65" t="inlineStr">
-        <is>
-          <t>DEVICE</t>
-        </is>
-      </c>
-      <c r="P8" s="65" t="inlineStr">
-        <is>
-          <t>BROWSER</t>
-        </is>
-      </c>
-      <c r="Q8" s="65" t="inlineStr">
-        <is>
-          <t>ISSUE LINK</t>
-        </is>
-      </c>
-      <c r="R8" s="65" t="inlineStr">
-        <is>
-          <t>COMMENT</t>
-        </is>
-      </c>
-      <c r="S8" s="66" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1" s="51">
-      <c r="A9" s="67" t="inlineStr">
-        <is>
-          <t>TC_001</t>
-        </is>
-      </c>
-      <c r="B9" s="79" t="inlineStr">
-        <is>
-          <t>Wallet</t>
-        </is>
-      </c>
-      <c r="C9" s="72" t="inlineStr">
-        <is>
-          <t>The profile drawer opens the account's wallets</t>
-        </is>
-      </c>
-      <c r="D9" s="70" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E9" s="71" t="inlineStr">
-        <is>
-          <t>User is signed in</t>
-        </is>
-      </c>
-      <c r="F9" s="72" t="inlineStr">
-        <is>
-          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
--When I open the Wallet page
--Then the page should list the wallets the account holds</t>
-        </is>
-      </c>
-      <c r="G9" s="72" t="inlineStr">
-        <is>
-          <t>Valid UMPay user</t>
-        </is>
-      </c>
-      <c r="H9" s="73" t="inlineStr">
-        <is>
-          <t>The wallet page should open from the profile drawer, listing every wallet the account holds</t>
-        </is>
-      </c>
-      <c r="I9" s="73" t="inlineStr">
-        <is>
-          <t>User is on the Wallet page</t>
-        </is>
-      </c>
-      <c r="J9" s="73" t="inlineStr">
-        <is>
-          <t>The drawer opened /v2/wallet, listing 10 wallets: HKD, IDR, VND, PHP, MYR, BDT, USD, THB, MXN, BRL</t>
-        </is>
-      </c>
-      <c r="K9" s="74" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L9" s="74" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="M9" s="58" t="inlineStr">
-        <is>
-          <t>KIMA</t>
-        </is>
-      </c>
-      <c r="N9" s="103" t="n">
-        <v>46272</v>
-      </c>
-      <c r="O9" s="53" t="inlineStr">
-        <is>
-          <t>Window OS</t>
-        </is>
-      </c>
-      <c r="P9" s="76" t="inlineStr">
-        <is>
-          <t>Chromium</t>
-        </is>
-      </c>
-      <c r="Q9" s="70" t="n"/>
-      <c r="R9" s="70" t="n"/>
-      <c r="S9" s="77" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="15.75" customHeight="1" s="51">
-      <c r="A10" s="67" t="inlineStr">
-        <is>
-          <t>TC_002</t>
-        </is>
-      </c>
-      <c r="B10" s="79" t="inlineStr">
-        <is>
-          <t>Wallet List</t>
-        </is>
-      </c>
-      <c r="C10" s="72" t="inlineStr">
-        <is>
-          <t>Every wallet names its currency, country, balance and what is blocked</t>
-        </is>
-      </c>
-      <c r="D10" s="70" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E10" s="71" t="inlineStr">
-        <is>
-          <t>User is on the Wallet page</t>
-        </is>
-      </c>
-      <c r="F10" s="72" t="inlineStr">
-        <is>
-          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
--When I open the Wallet page
--Then every wallet should name its currency, country, balance and what is blocked</t>
-        </is>
-      </c>
-      <c r="G10" s="72" t="inlineStr">
-        <is>
-          <t>Valid UMPay user</t>
-        </is>
-      </c>
-      <c r="H10" s="73" t="inlineStr">
-        <is>
-          <t>Every wallet should name its currency, its country, its balance and its blocked amount</t>
-        </is>
-      </c>
-      <c r="I10" s="73" t="inlineStr">
-        <is>
-          <t>User is on the Wallet page</t>
-        </is>
-      </c>
-      <c r="J10" s="73" t="inlineStr">
-        <is>
-          <t>All 10 wallets named their currency, country, balance and blocked amount</t>
-        </is>
-      </c>
-      <c r="K10" s="74" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L10" s="74" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="M10" s="58" t="inlineStr">
-        <is>
-          <t>KIMA</t>
-        </is>
-      </c>
-      <c r="N10" s="103" t="n">
-        <v>46272</v>
-      </c>
-      <c r="O10" s="53" t="inlineStr">
-        <is>
-          <t>Window OS</t>
-        </is>
-      </c>
-      <c r="P10" s="76" t="inlineStr">
-        <is>
-          <t>Chromium</t>
-        </is>
-      </c>
-      <c r="Q10" s="70" t="n"/>
-      <c r="R10" s="70" t="n"/>
-      <c r="S10" s="77" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" s="51">
-      <c r="A11" s="67" t="inlineStr">
-        <is>
-          <t>TC_003</t>
-        </is>
-      </c>
-      <c r="B11" s="79" t="inlineStr">
-        <is>
-          <t>Wallet List</t>
-        </is>
-      </c>
-      <c r="C11" s="72" t="inlineStr">
-        <is>
-          <t>Exactly one wallet is the main wallet</t>
-        </is>
-      </c>
-      <c r="D11" s="70" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E11" s="71" t="inlineStr">
-        <is>
-          <t>User is on the Wallet page</t>
-        </is>
-      </c>
-      <c r="F11" s="72" t="inlineStr">
-        <is>
-          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
--When I open the Wallet page
--Then exactly one wallet should be the main wallet</t>
-        </is>
-      </c>
-      <c r="G11" s="72" t="inlineStr">
-        <is>
-          <t>Valid UMPay user</t>
-        </is>
-      </c>
-      <c r="H11" s="73" t="inlineStr">
-        <is>
-          <t>One wallet should be marked as the main wallet, and every other should offer to become it</t>
-        </is>
-      </c>
-      <c r="I11" s="73" t="inlineStr">
-        <is>
-          <t>User is on the Wallet page</t>
-        </is>
-      </c>
-      <c r="J11" s="73" t="inlineStr">
-        <is>
-          <t>The main wallet was HKD, and the other 9 each offered to become it</t>
-        </is>
-      </c>
-      <c r="K11" s="74" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L11" s="74" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="M11" s="58" t="inlineStr">
-        <is>
-          <t>KIMA</t>
-        </is>
-      </c>
-      <c r="N11" s="103" t="n">
-        <v>46272</v>
-      </c>
-      <c r="O11" s="53" t="inlineStr">
-        <is>
-          <t>Window OS</t>
-        </is>
-      </c>
-      <c r="P11" s="76" t="inlineStr">
-        <is>
-          <t>Chromium</t>
-        </is>
-      </c>
-      <c r="Q11" s="70" t="n"/>
-      <c r="R11" s="70" t="n"/>
-      <c r="S11" s="77" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="15.75" customHeight="1" s="51">
-      <c r="A12" s="67" t="inlineStr">
-        <is>
-          <t>TC_004</t>
-        </is>
-      </c>
-      <c r="B12" s="79" t="inlineStr">
-        <is>
-          <t>Wallet List</t>
-        </is>
-      </c>
-      <c r="C12" s="72" t="inlineStr">
-        <is>
-          <t>Each wallet states its balance and what is blocked in its own currency</t>
-        </is>
-      </c>
-      <c r="D12" s="70" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E12" s="71" t="inlineStr">
-        <is>
-          <t>User is on the Wallet page</t>
-        </is>
-      </c>
-      <c r="F12" s="72" t="inlineStr">
-        <is>
-          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
--When I open the Wallet page
--Then each wallet's figures should be written in its own currency</t>
-        </is>
-      </c>
-      <c r="G12" s="72" t="inlineStr">
-        <is>
-          <t>Valid UMPay user</t>
-        </is>
-      </c>
-      <c r="H12" s="73" t="inlineStr">
-        <is>
-          <t>A wallet's balance and its blocked amount should be written in the same currency symbol</t>
-        </is>
-      </c>
-      <c r="I12" s="73" t="inlineStr">
-        <is>
-          <t>User is on the Wallet page</t>
-        </is>
-      </c>
-      <c r="J12" s="73" t="inlineStr">
-        <is>
-          <t>Every wallet used one symbol throughout: HKD=HK$, IDR=Rp, MYR=RM, USD=US$, BRL=R$, MXN=MXN$ and so on</t>
-        </is>
-      </c>
-      <c r="K12" s="74" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L12" s="74" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M12" s="58" t="inlineStr">
-        <is>
-          <t>KIMA</t>
-        </is>
-      </c>
-      <c r="N12" s="103" t="n">
-        <v>46272</v>
-      </c>
-      <c r="O12" s="53" t="inlineStr">
-        <is>
-          <t>Window OS</t>
-        </is>
-      </c>
-      <c r="P12" s="76" t="inlineStr">
-        <is>
-          <t>Chromium</t>
-        </is>
-      </c>
-      <c r="Q12" s="70" t="n"/>
-      <c r="R12" s="70" t="n"/>
-      <c r="S12" s="77" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15.75" customHeight="1" s="51">
-      <c r="A13" s="67" t="inlineStr">
-        <is>
-          <t>TC_005</t>
-        </is>
-      </c>
-      <c r="B13" s="79" t="inlineStr">
-        <is>
-          <t>Wallet Chart</t>
-        </is>
-      </c>
-      <c r="C13" s="72" t="inlineStr">
-        <is>
-          <t>The chart only names countries the account holds a wallet for</t>
-        </is>
-      </c>
-      <c r="D13" s="70" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E13" s="71" t="inlineStr">
-        <is>
-          <t>User is on the Wallet page</t>
-        </is>
-      </c>
-      <c r="F13" s="72" t="inlineStr">
-        <is>
-          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
--When I open the Wallet page
--Then every country in the chart should be one the account holds a wallet for</t>
-        </is>
-      </c>
-      <c r="G13" s="72" t="inlineStr">
-        <is>
-          <t>Valid UMPay user</t>
-        </is>
-      </c>
-      <c r="H13" s="73" t="inlineStr">
-        <is>
-          <t>Every country in the assets chart should be one the account holds a wallet for</t>
-        </is>
-      </c>
-      <c r="I13" s="73" t="inlineStr">
-        <is>
-          <t>User is on the Wallet page</t>
-        </is>
-      </c>
-      <c r="J13" s="73" t="inlineStr">
-        <is>
-          <t>The chart named Indonesia, Vietnam, Philippines, Malaysia and Bangladesh, all of them wallets the account holds</t>
-        </is>
-      </c>
-      <c r="K13" s="74" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L13" s="74" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M13" s="58" t="inlineStr">
-        <is>
-          <t>KIMA</t>
-        </is>
-      </c>
-      <c r="N13" s="103" t="n">
-        <v>46272</v>
-      </c>
-      <c r="O13" s="53" t="inlineStr">
-        <is>
-          <t>Window OS</t>
-        </is>
-      </c>
-      <c r="P13" s="76" t="inlineStr">
-        <is>
-          <t>Chromium</t>
-        </is>
-      </c>
-      <c r="Q13" s="70" t="n"/>
-      <c r="R13" s="70" t="n"/>
-      <c r="S13" s="77" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15.75" customHeight="1" s="51">
-      <c r="A14" s="67" t="inlineStr">
-        <is>
-          <t>TC_006</t>
-        </is>
-      </c>
-      <c r="B14" s="79" t="inlineStr">
-        <is>
-          <t>Wallet Detail</t>
-        </is>
-      </c>
-      <c r="C14" s="72" t="inlineStr">
-        <is>
-          <t>A wallet opens its own page</t>
-        </is>
-      </c>
-      <c r="D14" s="70" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E14" s="71" t="inlineStr">
-        <is>
-          <t>User is on the Wallet page</t>
-        </is>
-      </c>
-      <c r="F14" s="72" t="inlineStr">
-        <is>
-          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
--When I open the Wallet page
--And I open the wallet named in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
--Then that wallet's own page should open
--And the wallet should state its total, what is available and what is locked</t>
-        </is>
-      </c>
-      <c r="G14" s="72" t="inlineStr">
-        <is>
-          <t>Wallet: HKD</t>
-        </is>
-      </c>
-      <c r="H14" s="73" t="inlineStr">
-        <is>
-          <t>Opening a wallet should go to that wallet's own page, stating its total, available and locked balances</t>
-        </is>
-      </c>
-      <c r="I14" s="73" t="inlineStr">
-        <is>
-          <t>User is on the wallet's own page</t>
-        </is>
-      </c>
-      <c r="J14" s="73" t="inlineStr">
-        <is>
-          <t>The HKD wallet opened at /v2/wallet/detail/record?currencyCode=HKD, stating all three balances</t>
-        </is>
-      </c>
-      <c r="K14" s="74" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L14" s="74" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="M14" s="58" t="inlineStr">
-        <is>
-          <t>KIMA</t>
-        </is>
-      </c>
-      <c r="N14" s="103" t="n">
-        <v>46272</v>
-      </c>
-      <c r="O14" s="53" t="inlineStr">
-        <is>
-          <t>Window OS</t>
-        </is>
-      </c>
-      <c r="P14" s="76" t="inlineStr">
-        <is>
-          <t>Chromium</t>
-        </is>
-      </c>
-      <c r="Q14" s="70" t="n"/>
-      <c r="R14" s="70" t="n"/>
-      <c r="S14" s="77" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15.75" customHeight="1" s="51">
-      <c r="A15" s="67" t="inlineStr">
-        <is>
-          <t>TC_007</t>
-        </is>
-      </c>
-      <c r="B15" s="79" t="inlineStr">
-        <is>
-          <t>Wallet Detail</t>
-        </is>
-      </c>
-      <c r="C15" s="72" t="inlineStr">
-        <is>
-          <t>A wallet's total is what is available plus what is locked</t>
-        </is>
-      </c>
-      <c r="D15" s="70" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E15" s="71" t="inlineStr">
-        <is>
-          <t>User is on a wallet's own page</t>
-        </is>
-      </c>
-      <c r="F15" s="72" t="inlineStr">
-        <is>
-          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
--When I open the Wallet page
--And I open the wallet named in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
--Then the wallet's total should be what is available plus what is locked</t>
-        </is>
-      </c>
-      <c r="G15" s="72" t="inlineStr">
-        <is>
-          <t>Wallet: HKD</t>
-        </is>
-      </c>
-      <c r="H15" s="73" t="inlineStr">
-        <is>
-          <t>The total balance should equal the available balance plus the amount locked</t>
-        </is>
-      </c>
-      <c r="I15" s="73" t="inlineStr">
-        <is>
-          <t>User is on the wallet's own page</t>
-        </is>
-      </c>
-      <c r="J15" s="73" t="inlineStr">
-        <is>
-          <t>8369.51 available plus 5544.32 locked came to the stated total of 13913.83</t>
-        </is>
-      </c>
-      <c r="K15" s="74" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L15" s="74" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="M15" s="58" t="inlineStr">
-        <is>
-          <t>KIMA</t>
-        </is>
-      </c>
-      <c r="N15" s="103" t="n">
-        <v>46272</v>
-      </c>
-      <c r="O15" s="53" t="inlineStr">
-        <is>
-          <t>Window OS</t>
-        </is>
-      </c>
-      <c r="P15" s="76" t="inlineStr">
-        <is>
-          <t>Chromium</t>
-        </is>
-      </c>
-      <c r="Q15" s="70" t="n"/>
-      <c r="R15" s="70" t="n"/>
-      <c r="S15" s="77" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15.75" customHeight="1" s="51">
-      <c r="A16" s="67" t="inlineStr">
-        <is>
-          <t>TC_008</t>
-        </is>
-      </c>
-      <c r="B16" s="79" t="inlineStr">
-        <is>
-          <t>Wallet Detail</t>
-        </is>
-      </c>
-      <c r="C16" s="72" t="inlineStr">
-        <is>
-          <t>A wallet keeps what has moved and what is held in two tabs</t>
-        </is>
-      </c>
-      <c r="D16" s="70" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E16" s="71" t="inlineStr">
-        <is>
-          <t>User is on a wallet's own page</t>
-        </is>
-      </c>
-      <c r="F16" s="72" t="inlineStr">
-        <is>
-          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
--When I open the Wallet page
--And I open the wallet named in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
--Then the wallet should offer the tabs "Record, Locked"</t>
-        </is>
-      </c>
-      <c r="G16" s="72" t="inlineStr">
-        <is>
-          <t>Wallet: HKD</t>
-        </is>
-      </c>
-      <c r="H16" s="73" t="inlineStr">
-        <is>
-          <t>The wallet should offer a Record tab and a Locked tab</t>
-        </is>
-      </c>
-      <c r="I16" s="73" t="inlineStr">
-        <is>
-          <t>User is on the wallet's own page</t>
-        </is>
-      </c>
-      <c r="J16" s="73" t="inlineStr">
-        <is>
-          <t>The wallet offered both the Record and Locked tabs</t>
-        </is>
-      </c>
-      <c r="K16" s="74" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L16" s="74" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M16" s="58" t="inlineStr">
-        <is>
-          <t>KIMA</t>
-        </is>
-      </c>
-      <c r="N16" s="103" t="n">
-        <v>46272</v>
-      </c>
-      <c r="O16" s="53" t="inlineStr">
-        <is>
-          <t>Window OS</t>
-        </is>
-      </c>
-      <c r="P16" s="76" t="inlineStr">
-        <is>
-          <t>Chromium</t>
-        </is>
-      </c>
-      <c r="Q16" s="70" t="n"/>
-      <c r="R16" s="70" t="n"/>
-      <c r="S16" s="77" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15.75" customHeight="1" s="51">
-      <c r="A17" s="67" t="inlineStr">
-        <is>
-          <t>TC_009</t>
-        </is>
-      </c>
-      <c r="B17" s="79" t="inlineStr">
-        <is>
-          <t>Wallet Detail</t>
-        </is>
-      </c>
-      <c r="C17" s="72" t="inlineStr">
-        <is>
-          <t>The Record tab lists what has moved in that wallet</t>
-        </is>
-      </c>
-      <c r="D17" s="70" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E17" s="71" t="inlineStr">
-        <is>
-          <t>User is on a wallet's own page</t>
-        </is>
-      </c>
-      <c r="F17" s="72" t="inlineStr">
-        <is>
-          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
--When I open the Wallet page
--And I open the wallet named in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
--And I move to the wallet's "Record" tab
--Then every movement should name what it was, when it happened and how much</t>
-        </is>
-      </c>
-      <c r="G17" s="72" t="inlineStr">
-        <is>
-          <t>Wallet: HKD</t>
-        </is>
-      </c>
-      <c r="H17" s="73" t="inlineStr">
-        <is>
-          <t>Every movement should name what it was, when it happened and how much</t>
-        </is>
-      </c>
-      <c r="I17" s="73" t="inlineStr">
-        <is>
-          <t>User is on the wallet's own page</t>
-        </is>
-      </c>
-      <c r="J17" s="73" t="inlineStr">
-        <is>
-          <t>The Record tab listed 20 movements, the newest being Convert 2026-09-07 15:44:33 HK$-1</t>
-        </is>
-      </c>
-      <c r="K17" s="74" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L17" s="74" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="M17" s="58" t="inlineStr">
-        <is>
-          <t>KIMA</t>
-        </is>
-      </c>
-      <c r="N17" s="103" t="n">
-        <v>46272</v>
-      </c>
-      <c r="O17" s="53" t="inlineStr">
-        <is>
-          <t>Window OS</t>
-        </is>
-      </c>
-      <c r="P17" s="76" t="inlineStr">
-        <is>
-          <t>Chromium</t>
-        </is>
-      </c>
-      <c r="Q17" s="70" t="n"/>
-      <c r="R17" s="70" t="n"/>
-      <c r="S17" s="77" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" s="51">
-      <c r="A18" s="67" t="inlineStr">
-        <is>
-          <t>TC_010</t>
-        </is>
-      </c>
-      <c r="B18" s="79" t="inlineStr">
-        <is>
-          <t>Wallet Detail</t>
-        </is>
-      </c>
-      <c r="C18" s="72" t="inlineStr">
-        <is>
-          <t>The Locked tab lists what is being held against that wallet</t>
-        </is>
-      </c>
-      <c r="D18" s="70" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E18" s="71" t="inlineStr">
-        <is>
-          <t>User is on a wallet's own page</t>
-        </is>
-      </c>
-      <c r="F18" s="72" t="inlineStr">
-        <is>
-          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
--When I open the Wallet page
--And I open the wallet named in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
--And I move to the wallet's "Locked" tab
--Then every movement should name what it was, when it happened and how much</t>
-        </is>
-      </c>
-      <c r="G18" s="72" t="inlineStr">
-        <is>
-          <t>Wallet: HKD</t>
-        </is>
-      </c>
-      <c r="H18" s="73" t="inlineStr">
-        <is>
-          <t>Every held amount should name what it was, when it happened and how much</t>
-        </is>
-      </c>
-      <c r="I18" s="73" t="inlineStr">
-        <is>
-          <t>User is on the wallet's own page</t>
-        </is>
-      </c>
-      <c r="J18" s="73" t="inlineStr">
-        <is>
-          <t>The Locked tab listed 20 held amounts, the newest being Withdraw 2026-09-07 12:28:22 HK$-107</t>
-        </is>
-      </c>
-      <c r="K18" s="74" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L18" s="74" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M18" s="58" t="inlineStr">
-        <is>
-          <t>KIMA</t>
-        </is>
-      </c>
-      <c r="N18" s="103" t="n">
-        <v>46272</v>
-      </c>
-      <c r="O18" s="53" t="inlineStr">
-        <is>
-          <t>Window OS</t>
-        </is>
-      </c>
-      <c r="P18" s="76" t="inlineStr">
-        <is>
-          <t>Chromium</t>
-        </is>
-      </c>
-      <c r="Q18" s="70" t="n"/>
-      <c r="R18" s="70" t="n"/>
-      <c r="S18" s="77" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15.75" customHeight="1" s="51">
-      <c r="A19" s="67" t="inlineStr">
-        <is>
-          <t>TC_011</t>
-        </is>
-      </c>
-      <c r="B19" s="79" t="inlineStr">
-        <is>
-          <t>Wallet Detail</t>
-        </is>
-      </c>
-      <c r="C19" s="72" t="inlineStr">
-        <is>
-          <t>A wallet's own page offers to make it the main wallet</t>
-        </is>
-      </c>
-      <c r="D19" s="70" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E19" s="71" t="inlineStr">
-        <is>
-          <t>User is on a wallet's own page</t>
-        </is>
-      </c>
-      <c r="F19" s="72" t="inlineStr">
-        <is>
-          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
--When I open the Wallet page
--And I open the wallet named in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
--Then the wallet should offer to become the main wallet</t>
-        </is>
-      </c>
-      <c r="G19" s="72" t="inlineStr">
-        <is>
-          <t>Wallet: HKD</t>
-        </is>
-      </c>
-      <c r="H19" s="73" t="inlineStr">
-        <is>
-          <t>The wallet should offer a Set as main button</t>
-        </is>
-      </c>
-      <c r="I19" s="73" t="inlineStr">
-        <is>
-          <t>User is on the wallet's own page</t>
-        </is>
-      </c>
-      <c r="J19" s="73" t="inlineStr">
-        <is>
-          <t>The wallet offered to become the main wallet</t>
-        </is>
-      </c>
-      <c r="K19" s="74" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L19" s="74" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M19" s="58" t="inlineStr">
-        <is>
-          <t>KIMA</t>
-        </is>
-      </c>
-      <c r="N19" s="103" t="n">
-        <v>46272</v>
-      </c>
-      <c r="O19" s="53" t="inlineStr">
-        <is>
-          <t>Window OS</t>
-        </is>
-      </c>
-      <c r="P19" s="76" t="inlineStr">
-        <is>
-          <t>Chromium</t>
-        </is>
-      </c>
-      <c r="Q19" s="70" t="n"/>
-      <c r="R19" s="70" t="n"/>
-      <c r="S19" s="77" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-    </row>
     <row r="20" ht="15.75" customHeight="1" s="51">
       <c r="A20" s="67" t="inlineStr">
         <is>
@@ -10083,12 +9156,12 @@
       </c>
       <c r="B20" s="79" t="inlineStr">
         <is>
-          <t>Wallet Detail</t>
+          <t>Trade Record</t>
         </is>
       </c>
       <c r="C20" s="72" t="inlineStr">
         <is>
-          <t>Going back from a wallet returns to the list</t>
+          <t>An order's receipt can be downloaded</t>
         </is>
       </c>
       <c r="D20" s="70" t="inlineStr">
@@ -10098,37 +9171,36 @@
       </c>
       <c r="E20" s="71" t="inlineStr">
         <is>
-          <t>User is on a wallet's own page</t>
+          <t>User has opened an order from the trade record</t>
         </is>
       </c>
       <c r="F20" s="72" t="inlineStr">
         <is>
           <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
--When I open the Wallet page
--And I open the wallet named in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
--Then that wallet's own page should open
--When I go back to the wallets
--Then the wallets should be listed again</t>
+-When I open the Trade Record page
+-And I open the newest order
+-Then the order should offer to be kept
+-And downloading the order should produce a file</t>
         </is>
       </c>
       <c r="G20" s="72" t="inlineStr">
         <is>
-          <t>Wallet: HKD</t>
+          <t>The newest order</t>
         </is>
       </c>
       <c r="H20" s="73" t="inlineStr">
         <is>
-          <t>Going back should return to the list of wallets</t>
+          <t>An order should offer its receipt to be kept, as the bills and the commission listing both do - an order somebody cannot keep a copy of is one they cannot show to anybody asking where the money went</t>
         </is>
       </c>
       <c r="I20" s="73" t="inlineStr">
         <is>
-          <t>User is on the Wallet page</t>
+          <t>A receipt file exists</t>
         </is>
       </c>
       <c r="J20" s="73" t="inlineStr">
         <is>
-          <t>Going back returned to the wallet list, all 10 still listed</t>
+          <t>The order offers Download and Share beside Done, and downloading produced Withdraw-Ld859bxvvnGrONgm.png at 22,150 bytes</t>
         </is>
       </c>
       <c r="K20" s="74" t="inlineStr">
@@ -10147,7 +9219,7 @@
         </is>
       </c>
       <c r="N20" s="103" t="n">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="O20" s="53" t="inlineStr">
         <is>
@@ -10175,12 +9247,12 @@
       </c>
       <c r="B21" s="79" t="inlineStr">
         <is>
-          <t>Wallet Main</t>
+          <t>Trade Record</t>
         </is>
       </c>
       <c r="C21" s="72" t="inlineStr">
         <is>
-          <t>The main wallet can be moved to another wallet and put back</t>
+          <t>An order can be shared</t>
         </is>
       </c>
       <c r="D21" s="70" t="inlineStr">
@@ -10190,37 +9262,36 @@
       </c>
       <c r="E21" s="71" t="inlineStr">
         <is>
-          <t>User is on the Wallet page</t>
+          <t>User has opened an order from the trade record</t>
         </is>
       </c>
       <c r="F21" s="72" t="inlineStr">
         <is>
           <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
--When I open the Wallet page
--And I make the wallet named in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;" the main one
--Then that wallet should become the main one
--When I put the main wallet back
--Then the wallet that was main should be main again</t>
+-When I open the Trade Record page
+-And I open the newest order
+-When I share the order
+-Then the sharing choices should offer a way to copy the order</t>
         </is>
       </c>
       <c r="G21" s="72" t="inlineStr">
         <is>
-          <t>Move the main wallet to IDR</t>
+          <t>The newest order</t>
         </is>
       </c>
       <c r="H21" s="73" t="inlineStr">
         <is>
-          <t>The chosen wallet should become the main one, and setting the first one back should restore it</t>
+          <t>Sharing an order should offer a way to copy it, as the bills and the commission listing both do</t>
         </is>
       </c>
       <c r="I21" s="73" t="inlineStr">
         <is>
-          <t>The main wallet is as it was found</t>
+          <t>User is on the order</t>
         </is>
       </c>
       <c r="J21" s="73" t="inlineStr">
         <is>
-          <t>The main wallet moved from HKD to IDR and was put back to HKD, with nothing asked first</t>
+          <t>Sharing the order offered a way to copy it</t>
         </is>
       </c>
       <c r="K21" s="74" t="inlineStr">
@@ -10230,7 +9301,7 @@
       </c>
       <c r="L21" s="74" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="M21" s="58" t="inlineStr">
@@ -10239,7 +9310,7 @@
         </is>
       </c>
       <c r="N21" s="103" t="n">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="O21" s="53" t="inlineStr">
         <is>
@@ -10304,13 +9375,1592 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:T22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
+    <col width="10" customWidth="1" style="51" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1" s="51">
+      <c r="A1" s="52" t="inlineStr">
+        <is>
+          <t>Project Name</t>
+        </is>
+      </c>
+      <c r="B1" s="53" t="inlineStr">
+        <is>
+          <t>UMPay</t>
+        </is>
+      </c>
+      <c r="D1" s="54" t="n"/>
+      <c r="H1" s="55" t="n"/>
+      <c r="K1" s="56" t="n"/>
+      <c r="L1" s="54" t="n"/>
+      <c r="M1" s="54" t="n"/>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" s="51">
+      <c r="A2" s="57" t="inlineStr">
+        <is>
+          <t>Module/Feature Name</t>
+        </is>
+      </c>
+      <c r="B2" s="58" t="inlineStr">
+        <is>
+          <t>Wallet</t>
+        </is>
+      </c>
+      <c r="D2" s="54" t="n"/>
+      <c r="K2" s="56" t="n"/>
+      <c r="L2" s="54" t="n"/>
+      <c r="M2" s="54" t="n"/>
+      <c r="N2" s="54" t="n"/>
+      <c r="P2" s="59" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="Q2" s="59" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="R2" s="59" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1" s="51">
+      <c r="A3" s="57" t="inlineStr">
+        <is>
+          <t>Reference Document</t>
+        </is>
+      </c>
+      <c r="B3" s="58" t="n"/>
+      <c r="D3" s="54" t="n"/>
+      <c r="N3" s="60" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="O3" s="61">
+        <f>COUNTIF(K:K,"PASS")</f>
+        <v/>
+      </c>
+      <c r="P3" s="61">
+        <f>COUNTIFS(K:K,"PASS",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="61">
+        <f>COUNTIFS(K:K,"PASS",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R3" s="61">
+        <f>COUNTIFS(K:K,"PASS",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1" s="51">
+      <c r="A4" s="57" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B4" s="53" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="D4" s="54" t="n"/>
+      <c r="N4" s="60" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="O4" s="62">
+        <f>COUNTIF(K:K,"FAIL")</f>
+        <v/>
+      </c>
+      <c r="P4" s="62">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q4" s="62">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R4" s="62">
+        <f>COUNTIFS(K:K,"FAIL",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1" s="51">
+      <c r="A5" s="57" t="inlineStr">
+        <is>
+          <t>Date of Creation</t>
+        </is>
+      </c>
+      <c r="B5" s="63" t="n">
+        <v>46272</v>
+      </c>
+      <c r="D5" s="54" t="n"/>
+      <c r="N5" s="60" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="O5" s="64">
+        <f>COUNTIF(K:K,"PENDING")</f>
+        <v/>
+      </c>
+      <c r="P5" s="64">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"HIGH")</f>
+        <v/>
+      </c>
+      <c r="Q5" s="64">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"MEDIUM")</f>
+        <v/>
+      </c>
+      <c r="R5" s="64">
+        <f>COUNTIFS(K:K,"PENDING",L:L,"LOW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1" s="51">
+      <c r="A6" s="57" t="inlineStr">
+        <is>
+          <t>Date of Review</t>
+        </is>
+      </c>
+      <c r="B6" s="63" t="n">
+        <v>46272</v>
+      </c>
+      <c r="D6" s="54" t="n"/>
+      <c r="H6" s="55" t="n"/>
+    </row>
+    <row r="7" ht="20.25" customHeight="1" s="51">
+      <c r="D7" s="54" t="n"/>
+      <c r="H7" s="55" t="n"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1" s="51">
+      <c r="A8" s="65" t="inlineStr">
+        <is>
+          <t>TEST CASE ID</t>
+        </is>
+      </c>
+      <c r="B8" s="65" t="inlineStr">
+        <is>
+          <t>TEST SCENARIO</t>
+        </is>
+      </c>
+      <c r="C8" s="65" t="inlineStr">
+        <is>
+          <t>TEST CASE</t>
+        </is>
+      </c>
+      <c r="D8" s="65" t="inlineStr">
+        <is>
+          <t>TEST CATEGORY</t>
+        </is>
+      </c>
+      <c r="E8" s="65" t="inlineStr">
+        <is>
+          <t>PRE-CONDITION</t>
+        </is>
+      </c>
+      <c r="F8" s="65" t="inlineStr">
+        <is>
+          <t>TEST STEPS</t>
+        </is>
+      </c>
+      <c r="G8" s="65" t="inlineStr">
+        <is>
+          <t>TEST DATA</t>
+        </is>
+      </c>
+      <c r="H8" s="65" t="inlineStr">
+        <is>
+          <t>EXPECTED RESULTS</t>
+        </is>
+      </c>
+      <c r="I8" s="65" t="inlineStr">
+        <is>
+          <t>POST CONDITION</t>
+        </is>
+      </c>
+      <c r="J8" s="65" t="inlineStr">
+        <is>
+          <t>ACTUAL RESULT</t>
+        </is>
+      </c>
+      <c r="K8" s="65" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="L8" s="65" t="inlineStr">
+        <is>
+          <t>PRIORITY</t>
+        </is>
+      </c>
+      <c r="M8" s="65" t="inlineStr">
+        <is>
+          <t>TESTER</t>
+        </is>
+      </c>
+      <c r="N8" s="65" t="inlineStr">
+        <is>
+          <t>TEST DATE</t>
+        </is>
+      </c>
+      <c r="O8" s="65" t="inlineStr">
+        <is>
+          <t>DEVICE</t>
+        </is>
+      </c>
+      <c r="P8" s="65" t="inlineStr">
+        <is>
+          <t>BROWSER</t>
+        </is>
+      </c>
+      <c r="Q8" s="65" t="inlineStr">
+        <is>
+          <t>ISSUE LINK</t>
+        </is>
+      </c>
+      <c r="R8" s="65" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="S8" s="66" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" s="51">
+      <c r="A9" s="67" t="inlineStr">
+        <is>
+          <t>TC_001</t>
+        </is>
+      </c>
+      <c r="B9" s="79" t="inlineStr">
+        <is>
+          <t>Wallet</t>
+        </is>
+      </c>
+      <c r="C9" s="72" t="inlineStr">
+        <is>
+          <t>The profile drawer opens the account's wallets</t>
+        </is>
+      </c>
+      <c r="D9" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E9" s="71" t="inlineStr">
+        <is>
+          <t>User is signed in</t>
+        </is>
+      </c>
+      <c r="F9" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Wallet page
+-Then the page should list the wallets the account holds</t>
+        </is>
+      </c>
+      <c r="G9" s="72" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H9" s="73" t="inlineStr">
+        <is>
+          <t>The wallet page should open from the profile drawer, listing every wallet the account holds</t>
+        </is>
+      </c>
+      <c r="I9" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Wallet page</t>
+        </is>
+      </c>
+      <c r="J9" s="73" t="inlineStr">
+        <is>
+          <t>The drawer opened /v2/wallet, listing 10 wallets: HKD, IDR, VND, PHP, MYR, BDT, USD, THB, MXN, BRL</t>
+        </is>
+      </c>
+      <c r="K9" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L9" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M9" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N9" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O9" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P9" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q9" s="70" t="n"/>
+      <c r="R9" s="70" t="n"/>
+      <c r="S9" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15.75" customHeight="1" s="51">
+      <c r="A10" s="67" t="inlineStr">
+        <is>
+          <t>TC_002</t>
+        </is>
+      </c>
+      <c r="B10" s="79" t="inlineStr">
+        <is>
+          <t>Wallet List</t>
+        </is>
+      </c>
+      <c r="C10" s="72" t="inlineStr">
+        <is>
+          <t>Every wallet names its currency, country, balance and what is blocked</t>
+        </is>
+      </c>
+      <c r="D10" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E10" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Wallet page</t>
+        </is>
+      </c>
+      <c r="F10" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Wallet page
+-Then every wallet should name its currency, country, balance and what is blocked</t>
+        </is>
+      </c>
+      <c r="G10" s="72" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H10" s="73" t="inlineStr">
+        <is>
+          <t>Every wallet should name its currency, its country, its balance and its blocked amount</t>
+        </is>
+      </c>
+      <c r="I10" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Wallet page</t>
+        </is>
+      </c>
+      <c r="J10" s="73" t="inlineStr">
+        <is>
+          <t>All 10 wallets named their currency, country, balance and blocked amount</t>
+        </is>
+      </c>
+      <c r="K10" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L10" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M10" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N10" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O10" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P10" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q10" s="70" t="n"/>
+      <c r="R10" s="70" t="n"/>
+      <c r="S10" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15.75" customHeight="1" s="51">
+      <c r="A11" s="67" t="inlineStr">
+        <is>
+          <t>TC_003</t>
+        </is>
+      </c>
+      <c r="B11" s="79" t="inlineStr">
+        <is>
+          <t>Wallet List</t>
+        </is>
+      </c>
+      <c r="C11" s="72" t="inlineStr">
+        <is>
+          <t>Exactly one wallet is the main wallet</t>
+        </is>
+      </c>
+      <c r="D11" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E11" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Wallet page</t>
+        </is>
+      </c>
+      <c r="F11" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Wallet page
+-Then exactly one wallet should be the main wallet</t>
+        </is>
+      </c>
+      <c r="G11" s="72" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H11" s="73" t="inlineStr">
+        <is>
+          <t>One wallet should be marked as the main wallet, and every other should offer to become it</t>
+        </is>
+      </c>
+      <c r="I11" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Wallet page</t>
+        </is>
+      </c>
+      <c r="J11" s="73" t="inlineStr">
+        <is>
+          <t>The main wallet was HKD, and the other 9 each offered to become it</t>
+        </is>
+      </c>
+      <c r="K11" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L11" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M11" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N11" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O11" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P11" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q11" s="70" t="n"/>
+      <c r="R11" s="70" t="n"/>
+      <c r="S11" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="51">
+      <c r="A12" s="67" t="inlineStr">
+        <is>
+          <t>TC_004</t>
+        </is>
+      </c>
+      <c r="B12" s="79" t="inlineStr">
+        <is>
+          <t>Wallet List</t>
+        </is>
+      </c>
+      <c r="C12" s="72" t="inlineStr">
+        <is>
+          <t>Each wallet states its balance and what is blocked in its own currency</t>
+        </is>
+      </c>
+      <c r="D12" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E12" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Wallet page</t>
+        </is>
+      </c>
+      <c r="F12" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Wallet page
+-Then each wallet's figures should be written in its own currency</t>
+        </is>
+      </c>
+      <c r="G12" s="72" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H12" s="73" t="inlineStr">
+        <is>
+          <t>A wallet's balance and its blocked amount should be written in the same currency symbol</t>
+        </is>
+      </c>
+      <c r="I12" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Wallet page</t>
+        </is>
+      </c>
+      <c r="J12" s="73" t="inlineStr">
+        <is>
+          <t>Every wallet used one symbol throughout: HKD=HK$, IDR=Rp, MYR=RM, USD=US$, BRL=R$, MXN=MXN$ and so on</t>
+        </is>
+      </c>
+      <c r="K12" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L12" s="74" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M12" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N12" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O12" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P12" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q12" s="70" t="n"/>
+      <c r="R12" s="70" t="n"/>
+      <c r="S12" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15.75" customHeight="1" s="51">
+      <c r="A13" s="67" t="inlineStr">
+        <is>
+          <t>TC_005</t>
+        </is>
+      </c>
+      <c r="B13" s="79" t="inlineStr">
+        <is>
+          <t>Wallet Chart</t>
+        </is>
+      </c>
+      <c r="C13" s="72" t="inlineStr">
+        <is>
+          <t>The chart only names countries the account holds a wallet for</t>
+        </is>
+      </c>
+      <c r="D13" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E13" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Wallet page</t>
+        </is>
+      </c>
+      <c r="F13" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Wallet page
+-Then every country in the chart should be one the account holds a wallet for</t>
+        </is>
+      </c>
+      <c r="G13" s="72" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H13" s="73" t="inlineStr">
+        <is>
+          <t>Every country in the assets chart should be one the account holds a wallet for</t>
+        </is>
+      </c>
+      <c r="I13" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Wallet page</t>
+        </is>
+      </c>
+      <c r="J13" s="73" t="inlineStr">
+        <is>
+          <t>The chart named Indonesia, Vietnam, Philippines, Malaysia and Bangladesh, all of them wallets the account holds</t>
+        </is>
+      </c>
+      <c r="K13" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L13" s="74" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M13" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N13" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O13" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P13" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q13" s="70" t="n"/>
+      <c r="R13" s="70" t="n"/>
+      <c r="S13" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1" s="51">
+      <c r="A14" s="67" t="inlineStr">
+        <is>
+          <t>TC_006</t>
+        </is>
+      </c>
+      <c r="B14" s="79" t="inlineStr">
+        <is>
+          <t>Wallet Detail</t>
+        </is>
+      </c>
+      <c r="C14" s="72" t="inlineStr">
+        <is>
+          <t>A wallet opens its own page</t>
+        </is>
+      </c>
+      <c r="D14" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E14" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Wallet page</t>
+        </is>
+      </c>
+      <c r="F14" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Wallet page
+-And I open the wallet named in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-Then that wallet's own page should open
+-And the wallet should state its total, what is available and what is locked</t>
+        </is>
+      </c>
+      <c r="G14" s="72" t="inlineStr">
+        <is>
+          <t>Wallet: HKD</t>
+        </is>
+      </c>
+      <c r="H14" s="73" t="inlineStr">
+        <is>
+          <t>Opening a wallet should go to that wallet's own page, stating its total, available and locked balances</t>
+        </is>
+      </c>
+      <c r="I14" s="73" t="inlineStr">
+        <is>
+          <t>User is on the wallet's own page</t>
+        </is>
+      </c>
+      <c r="J14" s="73" t="inlineStr">
+        <is>
+          <t>The HKD wallet opened at /v2/wallet/detail/record?currencyCode=HKD, stating all three balances</t>
+        </is>
+      </c>
+      <c r="K14" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L14" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M14" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N14" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O14" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P14" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q14" s="70" t="n"/>
+      <c r="R14" s="70" t="n"/>
+      <c r="S14" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1" s="51">
+      <c r="A15" s="67" t="inlineStr">
+        <is>
+          <t>TC_007</t>
+        </is>
+      </c>
+      <c r="B15" s="79" t="inlineStr">
+        <is>
+          <t>Wallet Detail</t>
+        </is>
+      </c>
+      <c r="C15" s="72" t="inlineStr">
+        <is>
+          <t>A wallet's total is what is available plus what is locked</t>
+        </is>
+      </c>
+      <c r="D15" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E15" s="71" t="inlineStr">
+        <is>
+          <t>User is on a wallet's own page</t>
+        </is>
+      </c>
+      <c r="F15" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Wallet page
+-And I open the wallet named in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-Then the wallet's total should be what is available plus what is locked</t>
+        </is>
+      </c>
+      <c r="G15" s="72" t="inlineStr">
+        <is>
+          <t>Wallet: HKD</t>
+        </is>
+      </c>
+      <c r="H15" s="73" t="inlineStr">
+        <is>
+          <t>The total balance should equal the available balance plus the amount locked</t>
+        </is>
+      </c>
+      <c r="I15" s="73" t="inlineStr">
+        <is>
+          <t>User is on the wallet's own page</t>
+        </is>
+      </c>
+      <c r="J15" s="73" t="inlineStr">
+        <is>
+          <t>8369.51 available plus 5544.32 locked came to the stated total of 13913.83</t>
+        </is>
+      </c>
+      <c r="K15" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L15" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M15" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N15" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O15" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P15" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q15" s="70" t="n"/>
+      <c r="R15" s="70" t="n"/>
+      <c r="S15" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="51">
+      <c r="A16" s="67" t="inlineStr">
+        <is>
+          <t>TC_008</t>
+        </is>
+      </c>
+      <c r="B16" s="79" t="inlineStr">
+        <is>
+          <t>Wallet Detail</t>
+        </is>
+      </c>
+      <c r="C16" s="72" t="inlineStr">
+        <is>
+          <t>A wallet keeps what has moved and what is held in two tabs</t>
+        </is>
+      </c>
+      <c r="D16" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E16" s="71" t="inlineStr">
+        <is>
+          <t>User is on a wallet's own page</t>
+        </is>
+      </c>
+      <c r="F16" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Wallet page
+-And I open the wallet named in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-Then the wallet should offer the tabs "Record, Locked"</t>
+        </is>
+      </c>
+      <c r="G16" s="72" t="inlineStr">
+        <is>
+          <t>Wallet: HKD</t>
+        </is>
+      </c>
+      <c r="H16" s="73" t="inlineStr">
+        <is>
+          <t>The wallet should offer a Record tab and a Locked tab</t>
+        </is>
+      </c>
+      <c r="I16" s="73" t="inlineStr">
+        <is>
+          <t>User is on the wallet's own page</t>
+        </is>
+      </c>
+      <c r="J16" s="73" t="inlineStr">
+        <is>
+          <t>The wallet offered both the Record and Locked tabs</t>
+        </is>
+      </c>
+      <c r="K16" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L16" s="74" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M16" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N16" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O16" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P16" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q16" s="70" t="n"/>
+      <c r="R16" s="70" t="n"/>
+      <c r="S16" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1" s="51">
+      <c r="A17" s="67" t="inlineStr">
+        <is>
+          <t>TC_009</t>
+        </is>
+      </c>
+      <c r="B17" s="79" t="inlineStr">
+        <is>
+          <t>Wallet Detail</t>
+        </is>
+      </c>
+      <c r="C17" s="72" t="inlineStr">
+        <is>
+          <t>The Record tab lists what has moved in that wallet</t>
+        </is>
+      </c>
+      <c r="D17" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E17" s="71" t="inlineStr">
+        <is>
+          <t>User is on a wallet's own page</t>
+        </is>
+      </c>
+      <c r="F17" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Wallet page
+-And I open the wallet named in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-And I move to the wallet's "Record" tab
+-Then every movement should name what it was, when it happened and how much</t>
+        </is>
+      </c>
+      <c r="G17" s="72" t="inlineStr">
+        <is>
+          <t>Wallet: HKD</t>
+        </is>
+      </c>
+      <c r="H17" s="73" t="inlineStr">
+        <is>
+          <t>Every movement should name what it was, when it happened and how much</t>
+        </is>
+      </c>
+      <c r="I17" s="73" t="inlineStr">
+        <is>
+          <t>User is on the wallet's own page</t>
+        </is>
+      </c>
+      <c r="J17" s="73" t="inlineStr">
+        <is>
+          <t>The Record tab listed 20 movements, the newest being Convert 2026-09-07 15:44:33 HK$-1</t>
+        </is>
+      </c>
+      <c r="K17" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L17" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M17" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N17" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O17" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P17" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q17" s="70" t="n"/>
+      <c r="R17" s="70" t="n"/>
+      <c r="S17" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15.75" customHeight="1" s="51">
+      <c r="A18" s="67" t="inlineStr">
+        <is>
+          <t>TC_010</t>
+        </is>
+      </c>
+      <c r="B18" s="79" t="inlineStr">
+        <is>
+          <t>Wallet Detail</t>
+        </is>
+      </c>
+      <c r="C18" s="72" t="inlineStr">
+        <is>
+          <t>The Locked tab lists what is being held against that wallet</t>
+        </is>
+      </c>
+      <c r="D18" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E18" s="71" t="inlineStr">
+        <is>
+          <t>User is on a wallet's own page</t>
+        </is>
+      </c>
+      <c r="F18" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Wallet page
+-And I open the wallet named in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-And I move to the wallet's "Locked" tab
+-Then every movement should name what it was, when it happened and how much</t>
+        </is>
+      </c>
+      <c r="G18" s="72" t="inlineStr">
+        <is>
+          <t>Wallet: HKD</t>
+        </is>
+      </c>
+      <c r="H18" s="73" t="inlineStr">
+        <is>
+          <t>Every held amount should name what it was, when it happened and how much</t>
+        </is>
+      </c>
+      <c r="I18" s="73" t="inlineStr">
+        <is>
+          <t>User is on the wallet's own page</t>
+        </is>
+      </c>
+      <c r="J18" s="73" t="inlineStr">
+        <is>
+          <t>The Locked tab listed 20 held amounts, the newest being Withdraw 2026-09-07 12:28:22 HK$-107</t>
+        </is>
+      </c>
+      <c r="K18" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L18" s="74" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M18" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N18" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O18" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P18" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q18" s="70" t="n"/>
+      <c r="R18" s="70" t="n"/>
+      <c r="S18" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="51">
+      <c r="A19" s="67" t="inlineStr">
+        <is>
+          <t>TC_011</t>
+        </is>
+      </c>
+      <c r="B19" s="79" t="inlineStr">
+        <is>
+          <t>Wallet Detail</t>
+        </is>
+      </c>
+      <c r="C19" s="72" t="inlineStr">
+        <is>
+          <t>A wallet's own page offers to make it the main wallet</t>
+        </is>
+      </c>
+      <c r="D19" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E19" s="71" t="inlineStr">
+        <is>
+          <t>User is on a wallet's own page</t>
+        </is>
+      </c>
+      <c r="F19" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Wallet page
+-And I open the wallet named in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-Then the wallet should offer to become the main wallet</t>
+        </is>
+      </c>
+      <c r="G19" s="72" t="inlineStr">
+        <is>
+          <t>Wallet: HKD</t>
+        </is>
+      </c>
+      <c r="H19" s="73" t="inlineStr">
+        <is>
+          <t>The wallet should offer a Set as main button</t>
+        </is>
+      </c>
+      <c r="I19" s="73" t="inlineStr">
+        <is>
+          <t>User is on the wallet's own page</t>
+        </is>
+      </c>
+      <c r="J19" s="73" t="inlineStr">
+        <is>
+          <t>The wallet offered to become the main wallet</t>
+        </is>
+      </c>
+      <c r="K19" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L19" s="74" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M19" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N19" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O19" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P19" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q19" s="70" t="n"/>
+      <c r="R19" s="70" t="n"/>
+      <c r="S19" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" s="51">
+      <c r="A20" s="67" t="inlineStr">
+        <is>
+          <t>TC_012</t>
+        </is>
+      </c>
+      <c r="B20" s="79" t="inlineStr">
+        <is>
+          <t>Wallet Detail</t>
+        </is>
+      </c>
+      <c r="C20" s="72" t="inlineStr">
+        <is>
+          <t>Going back from a wallet returns to the list</t>
+        </is>
+      </c>
+      <c r="D20" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E20" s="71" t="inlineStr">
+        <is>
+          <t>User is on a wallet's own page</t>
+        </is>
+      </c>
+      <c r="F20" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Wallet page
+-And I open the wallet named in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-Then that wallet's own page should open
+-When I go back to the wallets
+-Then the wallets should be listed again</t>
+        </is>
+      </c>
+      <c r="G20" s="72" t="inlineStr">
+        <is>
+          <t>Wallet: HKD</t>
+        </is>
+      </c>
+      <c r="H20" s="73" t="inlineStr">
+        <is>
+          <t>Going back should return to the list of wallets</t>
+        </is>
+      </c>
+      <c r="I20" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Wallet page</t>
+        </is>
+      </c>
+      <c r="J20" s="73" t="inlineStr">
+        <is>
+          <t>Going back returned to the wallet list, all 10 still listed</t>
+        </is>
+      </c>
+      <c r="K20" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L20" s="74" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M20" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N20" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O20" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P20" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q20" s="70" t="n"/>
+      <c r="R20" s="70" t="n"/>
+      <c r="S20" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" s="51">
+      <c r="A21" s="67" t="inlineStr">
+        <is>
+          <t>TC_013</t>
+        </is>
+      </c>
+      <c r="B21" s="79" t="inlineStr">
+        <is>
+          <t>Wallet Main</t>
+        </is>
+      </c>
+      <c r="C21" s="72" t="inlineStr">
+        <is>
+          <t>The main wallet can be moved to another wallet and put back</t>
+        </is>
+      </c>
+      <c r="D21" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E21" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Wallet page</t>
+        </is>
+      </c>
+      <c r="F21" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Wallet page
+-And I make the wallet named in "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;" the main one
+-Then that wallet should become the main one
+-When I put the main wallet back
+-Then the wallet that was main should be main again</t>
+        </is>
+      </c>
+      <c r="G21" s="72" t="inlineStr">
+        <is>
+          <t>Move the main wallet to IDR</t>
+        </is>
+      </c>
+      <c r="H21" s="73" t="inlineStr">
+        <is>
+          <t>The chosen wallet should become the main one, and setting the first one back should restore it</t>
+        </is>
+      </c>
+      <c r="I21" s="73" t="inlineStr">
+        <is>
+          <t>The main wallet is as it was found</t>
+        </is>
+      </c>
+      <c r="J21" s="73" t="inlineStr">
+        <is>
+          <t>The main wallet moved from HKD to IDR and was put back to HKD, with nothing asked first</t>
+        </is>
+      </c>
+      <c r="K21" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L21" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M21" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N21" s="103" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O21" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P21" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q21" s="70" t="n"/>
+      <c r="R21" s="70" t="n"/>
+      <c r="S21" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1" s="51">
+      <c r="A22" s="67" t="inlineStr">
+        <is>
+          <t>TC_014</t>
+        </is>
+      </c>
+      <c r="B22" s="79" t="inlineStr">
+        <is>
+          <t>Wallet</t>
+        </is>
+      </c>
+      <c r="C22" s="72" t="inlineStr">
+        <is>
+          <t>The wallet page and the home page agree about what each wallet holds</t>
+        </is>
+      </c>
+      <c r="D22" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E22" s="71" t="inlineStr">
+        <is>
+          <t>User is signed in</t>
+        </is>
+      </c>
+      <c r="F22" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I note what the home page says each wallet holds
+-And I open the Wallet page
+-Then the wallet page should agree with the home page about what each wallet holds</t>
+        </is>
+      </c>
+      <c r="G22" s="72" t="inlineStr">
+        <is>
+          <t>Valid UMPay user</t>
+        </is>
+      </c>
+      <c r="H22" s="73" t="inlineStr">
+        <is>
+          <t>Both screens draw the same balances and should agree about them - a wallet reading one figure where somebody lands and another where they go next is worse than either being wrong, because there is no way to tell which to believe</t>
+        </is>
+      </c>
+      <c r="I22" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Wallet page</t>
+        </is>
+      </c>
+      <c r="J22" s="73" t="inlineStr">
+        <is>
+          <t>Both screens agree about all ten wallets. They do write the same amount differently - the home page draws the Mexican wallet as 289.50 and the wallet page as 289.5 - so the figures are compared as numbers rather than as text</t>
+        </is>
+      </c>
+      <c r="K22" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L22" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M22" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N22" s="103" t="n">
+        <v>46274</v>
+      </c>
+      <c r="O22" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P22" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q22" s="70" t="n"/>
+      <c r="R22" s="70" t="n"/>
+      <c r="S22" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="7">
+    <dataValidation sqref="K9:K22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"PASS,FAIL,PENDING"</formula1>
+    </dataValidation>
+    <dataValidation sqref="P9:P22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>METADATA!$H$2:$H$8</formula1>
+    </dataValidation>
+    <dataValidation sqref="O9:O22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>METADATA!$J$2:$J$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="D9:D22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>METADATA!$N$2:$N$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="B4 M9:M22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>METADATA!$F$2:$F$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="L9:L22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"HIGH,MEDIUM,LOW"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"WPAY,UMPay,OFL,UNCS"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S14" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S16" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S19" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S20" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S21" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S22" r:id="rId14"/>
+  </hyperlinks>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.9840277777777779" bottom="0.9840277777777779" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="0" useFirstPageNumber="0" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S25"/>
+  <dimension ref="A1:T25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -12180,7 +12830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S22"/>
+  <dimension ref="A1:T22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -13760,7 +14410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -14983,7 +15633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:T21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -16479,7 +17129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:T16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1"/>
@@ -17364,30 +18014,119 @@
         </is>
       </c>
     </row>
+    <row r="16" ht="15.75" customHeight="1" s="51">
+      <c r="A16" s="67" t="inlineStr">
+        <is>
+          <t>TC_008</t>
+        </is>
+      </c>
+      <c r="B16" s="78" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C16" s="72" t="inlineStr">
+        <is>
+          <t>The terms can be read from the registration page</t>
+        </is>
+      </c>
+      <c r="D16" s="70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E16" s="71" t="inlineStr">
+        <is>
+          <t>User is on the registration page</t>
+        </is>
+      </c>
+      <c r="F16" s="72" t="inlineStr">
+        <is>
+          <t>-Given I am on the UMPay registration page
+-Then the registration page should offer its terms to be read
+-Then the terms should be linked to somewhere they can be read</t>
+        </is>
+      </c>
+      <c r="G16" s="72" t="inlineStr">
+        <is>
+          <t>No account needed</t>
+        </is>
+      </c>
+      <c r="H16" s="73" t="inlineStr">
+        <is>
+          <t>The page should say what is being agreed to and link somewhere it can be read, since somebody asked to accept terms they cannot read is agreeing to nothing they know</t>
+        </is>
+      </c>
+      <c r="I16" s="73" t="inlineStr">
+        <is>
+          <t>User is on the registration page</t>
+        </is>
+      </c>
+      <c r="J16" s="73" t="inlineStr">
+        <is>
+          <t>The page says "By creating an account, you accept our Terms and Conditions" and links to https://umpay.me/term-condition. The link is read rather than followed: it carries target=_blank and points outside the application, so following it would make the case depend on a marketing page loading. The locator for it had been written into the page object and was used by nothing at all</t>
+        </is>
+      </c>
+      <c r="K16" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L16" s="74" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M16" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N16" s="103" t="n">
+        <v>46274</v>
+      </c>
+      <c r="O16" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P16" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q16" s="70" t="n"/>
+      <c r="R16" s="70" t="n"/>
+      <c r="S16" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A8:AA14"/>
   <dataValidations count="7">
-    <dataValidation sqref="K9:K15" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
+    <dataValidation sqref="K9:K16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
       <formula1>"PASS,FAIL,PENDING"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="P9:P15" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
+    <dataValidation sqref="P9:P16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
       <formula1>METADATA!$H$2:$H$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="O9:O15" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
+    <dataValidation sqref="O9:O16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
       <formula1>METADATA!$J$2:$J$7</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="D9:D15" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
+    <dataValidation sqref="D9:D16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
       <formula1>METADATA!$N$2:$N$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="B4 M9:M15" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
+    <dataValidation sqref="B4 M9:M16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
       <formula1>METADATA!$F$2:$F$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="L9:L15" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
+    <dataValidation sqref="L9:L16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
       <formula1>"HIGH,MEDIUM,LOW"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -17404,6 +18143,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S14" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S16" r:id="rId8"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.9840277777777779" bottom="0.9840277777777779" header="0.511805555555555" footer="0.511805555555555"/>
@@ -17417,7 +18157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -18640,7 +19380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:T22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -20085,25 +20825,116 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1" s="51"/>
+    <row r="22" ht="15.75" customHeight="1" s="51">
+      <c r="A22" s="67" t="inlineStr">
+        <is>
+          <t>TC_014</t>
+        </is>
+      </c>
+      <c r="B22" s="79" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C22" s="72" t="inlineStr">
+        <is>
+          <t>Changing the phone number is refused when it is not a number</t>
+        </is>
+      </c>
+      <c r="D22" s="70" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E22" s="71" t="inlineStr">
+        <is>
+          <t>User is changing the phone number in the settings</t>
+        </is>
+      </c>
+      <c r="F22" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Settings page
+-And I open "Phone Number" from the settings
+-And I fill the phone form from "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-And I go on from the form
+-Then the form should refuse to go on</t>
+        </is>
+      </c>
+      <c r="G22" s="72" t="inlineStr">
+        <is>
+          <t>Phone: abcdef</t>
+        </is>
+      </c>
+      <c r="H22" s="73" t="inlineStr">
+        <is>
+          <t>The form should refuse a phone number that is not a number, as it already refuses an empty one</t>
+        </is>
+      </c>
+      <c r="I22" s="73" t="inlineStr">
+        <is>
+          <t>Nothing is changed</t>
+        </is>
+      </c>
+      <c r="J22" s="73" t="inlineStr">
+        <is>
+          <t>The form refused to go on. The email form was held to both an empty box and a malformed address and the phone form had only ever been held to the empty one - this is the other half of the same rule</t>
+        </is>
+      </c>
+      <c r="K22" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L22" s="74" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M22" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N22" s="103" t="n">
+        <v>46274</v>
+      </c>
+      <c r="O22" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P22" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q22" s="70" t="n"/>
+      <c r="R22" s="70" t="n"/>
+      <c r="S22" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="7">
-    <dataValidation sqref="K9:K21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K9:K22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"PASS,FAIL,PENDING"</formula1>
     </dataValidation>
-    <dataValidation sqref="P9:P21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P9:P22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>METADATA!$H$2:$H$8</formula1>
     </dataValidation>
-    <dataValidation sqref="O9:O21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O9:O22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>METADATA!$J$2:$J$7</formula1>
     </dataValidation>
-    <dataValidation sqref="D9:D21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D9:D22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>METADATA!$N$2:$N$3</formula1>
     </dataValidation>
-    <dataValidation sqref="B4 M9:M21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B4 M9:M22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>METADATA!$F$2:$F$4</formula1>
     </dataValidation>
-    <dataValidation sqref="L9:L21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L9:L22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"HIGH,MEDIUM,LOW"</formula1>
     </dataValidation>
     <dataValidation sqref="B1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -20124,6 +20955,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S19" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S20" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S21" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S22" r:id="rId14"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.9840277777777779" bottom="0.9840277777777779" header="0.511805555555555" footer="0.511805555555555"/>
@@ -20137,7 +20969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:T19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -21435,7 +22267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -22645,7 +23477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:T20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -24044,7 +24876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:T14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -24897,7 +25729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:T14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -25748,7 +26580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:T16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -41886,7 +42718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AA24"/>
+  <dimension ref="A1:AB24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="2"/>
@@ -43768,7 +44600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:T15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="2"/>
@@ -44572,29 +45404,120 @@
         </is>
       </c>
     </row>
+    <row r="15" ht="15.75" customHeight="1" s="51">
+      <c r="A15" s="67" t="inlineStr">
+        <is>
+          <t>TC_007</t>
+        </is>
+      </c>
+      <c r="B15" s="79" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="C15" s="72" t="inlineStr">
+        <is>
+          <t>The deposit amount box refuses anything that is not an amount</t>
+        </is>
+      </c>
+      <c r="D15" s="70" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E15" s="71" t="inlineStr">
+        <is>
+          <t>User is on the Deposit page with the HKD wallet chosen</t>
+        </is>
+      </c>
+      <c r="F15" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "1" of "Sheet1" of "Deposit_TestData.xlsx"
+-When I navigate to Deposit page
+-And I choose the "HKD" wallet on the Deposit page
+-And I type "&lt;typed&gt;" at the deposit amount box
+-Then the deposit amount box should be left holding nothing</t>
+        </is>
+      </c>
+      <c r="G15" s="72" t="inlineStr">
+        <is>
+          <t>Amount: abcd, 0, -100</t>
+        </is>
+      </c>
+      <c r="H15" s="73" t="inlineStr">
+        <is>
+          <t>None of these should be accepted as an amount, as the withdraw form already refuses them</t>
+        </is>
+      </c>
+      <c r="I15" s="73" t="inlineStr">
+        <is>
+          <t>User is on the Deposit page</t>
+        </is>
+      </c>
+      <c r="J15" s="73" t="inlineStr">
+        <is>
+          <t>None of the three reached the box. "abcd", "0" and "-100" each left it holding nothing at all, the same way the withdraw form behaves</t>
+        </is>
+      </c>
+      <c r="K15" s="53" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L15" s="53" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M15" s="70" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N15" s="103" t="n">
+        <v>46274</v>
+      </c>
+      <c r="O15" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P15" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q15" s="70" t="n"/>
+      <c r="R15" s="70" t="n"/>
+      <c r="S15" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="7">
-    <dataValidation sqref="K9:K14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
+    <dataValidation sqref="K9:K15" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
       <formula1>"PASS,FAIL,PENDING"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="P9:P14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
+    <dataValidation sqref="P9:P15" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
       <formula1>METADATA!$H$2:$H$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="O9:O14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
+    <dataValidation sqref="O9:O15" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
       <formula1>METADATA!$J$2:$J$7</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="D9:D14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
+    <dataValidation sqref="D9:D15" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
       <formula1>METADATA!$N$2:$N$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="B4 M9:M14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
+    <dataValidation sqref="B4 M9:M15" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
       <formula1>METADATA!$F$2:$F$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="L9:L14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
+    <dataValidation sqref="L9:L15" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
       <formula1>"HIGH,MEDIUM,LOW"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -44610,6 +45533,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S14" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId7"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.9840277777777779" bottom="0.9840277777777779" header="0.511805555555555" footer="0.511805555555555"/>
@@ -44623,7 +45547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:T16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="2"/>
@@ -45670,7 +46594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:T22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -47149,29 +48073,122 @@
         </is>
       </c>
     </row>
+    <row r="22" ht="15.75" customHeight="1" s="51">
+      <c r="A22" s="67" t="inlineStr">
+        <is>
+          <t>TC_014</t>
+        </is>
+      </c>
+      <c r="B22" s="79" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C22" s="72" t="inlineStr">
+        <is>
+          <t>A transfer aimed at the account making it is refused</t>
+        </is>
+      </c>
+      <c r="D22" s="70" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E22" s="71" t="inlineStr">
+        <is>
+          <t>User is on the UMPay wallet transfer form</t>
+        </is>
+      </c>
+      <c r="F22" s="72" t="inlineStr">
+        <is>
+          <t>-Given I log into the UMPay application with valid email credentials using "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-When I open the Transfer hub
+-And I take the "UMPay to UMPay Wallet" route from the Transfer hub
+-Then the UMPay wallet transfer form should be shown
+-When I name the recipient by "EMAIL"
+-And I give the recipient's "EMAIL" from "&lt;row&gt;" of "&lt;excelSheetName&gt;" of "&lt;excelFileName&gt;"
+-Then the wallet transfer should not be ready to continue</t>
+        </is>
+      </c>
+      <c r="G22" s="72" t="inlineStr">
+        <is>
+          <t>Recipient: the account signed in, named by email</t>
+        </is>
+      </c>
+      <c r="H22" s="73" t="inlineStr">
+        <is>
+          <t>Naming your own account as the recipient should leave the transfer unable to go on</t>
+        </is>
+      </c>
+      <c r="I22" s="73" t="inlineStr">
+        <is>
+          <t>Nothing is sent</t>
+        </is>
+      </c>
+      <c r="J22" s="73" t="inlineStr">
+        <is>
+          <t>Naming the signed-in account as the recipient left the transfer not ready to continue, so it cannot be built at all. The recipient cases already in the file all name somebody who does not exist, which is a different question - this one names somebody who very much does</t>
+        </is>
+      </c>
+      <c r="K22" s="74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L22" s="74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M22" s="58" t="inlineStr">
+        <is>
+          <t>KIMA</t>
+        </is>
+      </c>
+      <c r="N22" s="103" t="n">
+        <v>46274</v>
+      </c>
+      <c r="O22" s="53" t="inlineStr">
+        <is>
+          <t>Window OS</t>
+        </is>
+      </c>
+      <c r="P22" s="76" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="Q22" s="70" t="n"/>
+      <c r="R22" s="70" t="n"/>
+      <c r="S22" s="77" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="7">
-    <dataValidation sqref="K9:K21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
+    <dataValidation sqref="K9:K22" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
       <formula1>"PASS,FAIL,PENDING"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="P9:P21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
+    <dataValidation sqref="P9:P22" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
       <formula1>METADATA!$H$2:$H$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="O9:O21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
+    <dataValidation sqref="O9:O22" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
       <formula1>METADATA!$J$2:$J$7</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="D9:D21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
+    <dataValidation sqref="D9:D22" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
       <formula1>METADATA!$N$2:$N$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="B4 M9:M21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
+    <dataValidation sqref="B4 M9:M22" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
       <formula1>METADATA!$F$2:$F$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="L9:L21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
+    <dataValidation sqref="L9:L22" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" operator="between">
       <formula1>"HIGH,MEDIUM,LOW"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -47194,6 +48211,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S19" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S20" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S21" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S22" r:id="rId14"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.9840277777777779" bottom="0.9840277777777779" header="0.511805555555555" footer="0.511805555555555"/>
@@ -47207,7 +48225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:T19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="2"/>
@@ -48518,7 +49536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:T20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>
@@ -49951,7 +50969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:T16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.63" customWidth="1" style="50" min="1" max="1025"/>

--- a/TestCase/UMPay End-to-End Test Cases.xlsx
+++ b/TestCase/UMPay End-to-End Test Cases.xlsx
@@ -27400,12 +27400,12 @@
       </c>
       <c r="C15" s="72" t="inlineStr">
         <is>
-          <t>What is held against a wallet is never shown as a negative amount</t>
+          <t>What is held against every wallet is written as a deduction</t>
         </is>
       </c>
       <c r="D15" s="70" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="E15" s="71" t="inlineStr">
@@ -27419,7 +27419,7 @@
 -When I am on the home page
 -And I reveal the amounts
 -And I show more wallets
--Then no wallet should show what is held against it as a negative amount</t>
+-Then what is held against every wallet should be written as a deduction</t>
         </is>
       </c>
       <c r="G15" s="72" t="inlineStr">
@@ -27429,7 +27429,7 @@
       </c>
       <c r="H15" s="73" t="inlineStr">
         <is>
-          <t>What is held against a wallet should be written as a quantity of money set aside rather than as a negative amount, which reads as money the account is owed</t>
+          <t>What is held against a wallet should be written as a deduction, which is the platform own convention - money set aside is shown as taken off what the wallet has rather than as a quantity beside it</t>
         </is>
       </c>
       <c r="I15" s="73" t="inlineStr">
@@ -27439,12 +27439,12 @@
       </c>
       <c r="J15" s="73" t="inlineStr">
         <is>
-          <t>DEFECT - every one of the ten wallets writes what is held against it as a negative amount: HKD -5970.32, IDR -30000, VND -350000, PHP -3282, MYR -60, BDT -14040, USD -292.96, THB -2094.16, MXN -98.08 and BRL -202.4, and the total reads "Total Blocked Amount: HK$ -10,684.58". The wallet page at /v2/wallet writes them the same way, so this is the figure the platform serves rather than a fault in one screen. Money set aside is a quantity, not a debt - a minus in front of it reads as money the account is owed rather than money it cannot spend</t>
+          <t>All ten wallets write what is held against them as a deduction: HKD -5970.32, IDR -30000, VND -350000, PHP -3282, MYR -60, BDT -14040, USD -292.96, THB -2094.16, MXN -98.08 and BRL -202.4, with the total reading -10,684.58. This case was first written the other way round, asserting that nothing held should ever be negative, and recorded the convention itself as a defect. It is expected behaviour and the case now holds the platform to it, so a wallet breaking the convention is what would fail</t>
         </is>
       </c>
       <c r="K15" s="74" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L15" s="74" t="inlineStr">
@@ -27458,7 +27458,7 @@
         </is>
       </c>
       <c r="N15" s="103" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="O15" s="53" t="inlineStr">
         <is>
